--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -15,6 +15,7 @@
     <sheet name="Mobile AMR" sheetId="6" state="visible" r:id="rId6"/>
     <sheet name="Representatives" sheetId="7" state="visible" r:id="rId7"/>
     <sheet name="Vehicle Types" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="Field Fallbacks" sheetId="9" state="visible" r:id="rId9"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1" refMode="A1" iterate="0" iterateCount="100" iterateDelta="0.0001"/>
@@ -2614,8 +2615,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2630,7 +2631,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K64"/>
+  <dimension ref="A1:N64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -2708,6 +2709,21 @@
           <t>Tender JSON Key</t>
         </is>
       </c>
+      <c r="L2" s="43" t="inlineStr">
+        <is>
+          <t>Scoring Rule</t>
+        </is>
+      </c>
+      <c r="M2" s="43" t="inlineStr">
+        <is>
+          <t>Threshold 1</t>
+        </is>
+      </c>
+      <c r="N2" s="43" t="inlineStr">
+        <is>
+          <t>Threshold 2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -2749,7 +2765,7 @@
       </c>
       <c r="G4" s="66" t="inlineStr">
         <is>
-          <t>Navigation technology. Output from allowed values only, comma-separated. null = not stated.</t>
+          <t>Navigation technology used by the AGV. Output from allowed values only, comma-separated. Mapping rules: 'SLAM' / 'natural feature' / 'free navigation' / 'marker-free' / 'environment mapping' / 'contour-based' → 'Natural Feature (SLAM)'; 'laser reflector' / 'reflector marker' / 'laser scanner with reflectors' → 'Laser Reflector'; 'magnetic tape' / 'magnetic stripe' → 'Magnetic Tape'; 'QR code' / 'barcode' / 'data matrix' → 'QR/DM Code'; 'inductive loop' / 'wire guidance' → 'Inductive Loop'; 'vision' / 'camera-based' → 'Vision'. If multiple navigation types are required, list all. null = not stated in the document.</t>
         </is>
       </c>
       <c r="H4" s="73" t="n"/>
@@ -2964,7 +2980,7 @@
       </c>
       <c r="G10" s="66" t="inlineStr">
         <is>
-          <t>Max rated load. Source: spec 'payload / load capacity'. Hard filter vs. the buyer's heaviest unit load. Use rated, not peak.</t>
+          <t>Maximum payload the AGV must carry per trip. CONSERVATIVE RULE (KO_IF_LT): extract the MAXIMUM loaded weight found in the document — the supplier must meet or exceed this. In pallet tables: use 'Max Loaded weight' / 'gross weight' — IGNORE 'tare weight' / 'empty pallet weight'. If multiple load types are listed, report the heaviest. Output in kg. Null if not stated anywhere.</t>
         </is>
       </c>
       <c r="H10" s="73" t="n"/>
@@ -3551,6 +3567,17 @@
       <c r="J25" s="100" t="n">
         <v>5</v>
       </c>
+      <c r="L25" s="43" t="inlineStr">
+        <is>
+          <t>tiered_lower</t>
+        </is>
+      </c>
+      <c r="M25" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="N25" s="43" t="n">
+        <v>30</v>
+      </c>
     </row>
     <row r="26" ht="15.75" customHeight="1" s="44">
       <c r="A26" s="72" t="inlineStr">
@@ -3637,6 +3664,14 @@
       <c r="J28" s="100" t="n">
         <v>7</v>
       </c>
+      <c r="L28" s="43" t="inlineStr">
+        <is>
+          <t>threshold_upper</t>
+        </is>
+      </c>
+      <c r="M28" s="43" t="n">
+        <v>8</v>
+      </c>
     </row>
     <row r="29" ht="33.75" customHeight="1" s="44">
       <c r="A29" s="64" t="inlineStr">
@@ -3716,6 +3751,11 @@
       <c r="J30" s="100" t="n">
         <v>6</v>
       </c>
+      <c r="L30" s="43" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="31" ht="33.75" customHeight="1" s="44">
       <c r="A31" s="64" t="inlineStr">
@@ -3806,6 +3846,11 @@
       <c r="J33" s="100" t="n">
         <v>5</v>
       </c>
+      <c r="L33" s="43" t="inlineStr">
+        <is>
+          <t>nonempty</t>
+        </is>
+      </c>
     </row>
     <row r="34" ht="33.75" customHeight="1" s="44">
       <c r="A34" s="67" t="inlineStr">
@@ -3929,7 +3974,7 @@
       <c r="H37" s="73" t="n"/>
       <c r="I37" s="43" t="inlineStr">
         <is>
-          <t>KO_BOOL_REQUIRED</t>
+          <t>KO_SUBSET</t>
         </is>
       </c>
       <c r="K37" s="43" t="inlineStr">
@@ -4024,6 +4069,11 @@
       <c r="K39" s="43" t="inlineStr">
         <is>
           <t>required_vda5050</t>
+        </is>
+      </c>
+      <c r="L39" s="43" t="inlineStr">
+        <is>
+          <t>bool_cond</t>
         </is>
       </c>
     </row>
@@ -4316,6 +4366,14 @@
       <c r="J48" s="100" t="n">
         <v>15</v>
       </c>
+      <c r="L48" s="43" t="inlineStr">
+        <is>
+          <t>proportional</t>
+        </is>
+      </c>
+      <c r="M48" s="43" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="49" ht="33.75" customHeight="1" s="44">
       <c r="A49" s="67" t="inlineStr">
@@ -4352,6 +4410,17 @@
       <c r="H49" s="77" t="n"/>
       <c r="J49" s="100" t="n">
         <v>10</v>
+      </c>
+      <c r="L49" s="43" t="inlineStr">
+        <is>
+          <t>tiered_lower</t>
+        </is>
+      </c>
+      <c r="M49" s="43" t="n">
+        <v>26</v>
+      </c>
+      <c r="N49" s="43" t="n">
+        <v>52</v>
       </c>
     </row>
     <row r="50" ht="33.75" customHeight="1" s="44">
@@ -4928,7 +4997,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K31"/>
+  <dimension ref="A1:N31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -5006,6 +5075,21 @@
           <t>Tender JSON Key</t>
         </is>
       </c>
+      <c r="L2" s="43" t="inlineStr">
+        <is>
+          <t>Scoring Rule</t>
+        </is>
+      </c>
+      <c r="M2" s="43" t="inlineStr">
+        <is>
+          <t>Threshold 1</t>
+        </is>
+      </c>
+      <c r="N2" s="43" t="inlineStr">
+        <is>
+          <t>Threshold 2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -5193,7 +5277,7 @@
       </c>
       <c r="I7" s="43" t="inlineStr">
         <is>
-          <t>KO_IF_LT</t>
+          <t>KO_SUBSET</t>
         </is>
       </c>
       <c r="K7" s="43" t="inlineStr">
@@ -5269,7 +5353,7 @@
       </c>
       <c r="G9" s="69" t="inlineStr">
         <is>
-          <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If doc states mm (e.g. 2700 mm) → divide by 1000 → 2.7. Hard filter; decisive for VNA.</t>
+          <t>Minimum working aisle width available in the facility, in METERS (not mm). CONSERVATIVE RULE (KO_IF_GT): if multiple aisle widths are stated, extract the MINIMUM — this is the tightest constraint. Example: '2000 mm rack-to-rack, min 1900 mm pallet-to-pallet' → output 1.9. If doc states mm → divide by 1000. Source: 'Gangbreite', 'aisle width', 'corridor width'. Hard filter: decisive for VNA and narrow-aisle forklifts. Null if not stated.</t>
         </is>
       </c>
       <c r="H9" s="77" t="n"/>
@@ -5353,7 +5437,7 @@
       </c>
       <c r="D12" s="81" t="inlineStr">
         <is>
-          <t>K.O.</t>
+          <t>Cond. K.O.</t>
         </is>
       </c>
       <c r="E12" s="76" t="inlineStr">
@@ -5368,7 +5452,7 @@
       </c>
       <c r="G12" s="66" t="inlineStr">
         <is>
-          <t>Forklift drive category. RULE: if required_vna=true → always output 'VNA Turret' (VNA turret trucks are a distinct drive type). Counterbalanced = wide-aisle floor transport (≥3 m), NOT VNA. Output from allowed values only.</t>
+          <t>Forklift drive category. RULE: if required_vna=true → always output 'VNA Turret'. OTHERWISE: ONLY output if the tender document explicitly names the drive type (e.g. 'Gegengewichtsstapler', 'counterbalanced forklift required', 'Schubmaststapler'). DO NOT infer from the task description alone — floor-level pallet transport does NOT imply Counterbalanced; only output if the buyer specifies it. Output from allowed values only, or null.</t>
         </is>
       </c>
       <c r="H12" s="73" t="n"/>
@@ -5429,6 +5513,14 @@
       </c>
       <c r="J14" s="100" t="n">
         <v>8</v>
+      </c>
+      <c r="L14" s="43" t="inlineStr">
+        <is>
+          <t>threshold_lower</t>
+        </is>
+      </c>
+      <c r="M14" s="43" t="n">
+        <v>20</v>
       </c>
     </row>
     <row r="15" ht="33.75" customHeight="1" s="44">
@@ -5539,6 +5631,14 @@
       <c r="J17" s="100" t="n">
         <v>6</v>
       </c>
+      <c r="L17" s="43" t="inlineStr">
+        <is>
+          <t>threshold_lower</t>
+        </is>
+      </c>
+      <c r="M17" s="43" t="n">
+        <v>20</v>
+      </c>
     </row>
     <row r="18" ht="33.75" customHeight="1" s="44">
       <c r="A18" s="64" t="inlineStr">
@@ -5703,6 +5803,11 @@
       <c r="K22" s="43" t="inlineStr">
         <is>
           <t>required_stacking</t>
+        </is>
+      </c>
+      <c r="L22" s="43" t="inlineStr">
+        <is>
+          <t>bool</t>
         </is>
       </c>
     </row>
@@ -6024,7 +6129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K20"/>
+  <dimension ref="A1:N20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -6102,6 +6207,21 @@
           <t>Tender JSON Key</t>
         </is>
       </c>
+      <c r="L2" s="43" t="inlineStr">
+        <is>
+          <t>Scoring Rule</t>
+        </is>
+      </c>
+      <c r="M2" s="43" t="inlineStr">
+        <is>
+          <t>Threshold 1</t>
+        </is>
+      </c>
+      <c r="N2" s="43" t="inlineStr">
+        <is>
+          <t>Threshold 2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -6300,6 +6420,11 @@
           <t>required_auto_hitch</t>
         </is>
       </c>
+      <c r="L7" s="43" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="33.75" customHeight="1" s="44">
       <c r="A8" s="64" t="inlineStr">
@@ -6499,6 +6624,11 @@
       </c>
       <c r="J13" s="100" t="n">
         <v>6</v>
+      </c>
+      <c r="L13" s="43" t="inlineStr">
+        <is>
+          <t>nonempty</t>
+        </is>
       </c>
     </row>
     <row r="14" ht="15.75" customHeight="1" s="44">
@@ -6787,7 +6917,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:K45"/>
+  <dimension ref="A1:N45"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -6865,6 +6995,21 @@
           <t>Tender JSON Key</t>
         </is>
       </c>
+      <c r="L2" s="43" t="inlineStr">
+        <is>
+          <t>Scoring Rule</t>
+        </is>
+      </c>
+      <c r="M2" s="43" t="inlineStr">
+        <is>
+          <t>Threshold 1</t>
+        </is>
+      </c>
+      <c r="N2" s="43" t="inlineStr">
+        <is>
+          <t>Threshold 2</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -7013,6 +7158,11 @@
       <c r="J6" s="100" t="n">
         <v>7</v>
       </c>
+      <c r="L6" s="43" t="inlineStr">
+        <is>
+          <t>bool</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="33.75" customHeight="1" s="44">
       <c r="A7" s="67" t="inlineStr">
@@ -7872,6 +8022,17 @@
       </c>
       <c r="J31" s="100" t="n">
         <v>8</v>
+      </c>
+      <c r="L31" s="43" t="inlineStr">
+        <is>
+          <t>tiered_upper</t>
+        </is>
+      </c>
+      <c r="M31" s="43" t="n">
+        <v>300</v>
+      </c>
+      <c r="N31" s="43" t="n">
+        <v>150</v>
       </c>
     </row>
     <row r="32" ht="33.75" customHeight="1" s="44">
@@ -8897,7 +9058,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G15"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" style="44" min="1" max="1"/>
@@ -9076,12 +9237,12 @@
       <c r="E6" s="104" t="inlineStr"/>
       <c r="F6" s="104" t="inlineStr">
         <is>
-          <t>AGV transports pallets on wide aisles (≥3m) or open floor between fixed transfer stations, floor-level pickup/deposit</t>
+          <t>AGV transports pallets on wide aisles (≥3m) or open floor between fixed transfer stations, floor-level pickup/deposit. USE THIS for heavy pallet transport (&gt;1000 kg) in F&amp;B, food production, or manufacturing environments — even when MES or OPC-UA integration is mentioned. The presence of filling lines or MES does NOT imply Mobile AMR if payload is heavy.</t>
         </is>
       </c>
       <c r="G6" s="104" t="inlineStr">
         <is>
-          <t>≥3m aisle, floor transport, transfer stations, warehouse/logistics</t>
+          <t>≥3m aisle, floor transport, transfer stations, warehouse/logistics, heavy pallet (&gt;1000 kg)</t>
         </is>
       </c>
     </row>
@@ -9215,18 +9376,18 @@
       </c>
       <c r="D11" s="104" t="inlineStr">
         <is>
-          <t>amr|mobile robot|fahrroboter|autonomer</t>
+          <t>amr|mobile robot|fahrroboter|autonomer|goods-to-person|goods to person</t>
         </is>
       </c>
       <c r="E11" s="104" t="inlineStr"/>
       <c r="F11" s="104" t="inlineStr">
         <is>
-          <t>Autonomous robot in PRODUCTION or MANUFACTURING environment (filling lines, assembly, processing), or with conveyor/shelf top modules, SLAM navigation, dispatched from MES/WMS. Payload typically &lt;1500 kg.</t>
+          <t>Autonomous robot in PRODUCTION or MANUFACTURING environment (filling lines, assembly, processing), or with conveyor/shelf top modules, SLAM navigation, dispatched from MES/WMS. ONLY use for LIGHT payloads (typically &lt;1000 kg). If payload &gt;1000 kg or if the task is heavy pallet transport → use Forklift AGV instead.</t>
         </is>
       </c>
       <c r="G11" s="104" t="inlineStr">
         <is>
-          <t>production, filling lines, manufacturing, SLAM, MES</t>
+          <t>production, filling lines, manufacturing, SLAM, MES — BUT only if payload &lt;1000 kg</t>
         </is>
       </c>
     </row>
@@ -9337,6 +9498,130 @@
       <c r="E15" s="104" t="inlineStr"/>
       <c r="F15" s="104" t="inlineStr"/>
       <c r="G15" s="104" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" s="43" t="inlineStr">
+        <is>
+          <t>AGV</t>
+        </is>
+      </c>
+      <c r="B16" s="43" t="inlineStr">
+        <is>
+          <t>Forklift AGV</t>
+        </is>
+      </c>
+      <c r="C16" s="43" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="D16" s="43" t="inlineStr">
+        <is>
+          <t>agv</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:E4"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="43" t="inlineStr">
+        <is>
+          <t>Text-based fallbacks for fields the LLM reliably misses. generate_all.py reads these into vehicle_types.json → field_text_fallbacks. app.py applies them after LLM extraction when the field is null.</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" s="43" t="inlineStr">
+        <is>
+          <t>Tender Key</t>
+        </is>
+      </c>
+      <c r="B2" s="43" t="inlineStr">
+        <is>
+          <t>Regex (applied to full PDF text)</t>
+        </is>
+      </c>
+      <c r="C2" s="43" t="inlineStr">
+        <is>
+          <t>Fallback Value (AP0 allowed value)</t>
+        </is>
+      </c>
+      <c r="D2" s="43" t="inlineStr">
+        <is>
+          <t>Only If Null</t>
+        </is>
+      </c>
+      <c r="E2" s="43" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" s="43" t="inlineStr">
+        <is>
+          <t>required_navigation</t>
+        </is>
+      </c>
+      <c r="B3" s="43" t="inlineStr">
+        <is>
+          <t>(?i)\bSLAM\b</t>
+        </is>
+      </c>
+      <c r="C3" s="43" t="inlineStr">
+        <is>
+          <t>Natural Feature (SLAM)</t>
+        </is>
+      </c>
+      <c r="D3" s="43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E3" s="43" t="inlineStr">
+        <is>
+          <t>SLAM keyword in document → infer SLAM navigation when LLM extraction returns null</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" s="43" t="inlineStr">
+        <is>
+          <t>required_navigation</t>
+        </is>
+      </c>
+      <c r="B4" s="43" t="inlineStr">
+        <is>
+          <t>(?i)(natural[\s\-]feature|marker[\s\-]free|free[\s\-]navigat)</t>
+        </is>
+      </c>
+      <c r="C4" s="43" t="inlineStr">
+        <is>
+          <t>Natural Feature (SLAM)</t>
+        </is>
+      </c>
+      <c r="D4" s="43" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="E4" s="43" t="inlineStr">
+        <is>
+          <t>Natural feature / marker-free / free navigation wording → SLAM</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -2615,8 +2615,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -3225,7 +3225,7 @@
       <c r="F17" s="77" t="n"/>
       <c r="G17" s="69" t="inlineStr">
         <is>
-          <t>Lowest rated operating temperature. Source: 'working temperature'. Cond. K.O.: binds only for cold stores/freezers (-25 °C); standard units bottom out near 0–5 °C.</t>
+          <t>Lowest rated operating temperature. Source: 'working temperature' in environment/operating conditions section. Cond. K.O.: binds only for cold stores/freezers (-25 °C); standard units bottom out near 0–5 °C. NULL RULE: ONLY extract from an explicit °C value in a technical specification section. Do NOT confuse with dates (e.g. '25th May', '2022-05-25'), revision numbers, or project metadata — these are never temperatures. If no operating temperature range is stated → null.</t>
         </is>
       </c>
       <c r="H17" s="77" t="n"/>
@@ -3269,7 +3269,7 @@
       <c r="F18" s="73" t="n"/>
       <c r="G18" s="66" t="inlineStr">
         <is>
-          <t>Highest rated operating temperature. Source: 'working temperature'. Cond. K.O.: relevant only for hot production halls.</t>
+          <t>Highest rated operating temperature. Source: 'working temperature' in environment/operating conditions section. Cond. K.O.: relevant only for hot production halls. NULL RULE: ONLY extract from an explicit °C value in a technical specification. Do NOT confuse with dates, year numbers, or version codes. If not stated → null.</t>
         </is>
       </c>
       <c r="H18" s="73" t="n"/>
@@ -3313,7 +3313,7 @@
       <c r="F19" s="77" t="n"/>
       <c r="G19" s="69" t="inlineStr">
         <is>
-          <t>Max rated relative humidity (non-condensing unless stated). Source: environment spec. Cond. K.O.: binds for wet/washdown areas; pair with ingress_protection_rating.</t>
+          <t>Max rated relative humidity (non-condensing unless stated). Source: environment spec — must appear as a % value. Cond. K.O.: binds for wet/washdown areas; pair with ingress_protection_rating. NULL RULE: null unless a humidity percentage is explicitly stated. Do NOT infer from warehouse type, food industry context, or cold-storage environment.</t>
         </is>
       </c>
       <c r="H19" s="77" t="n"/>
@@ -3357,7 +3357,7 @@
       <c r="F20" s="73" t="n"/>
       <c r="G20" s="66" t="inlineStr">
         <is>
-          <t>IP code for dust/water resistance. Source: spec 'IP rating'. Cond. K.O.: IP52+ binds for dust/moisture/washdown (F&amp;B, beverage); standard AMRs ≈ IP20. 'None' = no rating stated.</t>
+          <t>IP code for dust/water resistance. Source: spec 'IP rating' — must be explicitly printed (e.g. 'IP54', 'IP65'). Cond. K.O.: IP52+ binds for dust/moisture/washdown (F&amp;B, beverage); standard AMRs ≈ IP20. 'None' = no rating stated. NULL RULE: null if no IP code is explicitly stated. Warehouse type, AGV type, and storage environment do NOT imply an IP rating — a VNA high-bay warehouse is NOT necessarily IP65.</t>
         </is>
       </c>
       <c r="H20" s="83" t="inlineStr">
@@ -3453,7 +3453,7 @@
       <c r="F22" s="73" t="n"/>
       <c r="G22" s="66" t="inlineStr">
         <is>
-          <t>Max ramp gradient the loaded unit handles. Source: spec 'gradeability'. Cond. K.O.: binds only where the site has ramps/dock inclines. (moved here — applies to all types)</t>
+          <t>Max ramp gradient the loaded unit handles. Source: spec 'gradeability' — must appear as an explicit % value. Cond. K.O.: binds only where the site has ramps/dock inclines. NULL RULE: null unless a slope or gradient percentage is explicitly stated in the document. Do NOT apply typical industry values (e.g. '5%') when the document is silent on gradients.</t>
         </is>
       </c>
       <c r="H22" s="83" t="inlineStr">
@@ -3501,7 +3501,7 @@
       <c r="F23" s="77" t="n"/>
       <c r="G23" s="69" t="inlineStr">
         <is>
-          <t>Floor flatness the system requires for safe operation/high-lift. Source: install requirements. Cond. K.O.: binds when the site floor is below spec → costly grinding. (moved here — applies to all types)</t>
+          <t>Floor flatness the system requires for safe operation/high-lift. Source: install requirements — must name a standard or value. Cond. K.O.: binds when the site floor is below spec → costly grinding. NULL RULE: null unless a floor quality standard (DIN 15185, FM number, FF number, etc.) or explicit flatness value is named. Do NOT infer from VNA or high-bay context.</t>
         </is>
       </c>
       <c r="H23" s="83" t="inlineStr">
@@ -4050,7 +4050,7 @@
       <c r="F39" s="73" t="n"/>
       <c r="G39" s="66" t="inlineStr">
         <is>
-          <t>Supports VDA 5050 (open AGV↔master-control interface standard). Source: 'VDA 5050 ready'. Cond. K.O.: trending to a hard requirement for large EU multi-vendor tenders.</t>
+          <t>Supports VDA 5050 (open AGV↔master-control interface standard). Source: 'VDA 5050 ready' or 'VDA-5050'. Cond. K.O.: trending to a hard requirement for large EU multi-vendor tenders. NULL RULE: null unless the document literally contains 'VDA 5050' or 'VDA-5050'. Do NOT infer from fleet management, MES/WMS integration, or system openness requirements.</t>
         </is>
       </c>
       <c r="H39" s="83" t="inlineStr">
@@ -5437,7 +5437,7 @@
       </c>
       <c r="D12" s="81" t="inlineStr">
         <is>
-          <t>Cond. K.O.</t>
+          <t>Context</t>
         </is>
       </c>
       <c r="E12" s="76" t="inlineStr">
@@ -5452,15 +5452,17 @@
       </c>
       <c r="G12" s="66" t="inlineStr">
         <is>
-          <t>Forklift drive category. RULE: if required_vna=true → always output 'VNA Turret'. OTHERWISE: ONLY output if the tender document explicitly names the drive type (e.g. 'Gegengewichtsstapler', 'counterbalanced forklift required', 'Schubmaststapler'). DO NOT infer from the task description alone — floor-level pallet transport does NOT imply Counterbalanced; only output if the buyer specifies it. Output from allowed values only, or null.</t>
+          <t>Forklift drive category — describes the physical build of the forklift mechanism. There are five types:
+- Counterbalanced (Gegengewichtsstapler): rear counterweight, no front support legs, forks fully exposed. Can pick pallets directly from the floor and mate with closed conveyors. Wide aisles (≥3 m).
+- Reach Truck (Schubmaststapler): forks extend forward between two front legs. Handles racking in medium aisles (2–3 m), lifts up to ~8 m.
+- Straddle Stacker (Spreizenstapler): load sits between the front legs. Narrower aisles and higher lift than a reach truck.
+- Pallet Mover (Niederhubwagen): low-profile, floor-to-floor transport only, no high-lift to racking.
+- VNA Turret (Schmalgangstapler): only the turret rotates, not the chassis. Ultra-narrow aisles (&lt;2 m), high-bay racking up to 17 m. Always wire- or rail-guided in the aisle.
+EXTRACTION RULE: if required_vna=true → always output 'VNA Turret'. Otherwise: ONLY output if the buyer explicitly names a drive type or forklift category in the document (e.g. 'Gegengewichtsstapler', 'counterbalanced forklift', 'Schubmaststapler', 'reach truck required'). DO NOT infer from the task — floor-level pallet transport does NOT imply Counterbalanced. Output null if the buyer does not specify a drive type.</t>
         </is>
       </c>
       <c r="H12" s="73" t="n"/>
-      <c r="I12" s="102" t="inlineStr">
-        <is>
-          <t>KO_SUBSET</t>
-        </is>
-      </c>
+      <c r="I12" s="102" t="n"/>
       <c r="K12" s="43" t="inlineStr">
         <is>
           <t>required_drive_type</t>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -460,7 +460,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="2">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -483,6 +483,50 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="thin">
+        <color rgb="FFDDDDDD"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFDDDDDD"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFDDDDDD"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1">
@@ -494,7 +538,7 @@
     <xf numFmtId="42" fontId="3" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="106">
+  <cellXfs count="108">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="general" vertical="bottom"/>
     </xf>
@@ -781,6 +825,8 @@
     <xf numFmtId="0" fontId="41" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="42" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="43" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="5" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -2615,8 +2661,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2813,7 +2859,7 @@
       </c>
       <c r="G5" s="69" t="inlineStr">
         <is>
-          <t>Physical infrastructure required on-site (e.g. reflectors, magnets, grid). Cond. K.O.: scored by default; hard filter only when buyer cannot accept infrastructure modifications.</t>
+          <t>Specifies what physical navigation infrastructure must be permanently installed on-site for the AGV to operate (e.g. reflectors for laser navigation, magnetic tape or inductive loops embedded in the floor). Cond. K.O.: scored by default; hard filter only when buyer cannot accept infrastructure modifications. NULL RULE: null unless the document explicitly names a required infrastructure type — do NOT infer from AGV category, navigation technology, or industry context.</t>
         </is>
       </c>
       <c r="H5" s="77" t="n"/>
@@ -2866,9 +2912,17 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="J6" s="43" t="n">
+        <v>2</v>
+      </c>
       <c r="K6" s="105" t="inlineStr">
         <is>
           <t>required_outdoor</t>
+        </is>
+      </c>
+      <c r="L6" s="43" t="inlineStr">
+        <is>
+          <t>bool_cond</t>
         </is>
       </c>
     </row>
@@ -2980,7 +3034,7 @@
       </c>
       <c r="G10" s="66" t="inlineStr">
         <is>
-          <t>Maximum payload the AGV must carry per trip. CONSERVATIVE RULE (KO_IF_LT): extract the MAXIMUM loaded weight found in the document — the supplier must meet or exceed this. In pallet tables: use 'Max Loaded weight' / 'gross weight' — IGNORE 'tare weight' / 'empty pallet weight'. If multiple load types are listed, report the heaviest. Output in kg. Null if not stated anywhere.</t>
+          <t>Maximum payload the AGV must carry per trip, in kg. This value may appear as prose (e.g. 'a maximum of X kg', 'loads up to X kg', 'pallets weigh up to X kg') OR as a table column (labelled 'Max Loaded weight' / 'gross weight'). Read BOTH prose sentences and table cells — do not restrict search to tables only. In tables, use the loaded/gross weight — IGNORE 'tare weight' / 'empty pallet weight'. If a range or several load types are given, report the heaviest stated number. NULL RULE: Output null only if no maximum load weight is stated anywhere in the document text. CONSERVATIVE EXTRACTION: if multiple values are stated, extract the MAXIMUM — the supplier must meet or exceed this threshold.</t>
         </is>
       </c>
       <c r="H10" s="73" t="n"/>
@@ -3225,7 +3279,7 @@
       <c r="F17" s="77" t="n"/>
       <c r="G17" s="69" t="inlineStr">
         <is>
-          <t>Lowest rated operating temperature. Source: 'working temperature' in environment/operating conditions section. Cond. K.O.: binds only for cold stores/freezers (-25 °C); standard units bottom out near 0–5 °C. NULL RULE: ONLY extract from an explicit °C value in a technical specification section. Do NOT confuse with dates (e.g. '25th May', '2022-05-25'), revision numbers, or project metadata — these are never temperatures. If no operating temperature range is stated → null.</t>
+          <t>Lowest rated operating temperature the vehicle must sustain, in °C. NULL RULE — READ FIRST: this field is null by default. Only fill it if the tender document explicitly states an operating/working temperature value (with a °C or K unit) in an environment or technical-specification section. If the document does not state an operating temperature, output null. Do NOT supply any default, typical, or example value. Do NOT copy numbers from this field description, from matching-rule notes, or from domain guidance — those are explanatory text, never document evidence. Do NOT confuse temperatures with dates, year/revision numbers, quantities, or project metadata. Source: a 'working temperature' / 'operating temperature' figure in the document's environment or operating-conditions section.</t>
         </is>
       </c>
       <c r="H17" s="77" t="n"/>
@@ -3269,7 +3323,7 @@
       <c r="F18" s="73" t="n"/>
       <c r="G18" s="66" t="inlineStr">
         <is>
-          <t>Highest rated operating temperature. Source: 'working temperature' in environment/operating conditions section. Cond. K.O.: relevant only for hot production halls. NULL RULE: ONLY extract from an explicit °C value in a technical specification. Do NOT confuse with dates, year numbers, or version codes. If not stated → null.</t>
+          <t>Highest rated operating temperature the vehicle must sustain, in °C. NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states an operating/working temperature value (with a °C or K unit). If not stated, output null. Do NOT supply a default, typical, or example value, and do NOT copy numbers from this description or from rule notes. Do NOT confuse with dates, year numbers, or version codes. Source: a 'working temperature' / 'operating temperature' figure in the environment or operating-conditions section.</t>
         </is>
       </c>
       <c r="H18" s="73" t="n"/>
@@ -3313,7 +3367,7 @@
       <c r="F19" s="77" t="n"/>
       <c r="G19" s="69" t="inlineStr">
         <is>
-          <t>Max rated relative humidity (non-condensing unless stated). Source: environment spec — must appear as a % value. Cond. K.O.: binds for wet/washdown areas; pair with ingress_protection_rating. NULL RULE: null unless a humidity percentage is explicitly stated. Do NOT infer from warehouse type, food industry context, or cold-storage environment.</t>
+          <t>Maximum rated relative humidity the vehicle must tolerate, as a percentage. NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a relative-humidity value as a % figure in an environment or technical-specification section. If no humidity percentage is stated, output null. Do NOT supply a default, typical, or example value, and do NOT copy numbers from this description or from rule/domain notes. Do NOT infer humidity from warehouse type, food/beverage context, washdown wording, or cold-storage environment. Source: an explicit relative-humidity % figure in the environment specification.</t>
         </is>
       </c>
       <c r="H19" s="77" t="n"/>
@@ -3405,7 +3459,7 @@
       <c r="F21" s="77" t="n"/>
       <c r="G21" s="69" t="inlineStr">
         <is>
-          <t>Cleanroom certification, if any. Source: 'cleanroom version'. Cond. K.O.: binds only for pharma/semiconductor/sterile F&amp;B. 'None' = no cleanroom rating.</t>
+          <t>Cleanroom certification, if any. Source: 'cleanroom version'. Cond. K.O.: binds only for pharma/semiconductor/sterile F&amp;B. 'None' = no cleanroom rating. NULL RULE: output 'None' or null unless the document explicitly states a cleanroom ISO class (e.g. 'ISO 7', 'cleanroom version'). Do NOT infer from words like 'clean', 'hygiene', or 'food-grade'.</t>
         </is>
       </c>
       <c r="H21" s="83" t="inlineStr">
@@ -3453,7 +3507,7 @@
       <c r="F22" s="73" t="n"/>
       <c r="G22" s="66" t="inlineStr">
         <is>
-          <t>Max ramp gradient the loaded unit handles. Source: spec 'gradeability' — must appear as an explicit % value. Cond. K.O.: binds only where the site has ramps/dock inclines. NULL RULE: null unless a slope or gradient percentage is explicitly stated in the document. Do NOT apply typical industry values (e.g. '5%') when the document is silent on gradients.</t>
+          <t>Max ramp gradient the loaded unit handles. Source: spec 'gradeability' — must appear as an explicit % value. The value represents the steepest ramp gradient (%) the loaded vehicle must climb: 10 % ≈ 5.7° incline; most flat indoor warehouse floors have 0 % gradient and this field should be null. Cond. K.O.: binds only where the site has ramps/dock inclines. NULL RULE: null unless a slope or gradient percentage is explicitly stated in the document. Do NOT apply typical industry values (e.g. '5%') when the document is silent on gradients.</t>
         </is>
       </c>
       <c r="H22" s="83" t="inlineStr">
@@ -3889,6 +3943,14 @@
           <t>●</t>
         </is>
       </c>
+      <c r="J34" s="43" t="n">
+        <v>6</v>
+      </c>
+      <c r="L34" s="43" t="inlineStr">
+        <is>
+          <t>nonempty</t>
+        </is>
+      </c>
     </row>
     <row r="35" ht="33.75" customHeight="1" s="44">
       <c r="A35" s="64" t="inlineStr">
@@ -3953,7 +4015,7 @@
       </c>
       <c r="D37" s="81" t="inlineStr">
         <is>
-          <t>K.O.</t>
+          <t>Cond. K.O.</t>
         </is>
       </c>
       <c r="E37" s="76" t="inlineStr">
@@ -3968,7 +4030,7 @@
       </c>
       <c r="G37" s="66" t="inlineStr">
         <is>
-          <t>Architecture of the fleet controller. Source: 'fleet manager / software'. Implies lock-in vs. interoperability.</t>
+          <t>Architecture of the fleet controller. Source: 'fleet manager / software'. Implies lock-in vs. interoperability. NULL RULE: output null unless the tender explicitly names a required fleet-controller architecture (one of the allowed values). Do NOT infer from the mere presence of a WMS, fleet software, or VDA 5050 mention — those are separate fields.</t>
         </is>
       </c>
       <c r="H37" s="73" t="n"/>
@@ -4456,7 +4518,7 @@
       </c>
       <c r="G50" s="66" t="inlineStr">
         <is>
-          <t>Geographic service &amp; support reach. Source: 'locations / service network'. Cond. K.O.: hard filter when the buyer needs fast on-site SLA in a specific region. 'None' = no own network stated.</t>
+          <t>Geographic service &amp; support reach. Source: 'locations / service network'. Cond. K.O.: hard filter when the buyer needs fast on-site SLA in a specific region. 'None' = no own network stated. NULL RULE: output null unless the tender explicitly demands a service/support region. Do NOT infer coverage from the document language or buyer location.</t>
         </is>
       </c>
       <c r="H50" s="83" t="inlineStr">
@@ -4744,7 +4806,7 @@
       </c>
       <c r="G59" s="92" t="inlineStr">
         <is>
-          <t>HQ country of the selling company. Used as Cond. K.O. when buyer requires domestic or regional supplier.</t>
+          <t>HQ country of the selling company. Used as Cond. K.O. when buyer requires domestic or regional supplier. NULL RULE: output null unless the tender explicitly requires a domestic or specific-country supplier. Do NOT infer from buyer address or document language.</t>
         </is>
       </c>
       <c r="H59" s="90" t="inlineStr">
@@ -5131,7 +5193,7 @@
       </c>
       <c r="G4" s="66" t="inlineStr">
         <is>
-          <t>AGV fork lift height in METERS — the height the forks travel, NOT building height, rack height or storage height. Source: 'Hubhöhe / lift height / fork height' in the AGV specification. If only building or rack height is stated → null. Typical: 1.5–15 m.</t>
+          <t>AGV fork lift height in METERS — the height the forks travel, NOT building height, rack height or storage height. Source: 'Hubhöhe / lift height / fork height' in the AGV specification. If only building or rack height is stated → null. NULL RULE: null unless the document explicitly states a required AGV lift height as a technical specification with its own value and unit. Do NOT confuse with transfer station height, conveyor height, rack height, or building height — these are site dimensions, not AGV specifications. Do NOT compute, derive, or estimate the lift height from any other stated quantity — pallet height, stack height, number of storage levels, or rack capacity are design inputs, not AGV lift specifications. A lift height obtained by calculation rather than read directly from an AGV specification has no source sentence and must be output as null.</t>
         </is>
       </c>
       <c r="H4" s="73" t="n"/>
@@ -5193,7 +5255,7 @@
     <row r="6" ht="33.75" customHeight="1" s="44">
       <c r="A6" s="64" t="inlineStr">
         <is>
-          <t>fork_type</t>
+          <t>special_fork_option</t>
         </is>
       </c>
       <c r="B6" s="73" t="inlineStr">
@@ -5203,12 +5265,12 @@
       </c>
       <c r="C6" s="74" t="inlineStr">
         <is>
-          <t>Standard Fork | Telescopic | Side-Shift | Rotating | Clamp</t>
+          <t>Telescopic | Side-Shift | Clamp</t>
         </is>
       </c>
       <c r="D6" s="81" t="inlineStr">
         <is>
-          <t>K.O.</t>
+          <t>Cond. K.O.</t>
         </is>
       </c>
       <c r="E6" s="76" t="inlineStr">
@@ -5223,7 +5285,7 @@
       </c>
       <c r="G6" s="66" t="inlineStr">
         <is>
-          <t>Fork/attachment type. Output from allowed values only. Output null if not explicitly stated — do NOT assume Standard Fork as default. VNA RULE: if required_vna=true, Standard Fork does not apply to turret trucks — output null unless a specific fork attachment is explicitly stated.</t>
+          <t>Non-standard fork or attachment type required by the tender. NULL RULE — READ FIRST: null by default. Only output a value if the tender document EXPLICITLY names a non-standard attachment type — i.e. 'telescopic forks', 'side-shift', or 'clamp'. Standard forks are the default for all forklifts and must NOT be extracted as a requirement. Rotating forks are the default for VNA/narrow-aisle turret trucks and are resolved from the vehicle classification, not from this field. If the document does not explicitly name Telescopic, Side-Shift, or Clamp — output null. A null value never disqualifies any supplier; a wrong value eliminates qualified suppliers.</t>
         </is>
       </c>
       <c r="H6" s="73" t="n"/>
@@ -5234,7 +5296,7 @@
       </c>
       <c r="K6" s="43" t="inlineStr">
         <is>
-          <t>required_fork_type</t>
+          <t>required_special_fork_option</t>
         </is>
       </c>
     </row>
@@ -5353,7 +5415,7 @@
       </c>
       <c r="G9" s="69" t="inlineStr">
         <is>
-          <t>Minimum working aisle width available in the facility, in METERS (not mm). CONSERVATIVE RULE (KO_IF_GT): if multiple aisle widths are stated, extract the MINIMUM — this is the tightest constraint. Example: '2000 mm rack-to-rack, min 1900 mm pallet-to-pallet' → output 1.9. If doc states mm → divide by 1000. Source: 'Gangbreite', 'aisle width', 'corridor width'. Hard filter: decisive for VNA and narrow-aisle forklifts. Null if not stated.</t>
+          <t>Minimum working aisle width available in the facility, in METERS. ONLY extract if the document explicitly states an aisle, corridor, or rack-to-rack width. Source terms: 'Gangbreite', 'aisle width', 'working aisle', 'corridor width'. If no explicit width is stated anywhere in the document → output null. Do NOT infer or estimate a width from the warehouse type, the forklift category, or any typical or standard value — absence of a stated width means null, never a guess. If the figure is given in mm, divide by 1000. Do NOT confuse aisle width with lift height, rack height, vehicle height, or transfer-station height.</t>
         </is>
       </c>
       <c r="H9" s="77" t="n"/>
@@ -5779,7 +5841,7 @@
       </c>
       <c r="D22" s="81" t="inlineStr">
         <is>
-          <t>K.O.</t>
+          <t>Cond. K.O.</t>
         </is>
       </c>
       <c r="E22" s="76" t="inlineStr">
@@ -5799,19 +5861,13 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
-      <c r="J22" s="100" t="n">
-        <v>5</v>
-      </c>
+      <c r="J22" s="100" t="n"/>
       <c r="K22" s="43" t="inlineStr">
         <is>
           <t>required_stacking</t>
         </is>
       </c>
-      <c r="L22" s="43" t="inlineStr">
-        <is>
-          <t>bool</t>
-        </is>
-      </c>
+      <c r="L22" s="43" t="n"/>
     </row>
     <row r="23" ht="33.75" customHeight="1" s="44">
       <c r="A23" s="64" t="inlineStr">
@@ -6049,7 +6105,7 @@
       </c>
       <c r="D30" s="81" t="inlineStr">
         <is>
-          <t>K.O.</t>
+          <t>Cond. K.O.</t>
         </is>
       </c>
       <c r="E30" s="76" t="inlineStr">
@@ -6357,7 +6413,7 @@
       </c>
       <c r="G6" s="66" t="inlineStr">
         <is>
-          <t>Trailer attachment method. Output from allowed values only, comma-separated if multiple. null = not stated.</t>
+          <t>Trailer attachment method. Output from allowed values only, comma-separated if multiple. null = not stated. NULL RULE: output null unless the tender explicitly names a coupling method. Do NOT default to 'Automatic' or infer from 'auto_hitch'.</t>
         </is>
       </c>
       <c r="H6" s="73" t="n"/>
@@ -6785,7 +6841,7 @@
       <c r="F18" s="77" t="n"/>
       <c r="G18" s="69" t="inlineStr">
         <is>
-          <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If doc states mm (e.g. 2700 mm) → divide by 1000 → 2.7. Hard filter; decisive for VNA.</t>
+          <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If doc states mm (e.g. 2700 mm) → divide by 1000 → 2.7. Hard filter; decisive for VNA. WARNING: Do NOT confuse aisle width with other dimensions. Source terms: 'Gangbreite', 'aisle width', 'working aisle'. If no explicit aisle width is stated → output null.</t>
         </is>
       </c>
       <c r="H18" s="83" t="inlineStr">
@@ -6919,7 +6975,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N45"/>
+  <dimension ref="A1:N44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -7053,7 +7109,7 @@
       </c>
       <c r="G4" s="66" t="inlineStr">
         <is>
-          <t>AMR workflow function. [AMR ONLY] null for other types. Output from allowed values, comma-separated.</t>
+          <t>AMR workflow function. [AMR ONLY] null for other types. Output from allowed values, comma-separated. NULL RULE: output null unless the tender explicitly specifies the AMR workflow (Transport, Goods-to-Person, Picking support). Do NOT infer from general automation context.</t>
         </is>
       </c>
       <c r="H4" s="83" t="inlineStr">
@@ -7101,7 +7157,7 @@
       <c r="F5" s="77" t="n"/>
       <c r="G5" s="69" t="inlineStr">
         <is>
-          <t>Requires fixed storage grid. [AMR ONLY] true/false. null for other types.</t>
+          <t>Requires fixed storage grid. [AMR ONLY] true/false. null for other types. NULL RULE: output null unless the tender explicitly requires a fixed storage grid (e.g. AutoStore-style). Do NOT infer from 'racking' or 'shelving'.</t>
         </is>
       </c>
       <c r="H5" s="83" t="inlineStr">
@@ -7195,7 +7251,7 @@
       <c r="F7" s="77" t="n"/>
       <c r="G7" s="69" t="inlineStr">
         <is>
-          <t>Picking method. [AMR ONLY] null for other types. Output from allowed values.</t>
+          <t>Picking method. [AMR ONLY] null for other types. Output from allowed values. NULL RULE: output null unless the tender explicitly names a picking method. Do NOT infer from generic 'picking' mentions.</t>
         </is>
       </c>
       <c r="H7" s="83" t="inlineStr">
@@ -7485,1005 +7541,853 @@
       </c>
     </row>
     <row r="16" ht="33.75" customHeight="1" s="44">
-      <c r="A16" s="64" t="inlineStr">
-        <is>
-          <t>omnidirectional</t>
-        </is>
-      </c>
-      <c r="B16" s="73" t="inlineStr">
+      <c r="A16" s="67" t="inlineStr">
+        <is>
+          <t>min_turning_radius_mm</t>
+        </is>
+      </c>
+      <c r="B16" s="77" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C16" s="78" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D16" s="81" t="inlineStr">
+        <is>
+          <t>K.O.</t>
+        </is>
+      </c>
+      <c r="E16" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F16" s="77" t="n"/>
+      <c r="G16" s="69" t="inlineStr">
+        <is>
+          <t>Min turning radius (0 if omnidirectional). Source: spec. Filter vs. aisle/turn geometry; combine with footprint.</t>
+        </is>
+      </c>
+      <c r="H16" s="77" t="n"/>
+      <c r="I16" s="102" t="inlineStr">
+        <is>
+          <t>KO_IF_GT</t>
+        </is>
+      </c>
+      <c r="K16" s="43" t="inlineStr">
+        <is>
+          <t>required_max_turning_radius_mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="33.75" customHeight="1" s="44">
+      <c r="A17" s="72" t="inlineStr">
+        <is>
+          <t>── PICK &amp; DROP ACCURACY (order: lateral · depth · angle)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="15.75" customHeight="1" s="44">
+      <c r="A18" s="64" t="inlineStr">
+        <is>
+          <t>pick_req_accuracy_lat_mm</t>
+        </is>
+      </c>
+      <c r="D18" s="43" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="33.75" customHeight="1" s="44">
+      <c r="A19" s="67" t="inlineStr">
+        <is>
+          <t>pick_req_accuracy_dep_mm</t>
+        </is>
+      </c>
+      <c r="B19" s="77" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C19" s="78" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D19" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E19" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F19" s="77" t="n"/>
+      <c r="G19" s="69" t="inlineStr">
+        <is>
+          <t>Required pre-park accuracy in DEPTH to engage the carrier. Source: as above.</t>
+        </is>
+      </c>
+      <c r="H19" s="83" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="33.75" customHeight="1" s="44">
+      <c r="A20" s="64" t="inlineStr">
+        <is>
+          <t>pick_req_accuracy_angle_deg</t>
+        </is>
+      </c>
+      <c r="B20" s="73" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C20" s="74" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="D20" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E20" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F20" s="73" t="n"/>
+      <c r="G20" s="66" t="inlineStr">
+        <is>
+          <t>Required pre-park ANGLE accuracy to engage. Source: as above. Tighter angle need = stricter parking discipline upstream.</t>
+        </is>
+      </c>
+      <c r="H20" s="83" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="33.75" customHeight="1" s="44">
+      <c r="A21" s="67" t="inlineStr">
+        <is>
+          <t>drop_accuracy_lat_mm</t>
+        </is>
+      </c>
+      <c r="B21" s="77" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C21" s="78" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D21" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E21" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F21" s="77" t="n"/>
+      <c r="G21" s="69" t="inlineStr">
+        <is>
+          <t>Placement accuracy LATERALLY when the robot sets a carrier down at a defined position/marker. Source: spec 'positioning accuracy'. Matters when the dropped carrier must be re-acquired later. (added — was missing for AMR)</t>
+        </is>
+      </c>
+      <c r="H21" s="83" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="22" ht="33.75" customHeight="1" s="44">
+      <c r="A22" s="64" t="inlineStr">
+        <is>
+          <t>drop_accuracy_dep_mm</t>
+        </is>
+      </c>
+      <c r="B22" s="73" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C22" s="74" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D22" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E22" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F22" s="73" t="n"/>
+      <c r="G22" s="66" t="inlineStr">
+        <is>
+          <t>Placement accuracy in DEPTH at drop. Source: as above.</t>
+        </is>
+      </c>
+      <c r="H22" s="83" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="23" ht="33.75" customHeight="1" s="44">
+      <c r="A23" s="67" t="inlineStr">
+        <is>
+          <t>drop_accuracy_angle_deg</t>
+        </is>
+      </c>
+      <c r="B23" s="77" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C23" s="78" t="inlineStr">
+        <is>
+          <t>°</t>
+        </is>
+      </c>
+      <c r="D23" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E23" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F23" s="77" t="n"/>
+      <c r="G23" s="69" t="inlineStr">
+        <is>
+          <t>Angular placement accuracy at drop. Source: as above.</t>
+        </is>
+      </c>
+      <c r="H23" s="83" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="24" ht="33.75" customHeight="1" s="44">
+      <c r="A24" s="72" t="inlineStr">
+        <is>
+          <t>── STORAGE / G2P LAYOUT</t>
+        </is>
+      </c>
+    </row>
+    <row r="25" ht="15.75" customHeight="1" s="44">
+      <c r="A25" s="64" t="inlineStr">
+        <is>
+          <t>storage_system_type</t>
+        </is>
+      </c>
+      <c r="D25" s="43" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="I25" s="102" t="inlineStr">
+        <is>
+          <t>KO_SUBSET</t>
+        </is>
+      </c>
+      <c r="K25" s="43" t="inlineStr">
+        <is>
+          <t>required_storage_system</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="33.75" customHeight="1" s="44">
+      <c r="A26" s="67" t="inlineStr">
+        <is>
+          <t>shelf_height_mm</t>
+        </is>
+      </c>
+      <c r="B26" s="77" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C26" s="78" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
+      <c r="D26" s="79" t="inlineStr">
+        <is>
+          <t>Cond. K.O.</t>
+        </is>
+      </c>
+      <c r="E26" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F26" s="77" t="n"/>
+      <c r="G26" s="69" t="inlineStr">
+        <is>
+          <t>Max shelf/rack/pod height handled (Geek+ ~2.8 m; RoboShuttle ~11 m). Source: spec. Cond. K.O.: binds for G2P vs. building height; density driver.</t>
+        </is>
+      </c>
+      <c r="H26" s="83" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+      <c r="I26" s="102" t="inlineStr">
+        <is>
+          <t>KO_IF_LT</t>
+        </is>
+      </c>
+      <c r="K26" s="43" t="inlineStr">
+        <is>
+          <t>required_shelf_height_mm</t>
+        </is>
+      </c>
+    </row>
+    <row r="27" ht="33.75" customHeight="1" s="44">
+      <c r="A27" s="64" t="inlineStr">
+        <is>
+          <t>shelf_footprint_mm</t>
+        </is>
+      </c>
+      <c r="B27" s="73" t="inlineStr">
+        <is>
+          <t>Text</t>
+        </is>
+      </c>
+      <c r="C27" s="74" t="inlineStr">
+        <is>
+          <t>L × W mm</t>
+        </is>
+      </c>
+      <c r="D27" s="79" t="inlineStr">
+        <is>
+          <t>Cond. K.O.</t>
+        </is>
+      </c>
+      <c r="E27" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F27" s="73" t="n"/>
+      <c r="G27" s="66" t="inlineStr">
+        <is>
+          <t>Pod/shelf footprint the robot drives under (e.g. 880×880, 1020×1020). Source: spec 'shelf size'. Cond. K.O.: binds when matching existing shelving dimensions.</t>
+        </is>
+      </c>
+      <c r="H27" s="73" t="n"/>
+      <c r="I27" s="43" t="inlineStr">
+        <is>
+          <t>KO_IF_NEQ</t>
+        </is>
+      </c>
+      <c r="K27" s="43" t="inlineStr">
+        <is>
+          <t>required_shelf_footprint</t>
+        </is>
+      </c>
+    </row>
+    <row r="28" ht="33.75" customHeight="1" s="44">
+      <c r="A28" s="67" t="inlineStr">
+        <is>
+          <t>min_grid_area_m2</t>
+        </is>
+      </c>
+      <c r="B28" s="77" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C28" s="78" t="inlineStr">
+        <is>
+          <t>m²</t>
+        </is>
+      </c>
+      <c r="D28" s="82" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="E28" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F28" s="77" t="n"/>
+      <c r="G28" s="69" t="inlineStr">
+        <is>
+          <t>Smallest sensible storage field for a G2P deployment. Source: solution/sales. Entry-footprint orientation.</t>
+        </is>
+      </c>
+      <c r="H28" s="77" t="n"/>
+    </row>
+    <row r="29" ht="33.75" customHeight="1" s="44">
+      <c r="A29" s="72" t="inlineStr">
+        <is>
+          <t>── THROUGHPUT &amp; PICKING</t>
+        </is>
+      </c>
+    </row>
+    <row r="30" ht="15.75" customHeight="1" s="44">
+      <c r="A30" s="64" t="inlineStr">
+        <is>
+          <t>throughput_picks_per_hour</t>
+        </is>
+      </c>
+      <c r="D30" s="43" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="J30" s="100" t="n">
+        <v>8</v>
+      </c>
+      <c r="L30" s="43" t="inlineStr">
+        <is>
+          <t>tiered_upper</t>
+        </is>
+      </c>
+      <c r="M30" s="43" t="n">
+        <v>300</v>
+      </c>
+      <c r="N30" s="43" t="n">
+        <v>150</v>
+      </c>
+    </row>
+    <row r="31" ht="33.75" customHeight="1" s="44">
+      <c r="A31" s="67" t="inlineStr">
+        <is>
+          <t>throughput_basis</t>
+        </is>
+      </c>
+      <c r="B31" s="77" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="C31" s="78" t="inlineStr">
+        <is>
+          <t>Per station | Per robot | Per system</t>
+        </is>
+      </c>
+      <c r="D31" s="82" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="E31" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F31" s="77" t="n"/>
+      <c r="G31" s="69" t="inlineStr">
+        <is>
+          <t>What throughput_picks_per_hour refers to. Source: read the fine print of the vendor KPI. Essential to disambiguate G2P (per-station) vs picking (per-robot) numbers. (new — fixes the per-station/per-robot confusion)</t>
+        </is>
+      </c>
+      <c r="H31" s="83" t="inlineStr">
+        <is>
+          <t>●</t>
+        </is>
+      </c>
+    </row>
+    <row r="32" ht="33.75" customHeight="1" s="44">
+      <c r="A32" s="64" t="inlineStr">
+        <is>
+          <t>concurrent_robots_per_station</t>
+        </is>
+      </c>
+      <c r="B32" s="73" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C32" s="74" t="inlineStr">
+        <is>
+          <t># robots</t>
+        </is>
+      </c>
+      <c r="D32" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E32" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F32" s="73" t="n"/>
+      <c r="G32" s="66" t="inlineStr">
+        <is>
+          <t>How many robots queue/serve one G2P station at once. Source: solution spec. Implies station utilization &amp; peak throughput.</t>
+        </is>
+      </c>
+      <c r="H32" s="73" t="n"/>
+    </row>
+    <row r="33" ht="33.75" customHeight="1" s="44">
+      <c r="A33" s="67" t="inlineStr">
+        <is>
+          <t>order_lines_per_run</t>
+        </is>
+      </c>
+      <c r="B33" s="77" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C33" s="78" t="inlineStr">
+        <is>
+          <t># lines</t>
+        </is>
+      </c>
+      <c r="D33" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E33" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F33" s="77" t="n"/>
+      <c r="G33" s="69" t="inlineStr">
+        <is>
+          <t>Order lines per robot run before returning to a station (picking workflows). Source: solution spec. Travel efficiency / batch depth.</t>
+        </is>
+      </c>
+      <c r="H33" s="77" t="n"/>
+    </row>
+    <row r="34" ht="33.75" customHeight="1" s="44">
+      <c r="A34" s="64" t="inlineStr">
+        <is>
+          <t>task_interleaving</t>
+        </is>
+      </c>
+      <c r="B34" s="73" t="inlineStr">
         <is>
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C16" s="74" t="inlineStr">
+      <c r="C34" s="74" t="inlineStr">
         <is>
           <t>true / false</t>
         </is>
       </c>
-      <c r="D16" s="80" t="inlineStr">
+      <c r="D34" s="80" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="E16" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F16" s="73" t="n"/>
-      <c r="G16" s="66" t="inlineStr">
-        <is>
-          <t>Holonomic drive (sideways + spin), e.g. AGILOX 3–4 drive units. Source: 'omnidirectional'. Enables parallel rack-aisle entry &amp; tight turns.</t>
-        </is>
-      </c>
-      <c r="H16" s="73" t="n"/>
-    </row>
-    <row r="17" ht="33.75" customHeight="1" s="44">
-      <c r="A17" s="67" t="inlineStr">
-        <is>
-          <t>min_turning_radius_mm</t>
-        </is>
-      </c>
-      <c r="B17" s="77" t="inlineStr">
+      <c r="E34" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F34" s="73" t="n"/>
+      <c r="G34" s="66" t="inlineStr">
+        <is>
+          <t>Mixes pick + put-away + replenishment + returns in one run (Locus Origin). Source: 'task interleaving'. Higher asset utilization.</t>
+        </is>
+      </c>
+      <c r="H34" s="73" t="n"/>
+    </row>
+    <row r="35" ht="33.75" customHeight="1" s="44">
+      <c r="A35" s="67" t="inlineStr">
+        <is>
+          <t>storage_density_factor</t>
+        </is>
+      </c>
+      <c r="B35" s="77" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="C35" s="78" t="inlineStr">
+        <is>
+          <t>× vs. manual</t>
+        </is>
+      </c>
+      <c r="D35" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E35" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F35" s="77" t="n"/>
+      <c r="G35" s="69" t="inlineStr">
+        <is>
+          <t>Storage density vs. conventional shelving (Geek+ claims ~2.5×). Source: solution marketing — treat as a vendor claim.</t>
+        </is>
+      </c>
+      <c r="H35" s="77" t="n"/>
+    </row>
+    <row r="36" ht="33.75" customHeight="1" s="44">
+      <c r="A36" s="64" t="inlineStr">
+        <is>
+          <t>ergonomic_height_adjustable</t>
+        </is>
+      </c>
+      <c r="B36" s="73" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="C36" s="74" t="inlineStr">
+        <is>
+          <t>true / false</t>
+        </is>
+      </c>
+      <c r="D36" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E36" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F36" s="73" t="n"/>
+      <c r="G36" s="66" t="inlineStr">
+        <is>
+          <t>Pick/put height adjusts to operator ergonomics (picking workflows). Source: 'ergonomic / adjustable'. Sustains pick rate.</t>
+        </is>
+      </c>
+      <c r="H36" s="73" t="n"/>
+    </row>
+    <row r="37" ht="33.75" customHeight="1" s="44">
+      <c r="A37" s="67" t="inlineStr">
+        <is>
+          <t>onboard_ui</t>
+        </is>
+      </c>
+      <c r="B37" s="77" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="C37" s="78" t="inlineStr">
+        <is>
+          <t>true / false</t>
+        </is>
+      </c>
+      <c r="D37" s="80" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E37" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F37" s="77" t="n"/>
+      <c r="G37" s="69" t="inlineStr">
+        <is>
+          <t>Onboard screen guiding the worker (Locus Origin). Source: 'onboard display / UI'. Speeds training &amp; cuts errors.</t>
+        </is>
+      </c>
+      <c r="H37" s="77" t="n"/>
+    </row>
+    <row r="38" ht="33.75" customHeight="1" s="44">
+      <c r="A38" s="64" t="inlineStr">
+        <is>
+          <t>multi_language_display</t>
+        </is>
+      </c>
+      <c r="B38" s="73" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="C38" s="74" t="inlineStr">
+        <is>
+          <t>true / false</t>
+        </is>
+      </c>
+      <c r="D38" s="82" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="E38" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F38" s="73" t="n"/>
+      <c r="G38" s="66" t="inlineStr">
+        <is>
+          <t>Onboard UI supports multiple languages. Source: 'multi-language'. Relevant for diverse workforces.</t>
+        </is>
+      </c>
+      <c r="H38" s="73" t="n"/>
+    </row>
+    <row r="39" ht="33.75" customHeight="1" s="44">
+      <c r="A39" s="67" t="inlineStr">
+        <is>
+          <t>gamification</t>
+        </is>
+      </c>
+      <c r="B39" s="77" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="C39" s="78" t="inlineStr">
+        <is>
+          <t>true / false</t>
+        </is>
+      </c>
+      <c r="D39" s="82" t="inlineStr">
+        <is>
+          <t>Context</t>
+        </is>
+      </c>
+      <c r="E39" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F39" s="77" t="n"/>
+      <c r="G39" s="69" t="inlineStr">
+        <is>
+          <t>Optional worker gamification/incentive features (Locus). Source: 'gamification'. Soft productivity lever.</t>
+        </is>
+      </c>
+      <c r="H39" s="77" t="n"/>
+    </row>
+    <row r="40" ht="33.75" customHeight="1" s="44">
+      <c r="A40" s="72" t="inlineStr">
+        <is>
+          <t>── CONTAINER (picking workflows)</t>
+        </is>
+      </c>
+    </row>
+    <row r="41" ht="15.75" customHeight="1" s="44">
+      <c r="A41" s="64" t="inlineStr">
+        <is>
+          <t>onboard_container_type</t>
+        </is>
+      </c>
+      <c r="D41" s="43" t="inlineStr">
+        <is>
+          <t>Scoring</t>
+        </is>
+      </c>
+      <c r="I41" s="102" t="inlineStr">
+        <is>
+          <t>KO_SUBSET</t>
+        </is>
+      </c>
+      <c r="K41" s="43" t="inlineStr">
+        <is>
+          <t>required_container_type</t>
+        </is>
+      </c>
+    </row>
+    <row r="42" ht="33.75" customHeight="1" s="44">
+      <c r="A42" s="67" t="inlineStr">
+        <is>
+          <t>onboard_container_count</t>
+        </is>
+      </c>
+      <c r="B42" s="77" t="inlineStr">
         <is>
           <t>Integer</t>
         </is>
       </c>
-      <c r="C17" s="78" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D17" s="81" t="inlineStr">
-        <is>
-          <t>K.O.</t>
-        </is>
-      </c>
-      <c r="E17" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F17" s="77" t="n"/>
-      <c r="G17" s="69" t="inlineStr">
-        <is>
-          <t>Min turning radius (0 if omnidirectional). Source: spec. Filter vs. aisle/turn geometry; combine with footprint.</t>
-        </is>
-      </c>
-      <c r="H17" s="77" t="n"/>
-      <c r="I17" s="102" t="inlineStr">
-        <is>
-          <t>KO_IF_GT</t>
-        </is>
-      </c>
-      <c r="K17" s="43" t="inlineStr">
-        <is>
-          <t>required_max_turning_radius_mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="44">
-      <c r="A18" s="72" t="inlineStr">
-        <is>
-          <t>── PICK &amp; DROP ACCURACY (order: lateral · depth · angle)</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="33.75" customHeight="1" s="44">
-      <c r="A19" s="64" t="inlineStr">
-        <is>
-          <t>pick_req_accuracy_lat_mm</t>
-        </is>
-      </c>
-      <c r="B19" s="73" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C19" s="74" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D19" s="80" t="inlineStr">
+      <c r="C42" s="78" t="inlineStr">
+        <is>
+          <t># containers</t>
+        </is>
+      </c>
+      <c r="D42" s="80" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="E19" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F19" s="73" t="n"/>
-      <c r="G19" s="66" t="inlineStr">
-        <is>
-          <t>How precisely the cart/rack/pallet must be PRE-parked (laterally) for the robot to engage &amp; lift. Source: integration spec. Loose tolerance = forgiving of human placement → easier deployment.</t>
-        </is>
-      </c>
-      <c r="H19" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="33.75" customHeight="1" s="44">
-      <c r="A20" s="67" t="inlineStr">
-        <is>
-          <t>pick_req_accuracy_dep_mm</t>
-        </is>
-      </c>
-      <c r="B20" s="77" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C20" s="78" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D20" s="80" t="inlineStr">
+      <c r="E42" s="76" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="F42" s="77" t="n"/>
+      <c r="G42" s="69" t="inlineStr">
+        <is>
+          <t>Simultaneous containers carried (multi-order/batch picking). Source: spec/config. More = batch efficiency.</t>
+        </is>
+      </c>
+      <c r="H42" s="77" t="n"/>
+    </row>
+    <row r="43" ht="33.75" customHeight="1" s="44">
+      <c r="A43" s="72" t="inlineStr">
+        <is>
+          <t>── WMS</t>
+        </is>
+      </c>
+    </row>
+    <row r="44" ht="15.75" customHeight="1" s="44">
+      <c r="A44" s="64" t="inlineStr">
+        <is>
+          <t>wms_integration_native</t>
+        </is>
+      </c>
+      <c r="D44" s="43" t="inlineStr">
         <is>
           <t>Scoring</t>
         </is>
       </c>
-      <c r="E20" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F20" s="77" t="n"/>
-      <c r="G20" s="69" t="inlineStr">
-        <is>
-          <t>Required pre-park accuracy in DEPTH to engage the carrier. Source: as above.</t>
-        </is>
-      </c>
-      <c r="H20" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="33.75" customHeight="1" s="44">
-      <c r="A21" s="64" t="inlineStr">
-        <is>
-          <t>pick_req_accuracy_angle_deg</t>
-        </is>
-      </c>
-      <c r="B21" s="73" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C21" s="74" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="D21" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E21" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F21" s="73" t="n"/>
-      <c r="G21" s="66" t="inlineStr">
-        <is>
-          <t>Required pre-park ANGLE accuracy to engage. Source: as above. Tighter angle need = stricter parking discipline upstream.</t>
-        </is>
-      </c>
-      <c r="H21" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-    </row>
-    <row r="22" ht="33.75" customHeight="1" s="44">
-      <c r="A22" s="67" t="inlineStr">
-        <is>
-          <t>drop_accuracy_lat_mm</t>
-        </is>
-      </c>
-      <c r="B22" s="77" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C22" s="78" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D22" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E22" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F22" s="77" t="n"/>
-      <c r="G22" s="69" t="inlineStr">
-        <is>
-          <t>Placement accuracy LATERALLY when the robot sets a carrier down at a defined position/marker. Source: spec 'positioning accuracy'. Matters when the dropped carrier must be re-acquired later. (added — was missing for AMR)</t>
-        </is>
-      </c>
-      <c r="H22" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="33.75" customHeight="1" s="44">
-      <c r="A23" s="64" t="inlineStr">
-        <is>
-          <t>drop_accuracy_dep_mm</t>
-        </is>
-      </c>
-      <c r="B23" s="73" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C23" s="74" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D23" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E23" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F23" s="73" t="n"/>
-      <c r="G23" s="66" t="inlineStr">
-        <is>
-          <t>Placement accuracy in DEPTH at drop. Source: as above.</t>
-        </is>
-      </c>
-      <c r="H23" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-    </row>
-    <row r="24" ht="33.75" customHeight="1" s="44">
-      <c r="A24" s="67" t="inlineStr">
-        <is>
-          <t>drop_accuracy_angle_deg</t>
-        </is>
-      </c>
-      <c r="B24" s="77" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C24" s="78" t="inlineStr">
-        <is>
-          <t>°</t>
-        </is>
-      </c>
-      <c r="D24" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E24" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F24" s="77" t="n"/>
-      <c r="G24" s="69" t="inlineStr">
-        <is>
-          <t>Angular placement accuracy at drop. Source: as above.</t>
-        </is>
-      </c>
-      <c r="H24" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" s="44">
-      <c r="A25" s="72" t="inlineStr">
-        <is>
-          <t>── STORAGE / G2P LAYOUT</t>
-        </is>
-      </c>
-    </row>
-    <row r="26" ht="33.75" customHeight="1" s="44">
-      <c r="A26" s="64" t="inlineStr">
-        <is>
-          <t>storage_system_type</t>
-        </is>
-      </c>
-      <c r="B26" s="73" t="inlineStr">
-        <is>
-          <t>Dropdown</t>
-        </is>
-      </c>
-      <c r="C26" s="74" t="inlineStr">
-        <is>
-          <t>None | Shelf-to-Person | Bin-to-Person | Tote-to-Person | Pallet-to-Person</t>
-        </is>
-      </c>
-      <c r="D26" s="79" t="inlineStr">
-        <is>
-          <t>Cond. K.O.</t>
-        </is>
-      </c>
-      <c r="E26" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F26" s="73" t="n"/>
-      <c r="G26" s="66" t="inlineStr">
-        <is>
-          <t>For G2P workflows: what unit is brought to the picker (Geek+ P = shelf; RoboShuttle = tote). Source: product family. Cond. K.O.: binds only if workflow_capability includes Goods-to-Person; 'None' otherwise.</t>
-        </is>
-      </c>
-      <c r="H26" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="I26" s="102" t="inlineStr">
-        <is>
-          <t>KO_SUBSET</t>
-        </is>
-      </c>
-      <c r="K26" s="43" t="inlineStr">
-        <is>
-          <t>required_storage_system</t>
-        </is>
-      </c>
-    </row>
-    <row r="27" ht="33.75" customHeight="1" s="44">
-      <c r="A27" s="67" t="inlineStr">
-        <is>
-          <t>shelf_height_mm</t>
-        </is>
-      </c>
-      <c r="B27" s="77" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C27" s="78" t="inlineStr">
-        <is>
-          <t>mm</t>
-        </is>
-      </c>
-      <c r="D27" s="79" t="inlineStr">
-        <is>
-          <t>Cond. K.O.</t>
-        </is>
-      </c>
-      <c r="E27" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F27" s="77" t="n"/>
-      <c r="G27" s="69" t="inlineStr">
-        <is>
-          <t>Max shelf/rack/pod height handled (Geek+ ~2.8 m; RoboShuttle ~11 m). Source: spec. Cond. K.O.: binds for G2P vs. building height; density driver.</t>
-        </is>
-      </c>
-      <c r="H27" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="I27" s="102" t="inlineStr">
-        <is>
-          <t>KO_IF_LT</t>
-        </is>
-      </c>
-      <c r="K27" s="43" t="inlineStr">
-        <is>
-          <t>required_shelf_height_mm</t>
-        </is>
-      </c>
-    </row>
-    <row r="28" ht="33.75" customHeight="1" s="44">
-      <c r="A28" s="64" t="inlineStr">
-        <is>
-          <t>shelf_footprint_mm</t>
-        </is>
-      </c>
-      <c r="B28" s="73" t="inlineStr">
-        <is>
-          <t>Text</t>
-        </is>
-      </c>
-      <c r="C28" s="74" t="inlineStr">
-        <is>
-          <t>L × W mm</t>
-        </is>
-      </c>
-      <c r="D28" s="79" t="inlineStr">
-        <is>
-          <t>Cond. K.O.</t>
-        </is>
-      </c>
-      <c r="E28" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F28" s="73" t="n"/>
-      <c r="G28" s="66" t="inlineStr">
-        <is>
-          <t>Pod/shelf footprint the robot drives under (e.g. 880×880, 1020×1020). Source: spec 'shelf size'. Cond. K.O.: binds when matching existing shelving dimensions.</t>
-        </is>
-      </c>
-      <c r="H28" s="73" t="n"/>
-      <c r="I28" s="43" t="inlineStr">
-        <is>
-          <t>KO_IF_NEQ</t>
-        </is>
-      </c>
-      <c r="K28" s="43" t="inlineStr">
-        <is>
-          <t>required_shelf_footprint</t>
-        </is>
-      </c>
-    </row>
-    <row r="29" ht="33.75" customHeight="1" s="44">
-      <c r="A29" s="67" t="inlineStr">
-        <is>
-          <t>min_grid_area_m2</t>
-        </is>
-      </c>
-      <c r="B29" s="77" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C29" s="78" t="inlineStr">
-        <is>
-          <t>m²</t>
-        </is>
-      </c>
-      <c r="D29" s="82" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="E29" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F29" s="77" t="n"/>
-      <c r="G29" s="69" t="inlineStr">
-        <is>
-          <t>Smallest sensible storage field for a G2P deployment. Source: solution/sales. Entry-footprint orientation.</t>
-        </is>
-      </c>
-      <c r="H29" s="77" t="n"/>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="44">
-      <c r="A30" s="72" t="inlineStr">
-        <is>
-          <t>── THROUGHPUT &amp; PICKING</t>
-        </is>
-      </c>
-    </row>
-    <row r="31" ht="33.75" customHeight="1" s="44">
-      <c r="A31" s="64" t="inlineStr">
-        <is>
-          <t>throughput_picks_per_hour</t>
-        </is>
-      </c>
-      <c r="B31" s="73" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C31" s="74" t="inlineStr">
-        <is>
-          <t>picks/h</t>
-        </is>
-      </c>
-      <c r="D31" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E31" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F31" s="73" t="n"/>
-      <c r="G31" s="66" t="inlineStr">
-        <is>
-          <t>Pick/handling throughput. ALWAYS read together with throughput_basis (per-station vs per-robot vs per-system) — the figures are not comparable across vendors otherwise. Source: solution KPIs. (consolidates the old picks_per_hour and picks_per_hour_per_station)</t>
-        </is>
-      </c>
-      <c r="H31" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-      <c r="J31" s="100" t="n">
+      <c r="J44" s="43" t="n">
         <v>8</v>
       </c>
-      <c r="L31" s="43" t="inlineStr">
-        <is>
-          <t>tiered_upper</t>
-        </is>
-      </c>
-      <c r="M31" s="43" t="n">
-        <v>300</v>
-      </c>
-      <c r="N31" s="43" t="n">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="32" ht="33.75" customHeight="1" s="44">
-      <c r="A32" s="67" t="inlineStr">
-        <is>
-          <t>throughput_basis</t>
-        </is>
-      </c>
-      <c r="B32" s="77" t="inlineStr">
-        <is>
-          <t>Dropdown</t>
-        </is>
-      </c>
-      <c r="C32" s="78" t="inlineStr">
-        <is>
-          <t>Per station | Per robot | Per system</t>
-        </is>
-      </c>
-      <c r="D32" s="82" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="E32" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F32" s="77" t="n"/>
-      <c r="G32" s="69" t="inlineStr">
-        <is>
-          <t>What throughput_picks_per_hour refers to. Source: read the fine print of the vendor KPI. Essential to disambiguate G2P (per-station) vs picking (per-robot) numbers. (new — fixes the per-station/per-robot confusion)</t>
-        </is>
-      </c>
-      <c r="H32" s="83" t="inlineStr">
-        <is>
-          <t>●</t>
-        </is>
-      </c>
-    </row>
-    <row r="33" ht="33.75" customHeight="1" s="44">
-      <c r="A33" s="64" t="inlineStr">
-        <is>
-          <t>concurrent_robots_per_station</t>
-        </is>
-      </c>
-      <c r="B33" s="73" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C33" s="74" t="inlineStr">
-        <is>
-          <t># robots</t>
-        </is>
-      </c>
-      <c r="D33" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E33" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F33" s="73" t="n"/>
-      <c r="G33" s="66" t="inlineStr">
-        <is>
-          <t>How many robots queue/serve one G2P station at once. Source: solution spec. Implies station utilization &amp; peak throughput.</t>
-        </is>
-      </c>
-      <c r="H33" s="73" t="n"/>
-    </row>
-    <row r="34" ht="33.75" customHeight="1" s="44">
-      <c r="A34" s="67" t="inlineStr">
-        <is>
-          <t>order_lines_per_run</t>
-        </is>
-      </c>
-      <c r="B34" s="77" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C34" s="78" t="inlineStr">
-        <is>
-          <t># lines</t>
-        </is>
-      </c>
-      <c r="D34" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E34" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F34" s="77" t="n"/>
-      <c r="G34" s="69" t="inlineStr">
-        <is>
-          <t>Order lines per robot run before returning to a station (picking workflows). Source: solution spec. Travel efficiency / batch depth.</t>
-        </is>
-      </c>
-      <c r="H34" s="77" t="n"/>
-    </row>
-    <row r="35" ht="33.75" customHeight="1" s="44">
-      <c r="A35" s="64" t="inlineStr">
-        <is>
-          <t>task_interleaving</t>
-        </is>
-      </c>
-      <c r="B35" s="73" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="C35" s="74" t="inlineStr">
-        <is>
-          <t>true / false</t>
-        </is>
-      </c>
-      <c r="D35" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E35" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F35" s="73" t="n"/>
-      <c r="G35" s="66" t="inlineStr">
-        <is>
-          <t>Mixes pick + put-away + replenishment + returns in one run (Locus Origin). Source: 'task interleaving'. Higher asset utilization.</t>
-        </is>
-      </c>
-      <c r="H35" s="73" t="n"/>
-    </row>
-    <row r="36" ht="33.75" customHeight="1" s="44">
-      <c r="A36" s="67" t="inlineStr">
-        <is>
-          <t>storage_density_factor</t>
-        </is>
-      </c>
-      <c r="B36" s="77" t="inlineStr">
-        <is>
-          <t>Float</t>
-        </is>
-      </c>
-      <c r="C36" s="78" t="inlineStr">
-        <is>
-          <t>× vs. manual</t>
-        </is>
-      </c>
-      <c r="D36" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E36" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F36" s="77" t="n"/>
-      <c r="G36" s="69" t="inlineStr">
-        <is>
-          <t>Storage density vs. conventional shelving (Geek+ claims ~2.5×). Source: solution marketing — treat as a vendor claim.</t>
-        </is>
-      </c>
-      <c r="H36" s="77" t="n"/>
-    </row>
-    <row r="37" ht="33.75" customHeight="1" s="44">
-      <c r="A37" s="64" t="inlineStr">
-        <is>
-          <t>ergonomic_height_adjustable</t>
-        </is>
-      </c>
-      <c r="B37" s="73" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="C37" s="74" t="inlineStr">
-        <is>
-          <t>true / false</t>
-        </is>
-      </c>
-      <c r="D37" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E37" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F37" s="73" t="n"/>
-      <c r="G37" s="66" t="inlineStr">
-        <is>
-          <t>Pick/put height adjusts to operator ergonomics (picking workflows). Source: 'ergonomic / adjustable'. Sustains pick rate.</t>
-        </is>
-      </c>
-      <c r="H37" s="73" t="n"/>
-    </row>
-    <row r="38" ht="33.75" customHeight="1" s="44">
-      <c r="A38" s="67" t="inlineStr">
-        <is>
-          <t>onboard_ui</t>
-        </is>
-      </c>
-      <c r="B38" s="77" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="C38" s="78" t="inlineStr">
-        <is>
-          <t>true / false</t>
-        </is>
-      </c>
-      <c r="D38" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E38" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F38" s="77" t="n"/>
-      <c r="G38" s="69" t="inlineStr">
-        <is>
-          <t>Onboard screen guiding the worker (Locus Origin). Source: 'onboard display / UI'. Speeds training &amp; cuts errors.</t>
-        </is>
-      </c>
-      <c r="H38" s="77" t="n"/>
-    </row>
-    <row r="39" ht="33.75" customHeight="1" s="44">
-      <c r="A39" s="64" t="inlineStr">
-        <is>
-          <t>multi_language_display</t>
-        </is>
-      </c>
-      <c r="B39" s="73" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="C39" s="74" t="inlineStr">
-        <is>
-          <t>true / false</t>
-        </is>
-      </c>
-      <c r="D39" s="82" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="E39" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F39" s="73" t="n"/>
-      <c r="G39" s="66" t="inlineStr">
-        <is>
-          <t>Onboard UI supports multiple languages. Source: 'multi-language'. Relevant for diverse workforces.</t>
-        </is>
-      </c>
-      <c r="H39" s="73" t="n"/>
-    </row>
-    <row r="40" ht="33.75" customHeight="1" s="44">
-      <c r="A40" s="67" t="inlineStr">
-        <is>
-          <t>gamification</t>
-        </is>
-      </c>
-      <c r="B40" s="77" t="inlineStr">
-        <is>
-          <t>Boolean</t>
-        </is>
-      </c>
-      <c r="C40" s="78" t="inlineStr">
-        <is>
-          <t>true / false</t>
-        </is>
-      </c>
-      <c r="D40" s="82" t="inlineStr">
-        <is>
-          <t>Context</t>
-        </is>
-      </c>
-      <c r="E40" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F40" s="77" t="n"/>
-      <c r="G40" s="69" t="inlineStr">
-        <is>
-          <t>Optional worker gamification/incentive features (Locus). Source: 'gamification'. Soft productivity lever.</t>
-        </is>
-      </c>
-      <c r="H40" s="77" t="n"/>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" s="44">
-      <c r="A41" s="72" t="inlineStr">
-        <is>
-          <t>── CONTAINER (picking workflows)</t>
-        </is>
-      </c>
-    </row>
-    <row r="42" ht="33.75" customHeight="1" s="44">
-      <c r="A42" s="64" t="inlineStr">
-        <is>
-          <t>onboard_container_type</t>
-        </is>
-      </c>
-      <c r="B42" s="73" t="inlineStr">
-        <is>
-          <t>Multi-Select</t>
-        </is>
-      </c>
-      <c r="C42" s="74" t="inlineStr">
-        <is>
-          <t>None | Tote | Bag | Open shelf | Bulk bin | Shipping box | Conveyor belt</t>
-        </is>
-      </c>
-      <c r="D42" s="79" t="inlineStr">
-        <is>
-          <t>Cond. K.O.</t>
-        </is>
-      </c>
-      <c r="E42" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F42" s="73" t="n"/>
-      <c r="G42" s="66" t="inlineStr">
-        <is>
-          <t>Onboard storage formats (Locus configurable). Source: 'configurations'. Cond. K.O.: binds for picking workflows — must match the buyer's pick containers; 'None' for pure transport.</t>
-        </is>
-      </c>
-      <c r="H42" s="73" t="n"/>
-      <c r="I42" s="102" t="inlineStr">
-        <is>
-          <t>KO_SUBSET</t>
-        </is>
-      </c>
-      <c r="K42" s="43" t="inlineStr">
-        <is>
-          <t>required_container_type</t>
-        </is>
-      </c>
-    </row>
-    <row r="43" ht="33.75" customHeight="1" s="44">
-      <c r="A43" s="67" t="inlineStr">
-        <is>
-          <t>onboard_container_count</t>
-        </is>
-      </c>
-      <c r="B43" s="77" t="inlineStr">
-        <is>
-          <t>Integer</t>
-        </is>
-      </c>
-      <c r="C43" s="78" t="inlineStr">
-        <is>
-          <t># containers</t>
-        </is>
-      </c>
-      <c r="D43" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E43" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F43" s="77" t="n"/>
-      <c r="G43" s="69" t="inlineStr">
-        <is>
-          <t>Simultaneous containers carried (multi-order/batch picking). Source: spec/config. More = batch efficiency.</t>
-        </is>
-      </c>
-      <c r="H43" s="77" t="n"/>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" s="44">
-      <c r="A44" s="72" t="inlineStr">
-        <is>
-          <t>── WMS</t>
-        </is>
-      </c>
-    </row>
-    <row r="45" ht="33.75" customHeight="1" s="44">
-      <c r="A45" s="64" t="inlineStr">
-        <is>
-          <t>wms_integration_native</t>
-        </is>
-      </c>
-      <c r="B45" s="73" t="inlineStr">
-        <is>
-          <t>Multi-Select</t>
-        </is>
-      </c>
-      <c r="C45" s="74" t="inlineStr">
-        <is>
-          <t>None | SAP EWM | Oracle WMS | Manhattan | Blue Yonder | Custom API</t>
-        </is>
-      </c>
-      <c r="D45" s="80" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
-      <c r="E45" s="76" t="inlineStr">
-        <is>
-          <t>Base Model</t>
-        </is>
-      </c>
-      <c r="F45" s="73" t="n"/>
-      <c r="G45" s="66" t="inlineStr">
-        <is>
-          <t>Native WMS/WES connectors out-of-the-box. Source: 'integrations'. Mission-critical for G2P &amp; picking → weigh heavily. (generic interfaces live in SHARED.integration_capability)</t>
-        </is>
-      </c>
-      <c r="H45" s="73" t="n"/>
-    </row>
+      <c r="L44" s="43" t="inlineStr">
+        <is>
+          <t>nonempty</t>
+        </is>
+      </c>
+    </row>
+    <row r="45" ht="33.75" customHeight="1" s="44"/>
   </sheetData>
-  <mergeCells count="9">
-    <mergeCell ref="A18:H18"/>
+  <mergeCells count="4">
+    <mergeCell ref="A15:H15"/>
     <mergeCell ref="A3:H3"/>
-    <mergeCell ref="A30:H30"/>
-    <mergeCell ref="A15:H15"/>
-    <mergeCell ref="A25:H25"/>
-    <mergeCell ref="A41:H41"/>
-    <mergeCell ref="A44:H44"/>
+    <mergeCell ref="A8:H8"/>
     <mergeCell ref="A1:H1"/>
-    <mergeCell ref="A8:H8"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -2661,8 +2661,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
@@ -2677,7 +2677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N64"/>
+  <dimension ref="A1:Q64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -2770,6 +2770,21 @@
           <t>Threshold 2</t>
         </is>
       </c>
+      <c r="O2" s="43" t="inlineStr">
+        <is>
+          <t>Plausibility Min</t>
+        </is>
+      </c>
+      <c r="P2" s="43" t="inlineStr">
+        <is>
+          <t>Plausibility Max</t>
+        </is>
+      </c>
+      <c r="Q2" s="43" t="inlineStr">
+        <is>
+          <t>Tender Unit</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -3048,6 +3063,17 @@
           <t>required_weight_capacity_kg</t>
         </is>
       </c>
+      <c r="O10" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="P10" s="43" t="n">
+        <v>50000</v>
+      </c>
+      <c r="Q10" s="43" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="33.75" customHeight="1" s="44">
       <c r="A11" s="67" t="inlineStr">
@@ -3293,6 +3319,17 @@
           <t>required_temp_min_c</t>
         </is>
       </c>
+      <c r="O17" s="43" t="n">
+        <v>-40</v>
+      </c>
+      <c r="P17" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q17" s="43" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
     </row>
     <row r="18" ht="33.75" customHeight="1" s="44">
       <c r="A18" s="64" t="inlineStr">
@@ -3337,6 +3374,17 @@
           <t>required_temp_max_c</t>
         </is>
       </c>
+      <c r="O18" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P18" s="43" t="n">
+        <v>60</v>
+      </c>
+      <c r="Q18" s="43" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="33.75" customHeight="1" s="44">
       <c r="A19" s="67" t="inlineStr">
@@ -3381,6 +3429,17 @@
           <t>required_humidity_max_pct</t>
         </is>
       </c>
+      <c r="O19" s="43" t="n">
+        <v>10</v>
+      </c>
+      <c r="P19" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="Q19" s="43" t="inlineStr">
+        <is>
+          <t>%</t>
+        </is>
+      </c>
     </row>
     <row r="20" ht="33.75" customHeight="1" s="44">
       <c r="A20" s="64" t="inlineStr">
@@ -3523,6 +3582,17 @@
       <c r="K22" s="43" t="inlineStr">
         <is>
           <t>required_max_gradient_pct</t>
+        </is>
+      </c>
+      <c r="O22" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P22" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q22" s="43" t="inlineStr">
+        <is>
+          <t>%</t>
         </is>
       </c>
     </row>
@@ -5059,7 +5129,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N31"/>
+  <dimension ref="A1:Q31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -5152,6 +5222,21 @@
           <t>Threshold 2</t>
         </is>
       </c>
+      <c r="O2" s="43" t="inlineStr">
+        <is>
+          <t>Plausibility Min</t>
+        </is>
+      </c>
+      <c r="P2" s="43" t="inlineStr">
+        <is>
+          <t>Plausibility Max</t>
+        </is>
+      </c>
+      <c r="Q2" s="43" t="inlineStr">
+        <is>
+          <t>Tender Unit</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -5207,6 +5292,17 @@
           <t>required_max_lift_height_m</t>
         </is>
       </c>
+      <c r="O4" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P4" s="43" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q4" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="33.75" customHeight="1" s="44">
       <c r="A5" s="67" t="inlineStr">
@@ -5251,6 +5347,17 @@
           <t>required_max_vehicle_height_mm</t>
         </is>
       </c>
+      <c r="O5" s="43" t="n">
+        <v>500</v>
+      </c>
+      <c r="P5" s="43" t="n">
+        <v>5000</v>
+      </c>
+      <c r="Q5" s="43" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="33.75" customHeight="1" s="44">
       <c r="A6" s="64" t="inlineStr">
@@ -5427,6 +5534,17 @@
       <c r="K9" s="105" t="inlineStr">
         <is>
           <t>required_min_aisle_width_m</t>
+        </is>
+      </c>
+      <c r="O9" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P9" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q9" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
         </is>
       </c>
     </row>
@@ -6187,7 +6305,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N20"/>
+  <dimension ref="A1:Q20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -6280,6 +6398,21 @@
           <t>Threshold 2</t>
         </is>
       </c>
+      <c r="O2" s="43" t="inlineStr">
+        <is>
+          <t>Plausibility Min</t>
+        </is>
+      </c>
+      <c r="P2" s="43" t="inlineStr">
+        <is>
+          <t>Plausibility Max</t>
+        </is>
+      </c>
+      <c r="Q2" s="43" t="inlineStr">
+        <is>
+          <t>Tender Unit</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -6335,6 +6468,17 @@
           <t>required_towing_capacity_kg</t>
         </is>
       </c>
+      <c r="O4" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="P4" s="43" t="n">
+        <v>100000</v>
+      </c>
+      <c r="Q4" s="43" t="inlineStr">
+        <is>
+          <t>kg</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="33.75" customHeight="1" s="44">
       <c r="A5" s="67" t="inlineStr">
@@ -6379,6 +6523,17 @@
           <t>required_min_trailers</t>
         </is>
       </c>
+      <c r="O5" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P5" s="43" t="n">
+        <v>50</v>
+      </c>
+      <c r="Q5" s="43" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="33.75" customHeight="1" s="44">
       <c r="A6" s="64" t="inlineStr">
@@ -6859,6 +7014,17 @@
           <t>required_min_aisle_width_m</t>
         </is>
       </c>
+      <c r="O18" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P18" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q18" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
+        </is>
+      </c>
     </row>
     <row r="19" ht="33.75" customHeight="1" s="44">
       <c r="A19" s="64" t="inlineStr">
@@ -6907,6 +7073,17 @@
           <t>required_max_turning_radius_mm</t>
         </is>
       </c>
+      <c r="O19" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="P19" s="43" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q19" s="43" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="86" t="inlineStr">
@@ -6953,6 +7130,17 @@
       <c r="K20" s="43" t="inlineStr">
         <is>
           <t>required_min_aisle_width_m</t>
+        </is>
+      </c>
+      <c r="O20" s="43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P20" s="43" t="n">
+        <v>5</v>
+      </c>
+      <c r="Q20" s="43" t="inlineStr">
+        <is>
+          <t>m</t>
         </is>
       </c>
     </row>
@@ -6975,7 +7163,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:N44"/>
+  <dimension ref="A1:Q44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -7068,6 +7256,21 @@
           <t>Threshold 2</t>
         </is>
       </c>
+      <c r="O2" s="43" t="inlineStr">
+        <is>
+          <t>Plausibility Min</t>
+        </is>
+      </c>
+      <c r="P2" s="43" t="inlineStr">
+        <is>
+          <t>Plausibility Max</t>
+        </is>
+      </c>
+      <c r="Q2" s="43" t="inlineStr">
+        <is>
+          <t>Tender Unit</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -7324,6 +7527,17 @@
           <t>required_lift_height_mm</t>
         </is>
       </c>
+      <c r="O9" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="P9" s="43" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q9" s="43" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="33.75" customHeight="1" s="44">
       <c r="A10" s="67" t="inlineStr">
@@ -7368,6 +7582,17 @@
           <t>required_ground_clearance_mm</t>
         </is>
       </c>
+      <c r="O10" s="43" t="n">
+        <v>0</v>
+      </c>
+      <c r="P10" s="43" t="n">
+        <v>300</v>
+      </c>
+      <c r="Q10" s="43" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="33.75" customHeight="1" s="44">
       <c r="A11" s="64" t="inlineStr">
@@ -7583,6 +7808,17 @@
           <t>required_max_turning_radius_mm</t>
         </is>
       </c>
+      <c r="O16" s="43" t="n">
+        <v>100</v>
+      </c>
+      <c r="P16" s="43" t="n">
+        <v>20000</v>
+      </c>
+      <c r="Q16" s="43" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
     </row>
     <row r="17" ht="33.75" customHeight="1" s="44">
       <c r="A17" s="72" t="inlineStr">
@@ -7867,6 +8103,17 @@
       <c r="K26" s="43" t="inlineStr">
         <is>
           <t>required_shelf_height_mm</t>
+        </is>
+      </c>
+      <c r="O26" s="43" t="n">
+        <v>500</v>
+      </c>
+      <c r="P26" s="43" t="n">
+        <v>15000</v>
+      </c>
+      <c r="Q26" s="43" t="inlineStr">
+        <is>
+          <t>mm</t>
         </is>
       </c>
     </row>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -2661,9 +2661,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <printOptions horizontalCentered="0" verticalCentered="0" headings="0" gridLines="0" gridLinesSet="1"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2677,7 +2677,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q64"/>
+  <dimension ref="A1:X64"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -2785,6 +2785,11 @@
           <t>Tender Unit</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>result_card</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -2840,6 +2845,9 @@
           <t>required_navigation</t>
         </is>
       </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" ht="33.75" customHeight="1" s="44">
       <c r="A5" s="67" t="inlineStr">
@@ -3074,6 +3082,9 @@
           <t>kg</t>
         </is>
       </c>
+      <c r="R10" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="11" ht="33.75" customHeight="1" s="44">
       <c r="A11" s="67" t="inlineStr">
@@ -3207,6 +3218,9 @@
         </is>
       </c>
       <c r="H14" s="73" t="n"/>
+      <c r="R14" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="15" ht="33.75" customHeight="1" s="44">
       <c r="A15" s="67" t="inlineStr">
@@ -3796,6 +3810,9 @@
       <c r="M28" s="43" t="n">
         <v>8</v>
       </c>
+      <c r="R28" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="29" ht="33.75" customHeight="1" s="44">
       <c r="A29" s="64" t="inlineStr">
@@ -3880,6 +3897,9 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="R30" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="31" ht="33.75" customHeight="1" s="44">
       <c r="A31" s="64" t="inlineStr">
@@ -4207,6 +4227,9 @@
         <is>
           <t>bool_cond</t>
         </is>
+      </c>
+      <c r="R39" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="40" ht="33.75" customHeight="1" s="44">
@@ -4506,6 +4529,9 @@
       <c r="M48" s="43" t="n">
         <v>20</v>
       </c>
+      <c r="R48" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="49" ht="33.75" customHeight="1" s="44">
       <c r="A49" s="67" t="inlineStr">
@@ -4554,6 +4580,9 @@
       <c r="N49" s="43" t="n">
         <v>52</v>
       </c>
+      <c r="R49" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="50" ht="33.75" customHeight="1" s="44">
       <c r="A50" s="64" t="inlineStr">
@@ -4605,6 +4634,9 @@
         <is>
           <t>required_service_coverage</t>
         </is>
+      </c>
+      <c r="R50" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="51" ht="33.75" customHeight="1" s="44">
@@ -5129,7 +5161,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q31"/>
+  <dimension ref="A1:X31"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -5237,6 +5269,11 @@
           <t>Tender Unit</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>result_card</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -5303,6 +5340,9 @@
           <t>m</t>
         </is>
       </c>
+      <c r="R4" t="b">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" ht="33.75" customHeight="1" s="44">
       <c r="A5" s="67" t="inlineStr">
@@ -5546,6 +5586,9 @@
         <is>
           <t>m</t>
         </is>
+      </c>
+      <c r="R9" t="b">
+        <v>1</v>
       </c>
     </row>
     <row r="10" ht="33.75" customHeight="1" s="44">
@@ -6305,7 +6348,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q20"/>
+  <dimension ref="A1:X20"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -6411,6 +6454,11 @@
       <c r="Q2" s="43" t="inlineStr">
         <is>
           <t>Tender Unit</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>result_card</t>
         </is>
       </c>
     </row>
@@ -7163,7 +7211,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="0"/>
   </sheetPr>
-  <dimension ref="A1:Q44"/>
+  <dimension ref="A1:X44"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="0" outlineLevelRow="0"/>
   <cols>
     <col width="24" customWidth="1" style="43" min="1" max="1"/>
@@ -7271,6 +7319,11 @@
           <t>Tender Unit</t>
         </is>
       </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>result_card</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15.75" customHeight="1" s="44">
       <c r="A3" s="72" t="inlineStr">
@@ -7828,16 +7881,8 @@
       </c>
     </row>
     <row r="18" ht="15.75" customHeight="1" s="44">
-      <c r="A18" s="64" t="inlineStr">
-        <is>
-          <t>pick_req_accuracy_lat_mm</t>
-        </is>
-      </c>
-      <c r="D18" s="43" t="inlineStr">
-        <is>
-          <t>Scoring</t>
-        </is>
-      </c>
+      <c r="A18" s="64" t="n"/>
+      <c r="D18" s="43" t="n"/>
     </row>
     <row r="19" ht="33.75" customHeight="1" s="44">
       <c r="A19" s="67" t="inlineStr">
@@ -8042,9 +8087,24 @@
           <t>storage_system_type</t>
         </is>
       </c>
+      <c r="B25" s="43" t="inlineStr">
+        <is>
+          <t>Multi-Select</t>
+        </is>
+      </c>
+      <c r="C25" s="43" t="inlineStr">
+        <is>
+          <t>Bin-to-Person | Tote-to-Person | Shelf-to-Person | Pallet-to-Person</t>
+        </is>
+      </c>
       <c r="D25" s="43" t="inlineStr">
         <is>
           <t>Context</t>
+        </is>
+      </c>
+      <c r="E25" s="43" t="inlineStr">
+        <is>
+          <t>Base Model</t>
         </is>
       </c>
       <c r="I25" s="102" t="inlineStr">
@@ -8208,9 +8268,29 @@
           <t>throughput_picks_per_hour</t>
         </is>
       </c>
+      <c r="B30" s="43" t="inlineStr">
+        <is>
+          <t>Integer</t>
+        </is>
+      </c>
+      <c r="C30" s="43" t="inlineStr">
+        <is>
+          <t>picks/h</t>
+        </is>
+      </c>
       <c r="D30" s="43" t="inlineStr">
         <is>
           <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E30" s="43" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G30" s="43" t="inlineStr">
+        <is>
+          <t>Maximum throughput in picks per hour as a single integer — the rated capacity of the system. Source: datasheet throughput / performance section.</t>
         </is>
       </c>
       <c r="J30" s="100" t="n">
@@ -8227,6 +8307,12 @@
       <c r="N30" s="43" t="n">
         <v>150</v>
       </c>
+      <c r="O30" s="43" t="n">
+        <v>1</v>
+      </c>
+      <c r="P30" s="43" t="n">
+        <v>1000</v>
+      </c>
     </row>
     <row r="31" ht="33.75" customHeight="1" s="44">
       <c r="A31" s="67" t="inlineStr">
@@ -8551,9 +8637,24 @@
           <t>onboard_container_type</t>
         </is>
       </c>
+      <c r="B41" s="43" t="inlineStr">
+        <is>
+          <t>Multi-Select</t>
+        </is>
+      </c>
+      <c r="C41" s="43" t="inlineStr">
+        <is>
+          <t>Tote | Bin | Pallet | Shelf | None</t>
+        </is>
+      </c>
       <c r="D41" s="43" t="inlineStr">
         <is>
           <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E41" s="43" t="inlineStr">
+        <is>
+          <t>Base Model</t>
         </is>
       </c>
       <c r="I41" s="102" t="inlineStr">
@@ -8614,9 +8715,24 @@
           <t>wms_integration_native</t>
         </is>
       </c>
+      <c r="B44" s="43" t="inlineStr">
+        <is>
+          <t>Multi-Select</t>
+        </is>
+      </c>
+      <c r="C44" s="43" t="inlineStr">
+        <is>
+          <t>SAP EWM | Oracle WMS | Microsoft Dynamics 365 | Custom API | REST API</t>
+        </is>
+      </c>
       <c r="D44" s="43" t="inlineStr">
         <is>
           <t>Scoring</t>
+        </is>
+      </c>
+      <c r="E44" s="43" t="inlineStr">
+        <is>
+          <t>Base Model</t>
         </is>
       </c>
       <c r="J44" s="43" t="n">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -24,7 +24,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="41">
+  <fonts count="42">
     <font>
       <name val="Calibri"/>
       <charset val="1"/>
@@ -298,8 +298,11 @@
       <color rgb="FF1A5276"/>
       <sz val="9"/>
     </font>
+    <font>
+      <b val="1"/>
+    </font>
   </fonts>
-  <fills count="24">
+  <fills count="25">
     <fill>
       <patternFill/>
     </fill>
@@ -429,6 +432,12 @@
         <fgColor rgb="FF4A4A8A"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00D9D9D9"/>
+        <bgColor rgb="00D9D9D9"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="2">
     <border>
@@ -457,7 +466,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="64">
+  <cellXfs count="73">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
@@ -605,6 +614,33 @@
     </xf>
     <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="24" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="24" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="6" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="9" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="17" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="20" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -2560,9 +2596,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -2578,16 +2614,24 @@
   <dimension ref="A1:R64"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="57" min="1" max="1"/>
-    <col width="13" customWidth="1" style="57" min="2" max="2"/>
-    <col width="30" customWidth="1" style="57" min="3" max="3"/>
-    <col width="10" customWidth="1" style="57" min="4" max="4"/>
-    <col width="13" customWidth="1" style="57" min="5" max="5"/>
-    <col width="7" customWidth="1" style="57" min="6" max="6"/>
-    <col width="60" customWidth="1" style="57" min="7" max="7"/>
-    <col width="69.83203125" customWidth="1" style="57" min="8" max="8"/>
+    <col width="30" customWidth="1" style="57" min="1" max="1"/>
+    <col width="14" customWidth="1" style="57" min="2" max="2"/>
+    <col width="28" customWidth="1" style="57" min="3" max="3"/>
+    <col width="8" customWidth="1" style="57" min="4" max="4"/>
+    <col width="12" customWidth="1" style="57" min="5" max="5"/>
+    <col width="10" customWidth="1" style="57" min="6" max="6"/>
+    <col width="50" customWidth="1" style="57" min="7" max="7"/>
+    <col width="20" customWidth="1" style="57" min="8" max="8"/>
+    <col width="10" customWidth="1" style="57" min="9" max="9"/>
     <col width="16" customWidth="1" style="57" min="10" max="10"/>
-    <col width="34" customWidth="1" style="57" min="11" max="11"/>
+    <col width="13" customWidth="1" style="57" min="11" max="11"/>
+    <col width="13" customWidth="1" style="57" min="12" max="12"/>
+    <col width="13" customWidth="1" style="57" min="13" max="13"/>
+    <col width="13" customWidth="1" style="57" min="14" max="14"/>
+    <col width="13" customWidth="1" style="57" min="15" max="15"/>
+    <col width="14" customWidth="1" style="57" min="16" max="16"/>
+    <col width="52" customWidth="1" style="57" min="17" max="17"/>
+    <col width="12" customWidth="1" style="57" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="57">
@@ -2596,107 +2640,113 @@
           <t>Fields applying to ALL AGV/AMR subtypes — written into base_model_extensions for every base model. Universal fields are consolidated here: power, gradient, floor flatness, stop accuracy, station applications, fleet size. ● = added/changed by Claude. v0.7: navigation_type + infrastructure_required → Cond. K.O.; Company/Product fields added.. Colour = level (red K.O. · orange Cond. K.O. · yellow Scoring · green Context).</t>
         </is>
       </c>
+      <c r="C1" s="64" t="n"/>
+      <c r="G1" s="64" t="n"/>
+      <c r="Q1" s="64" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="57">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>Allowed Values</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="66" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="65" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>LLM Hint</t>
         </is>
       </c>
-      <c r="H2" s="51" t="inlineStr">
+      <c r="H2" s="66" t="inlineStr">
         <is>
           <t>Matching Operator</t>
         </is>
       </c>
-      <c r="I2" s="51" t="inlineStr">
+      <c r="I2" s="66" t="inlineStr">
         <is>
           <t>Scoring Weight</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="66" t="inlineStr">
         <is>
           <t>Score Function</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="66" t="inlineStr">
         <is>
           <t>Score Threshold A</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="66" t="inlineStr">
         <is>
           <t>Score Threshold B</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="66" t="inlineStr">
         <is>
           <t>Plausibility Min</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="66" t="inlineStr">
         <is>
           <t>Plausibility Max</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="66" t="inlineStr">
         <is>
           <t>result_card</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="66" t="inlineStr">
         <is>
           <t>Display Mode</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="66" t="inlineStr">
         <is>
           <t>UI Hint</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="66" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="57">
+    <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="62" t="inlineStr">
         <is>
           <t>── NAVIGATION &amp; INFRASTRUCTURE</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="33.75" customHeight="1" s="57">
+      <c r="C3" s="64" t="n"/>
+      <c r="G3" s="64" t="n"/>
+      <c r="Q3" s="64" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>navigation_type</t>
@@ -2707,7 +2757,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>Laser Reflector | Natural Feature (SLAM) | Magnetic Tape | QR/DM Code | Contour | Inductive Loop | Vision</t>
         </is>
@@ -2722,7 +2772,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="68" t="inlineStr">
         <is>
           <t>Navigation technology used by the AGV. Output from allowed values only, comma-separated. Mapping rules: 'SLAM' / 'natural feature' / 'free navigation' / 'marker-free' / 'environment mapping' / 'contour-based' → 'Natural Feature (SLAM)'; 'laser reflector' / 'reflector marker' / 'laser scanner with reflectors' → 'Laser Reflector'; 'magnetic tape' / 'magnetic stripe' → 'Magnetic Tape'; 'QR code' / 'barcode' / 'data matrix' → 'QR/DM Code'; 'inductive loop' / 'wire guidance' → 'Inductive Loop'; 'vision' / 'camera-based' → 'Vision'. If multiple navigation types are required, list all. null = not stated in the document.</t>
         </is>
@@ -2735,13 +2785,18 @@
       <c r="O4" t="b">
         <v>1</v>
       </c>
+      <c r="Q4" s="64" t="inlineStr">
+        <is>
+          <t>Welche Navigationsart ist vorgesehen oder erlaubt? (z. B. Natural Feature/SLAM, Magnetband, QR-Code)</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>18b0abbe-33f3-4dbc-b03e-cb9fdb216fb8</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="33.75" customHeight="1" s="57">
+    <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>infrastructure_required</t>
@@ -2752,7 +2807,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n"/>
+      <c r="C5" s="69" t="n"/>
       <c r="E5" s="37" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -2763,7 +2818,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="70" t="inlineStr">
         <is>
           <t>Specifies what physical navigation infrastructure must be permanently installed on-site for the AGV to operate (e.g. reflectors for laser navigation, magnetic tape or inductive loops embedded in the floor). Cond. K.O.: scored by default; hard filter only when buyer cannot accept infrastructure modifications. NULL RULE: null unless the document explicitly names a required infrastructure type — do NOT infer from AGV category, navigation technology, or industry context.</t>
         </is>
@@ -2773,13 +2828,18 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="Q5" s="64" t="inlineStr">
+        <is>
+          <t>Ist die Installation von Infrastruktur akzeptabel? (z. B. Leitdrähte, Reflektoren, QR-Codes)</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>ba4b544a-6e32-4127-8ee8-d68e2ef3c7fc</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="33.75" customHeight="1" s="57">
+    <row r="6" ht="15" customHeight="1" s="57">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>outdoor_capable</t>
@@ -2790,7 +2850,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n"/>
+      <c r="C6" s="67" t="n"/>
       <c r="E6" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -2801,7 +2861,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="68" t="inlineStr">
         <is>
           <t>Outdoor operation required. Output true or false (boolean) — never 'yes'/'no'. null = not stated.</t>
         </is>
@@ -2819,13 +2879,18 @@
           <t>bool_cond</t>
         </is>
       </c>
+      <c r="Q6" s="64" t="inlineStr">
+        <is>
+          <t>Wird Außenbetrieb benötigt?</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>f1aafec8-86c0-4d3a-81f7-e07ec2e60a85</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="33.75" customHeight="1" s="57">
+    <row r="7" ht="15" customHeight="1" s="57">
       <c r="A7" s="19" t="inlineStr">
         <is>
           <t>autonomous_obstacle_bypass</t>
@@ -2836,7 +2901,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n"/>
+      <c r="C7" s="69" t="n"/>
       <c r="E7" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -2847,18 +2912,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="70" t="inlineStr">
         <is>
           <t>Re-routes AROUND obstacles autonomously vs. only stopping &amp; waiting. Source: 'dynamic obstacle avoidance'. Implies throughput in busy mixed-traffic aisles.</t>
         </is>
       </c>
+      <c r="Q7" s="64" t="inlineStr">
+        <is>
+          <t>Kann das AGV Hindernissen eigenständig ausweichen ohne anzuhalten?</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>31ee8eb5-cd88-483a-ad11-bd1c8bc27d99</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="33.75" customHeight="1" s="57">
+    <row r="8" ht="15" customHeight="1" s="57">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>omnidirectional_movement</t>
@@ -2869,7 +2939,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n"/>
+      <c r="C8" s="67" t="n"/>
       <c r="E8" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -2880,25 +2950,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G8" s="68" t="inlineStr">
         <is>
           <t>Holonomic drive — sideways + spin on the spot (Mecanum / multi-steer). Source: 'omnidirectional'. Implies maneuverability in tight aisles.</t>
         </is>
       </c>
+      <c r="Q8" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AGV in alle Richtungen ohne Wenden fahren können (omnidirektional)?</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>152f5c62-ca84-4446-a6df-dccdfaf2da4f</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="15.75" customHeight="1" s="57">
+    <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="62" t="inlineStr">
         <is>
           <t>── LOAD HANDLING</t>
         </is>
       </c>
-    </row>
-    <row r="10" ht="33.75" customHeight="1" s="57">
+      <c r="C9" s="64" t="n"/>
+      <c r="G9" s="64" t="n"/>
+      <c r="Q9" s="64" t="n"/>
+    </row>
+    <row r="10" ht="15" customHeight="1" s="57">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>max_payload_kg</t>
@@ -2909,7 +2987,7 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n"/>
+      <c r="C10" s="67" t="n"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>kg</t>
@@ -2925,7 +3003,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="68" t="inlineStr">
         <is>
           <t>Maximum payload the AGV must carry per trip, in kg. This value may appear as prose (e.g. 'a maximum of X kg', 'loads up to X kg', 'pallets weigh up to X kg') OR as a table column (labelled 'Max Loaded weight' / 'gross weight'). Read BOTH prose sentences and table cells — do not restrict search to tables only. In tables, use the loaded/gross weight — IGNORE 'tare weight' / 'empty pallet weight'. If a range or several load types are given, report the heaviest stated number. NULL RULE: Output null only if no maximum load weight is stated anywhere in the document text. CONSERVATIVE EXTRACTION: if multiple values are stated, extract the MAXIMUM — the supplier must meet or exceed this threshold.</t>
         </is>
@@ -2944,13 +3022,18 @@
       <c r="O10" t="b">
         <v>1</v>
       </c>
+      <c r="Q10" s="64" t="inlineStr">
+        <is>
+          <t>Wie hoch ist die maximale Nutzlast pro Ladungsträger? Das AGV muss mindestens dieses Gewicht tragen können (kg).</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>bda1cd9b-cfb6-474e-a858-a3fde419a94d</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="33.75" customHeight="1" s="57">
+    <row r="11" ht="15" customHeight="1" s="57">
       <c r="A11" s="19" t="inlineStr">
         <is>
           <t>load_type</t>
@@ -2961,7 +3044,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C11" s="28" t="inlineStr">
+      <c r="C11" s="69" t="inlineStr">
         <is>
           <t>None | Pallet EUR | Pallet ISO | Tote | Roll Container | Custom Carrier</t>
         </is>
@@ -2976,7 +3059,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G11" s="21" t="inlineStr">
+      <c r="G11" s="70" t="inlineStr">
         <is>
           <t>Load carriers handled. Output ONLY from allowed values — do NOT describe the process (e.g. 'floor delivery'). null = not determinable from document.</t>
         </is>
@@ -2986,13 +3069,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q11" s="64" t="inlineStr">
+        <is>
+          <t>Welche Ladungsträgertypen werden transportiert? (z. B. Europalette, Gitterbox, Behälter — alle zutreffenden auswählen)</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>3cf372d4-e297-4827-b38e-8838a1e7f5bd</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33.75" customHeight="1" s="57">
+    <row r="12" ht="15" customHeight="1" s="57">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>multi_load_compatibility</t>
@@ -3003,7 +3091,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="67" t="n"/>
       <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -3014,7 +3102,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="68" t="inlineStr">
         <is>
           <t>Handles several carrier types/sizes in ONE workflow without manual reconfiguration. Source: 'auto fork adjust / mixed loads'. Cond. K.O.: hard filter only if the buyer runs mixed loads.</t>
         </is>
@@ -3024,20 +3112,28 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="Q12" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AGV mehrere Ladungsträger gleichzeitig transportieren können?</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>2faf934a-73a1-4cfe-bc56-b494a2a46a28</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="57">
+    <row r="13" ht="15" customHeight="1" s="57">
       <c r="A13" s="62" t="inlineStr">
         <is>
           <t>── DIMENSIONS &amp; ENVIRONMENT</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="33.75" customHeight="1" s="57">
+      <c r="C13" s="64" t="n"/>
+      <c r="G13" s="64" t="n"/>
+      <c r="Q13" s="64" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>max_speed_ms</t>
@@ -3048,7 +3144,7 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n"/>
+      <c r="C14" s="67" t="n"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>m/s</t>
@@ -3064,7 +3160,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G14" s="68" t="inlineStr">
         <is>
           <t>Top travel speed (capture rated/unloaded if only one given). Source: spec table. Implies cycle time; check safety-derated speed too.</t>
         </is>
@@ -3072,13 +3168,18 @@
       <c r="O14" t="b">
         <v>1</v>
       </c>
+      <c r="Q14" s="64" t="inlineStr">
+        <is>
+          <t>Wie schnell soll das AGV maximal fahren? (m/s; z. B. 1,5 m/s)</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>7b313001-a796-4f57-bbf5-6b3b67367a3b</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="33.75" customHeight="1" s="57">
+    <row r="15" ht="15" customHeight="1" s="57">
       <c r="A15" s="19" t="inlineStr">
         <is>
           <t>length_mm</t>
@@ -3089,7 +3190,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C15" s="28" t="n"/>
+      <c r="C15" s="69" t="n"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>mm</t>
@@ -3105,18 +3206,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="70" t="inlineStr">
         <is>
           <t>Vehicle length. Source: dimensions (L×W×H). Used with width for footprint &amp; turn calculations.</t>
         </is>
       </c>
+      <c r="Q15" s="64" t="inlineStr">
+        <is>
+          <t>Wie lang ist das Fahrzeug? (mm; nur zur Information)</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>6776eb08-6b03-4a3e-a605-0e009854e864</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="33.75" customHeight="1" s="57">
+    <row r="16" ht="15" customHeight="1" s="57">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>width_mm</t>
@@ -3127,7 +3233,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C16" s="24" t="n"/>
+      <c r="C16" s="67" t="n"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>mm</t>
@@ -3143,18 +3249,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="G16" s="68" t="inlineStr">
         <is>
           <t>Vehicle width. Source: dimensions. Drives min aisle/door clearance.</t>
         </is>
       </c>
+      <c r="Q16" s="64" t="inlineStr">
+        <is>
+          <t>Wie breit ist das Fahrzeug? (mm; nur zur Information)</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>b86e480d-85b0-4da0-a044-f14efe49b28f</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="33.75" customHeight="1" s="57">
+    <row r="17" ht="15" customHeight="1" s="57">
       <c r="A17" s="19" t="inlineStr">
         <is>
           <t>operating_temp_min_c</t>
@@ -3165,7 +3276,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C17" s="28" t="n"/>
+      <c r="C17" s="69" t="n"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>°C</t>
@@ -3181,7 +3292,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="70" t="inlineStr">
         <is>
           <t>Lowest rated operating temperature the vehicle must sustain, in °C. NULL RULE — READ FIRST: this field is null by default. Only fill it if the tender document explicitly states an operating/working temperature value (with a °C or K unit) in an environment or technical-specification section. If the document does not state an operating temperature, output null. Do NOT supply any default, typical, or example value. Do NOT copy numbers from this field description, from matching-rule notes, or from domain guidance — those are explanatory text, never document evidence. Do NOT confuse temperatures with dates, year/revision numbers, quantities, or project metadata. Source: a 'working temperature' / 'operating temperature' figure in the document's environment or operating-conditions section.</t>
         </is>
@@ -3197,13 +3308,18 @@
       <c r="N17" t="n">
         <v>30</v>
       </c>
+      <c r="Q17" s="64" t="inlineStr">
+        <is>
+          <t>Wie kalt wird es am Betriebsort mindestens? (°C; z. B. –20 °C für Tiefkühlbereich)</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>6c7b2b2c-4f44-4bba-83c8-d2243cd787eb</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="33.75" customHeight="1" s="57">
+    <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>operating_temp_max_c</t>
@@ -3214,7 +3330,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C18" s="24" t="n"/>
+      <c r="C18" s="67" t="n"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>°C</t>
@@ -3230,7 +3346,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G18" s="68" t="inlineStr">
         <is>
           <t>Highest rated operating temperature the vehicle must sustain, in °C. NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states an operating/working temperature value (with a °C or K unit). If not stated, output null. Do NOT supply a default, typical, or example value, and do NOT copy numbers from this description or from rule notes. Do NOT confuse with dates, year numbers, or version codes. Source: a 'working temperature' / 'operating temperature' figure in the environment or operating-conditions section.</t>
         </is>
@@ -3246,13 +3362,18 @@
       <c r="N18" t="n">
         <v>60</v>
       </c>
+      <c r="Q18" s="64" t="inlineStr">
+        <is>
+          <t>Wie warm wird es am Betriebsort maximal? (°C; z. B. 30 °C für Produktionshalle)</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>67c103ef-c16f-4785-bfcf-8e264a462580</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="33.75" customHeight="1" s="57">
+    <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="19" t="inlineStr">
         <is>
           <t>operating_humidity_max_pct</t>
@@ -3263,7 +3384,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C19" s="28" t="n"/>
+      <c r="C19" s="69" t="n"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>%</t>
@@ -3279,7 +3400,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="70" t="inlineStr">
         <is>
           <t>Maximum rated relative humidity the vehicle must tolerate, as a percentage. NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a relative-humidity value as a % figure in an environment or technical-specification section. If no humidity percentage is stated, output null. Do NOT supply a default, typical, or example value, and do NOT copy numbers from this description or from rule/domain notes. Do NOT infer humidity from warehouse type, food/beverage context, washdown wording, or cold-storage environment. Source: an explicit relative-humidity % figure in the environment specification.</t>
         </is>
@@ -3295,13 +3416,18 @@
       <c r="N19" t="n">
         <v>100</v>
       </c>
+      <c r="Q19" s="64" t="inlineStr">
+        <is>
+          <t>Wie hoch ist die maximale relative Luftfeuchtigkeit am Betriebsort? (%)</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>9a61e67e-417c-44c6-946e-61ac6a02a17c</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="33.75" customHeight="1" s="57">
+    <row r="20" ht="15" customHeight="1" s="57">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>ingress_protection_rating</t>
@@ -3312,7 +3438,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C20" s="24" t="inlineStr">
+      <c r="C20" s="67" t="inlineStr">
         <is>
           <t>None | IP20 | IP44 | IP52 | IP54 | IP65 | IP67</t>
         </is>
@@ -3327,7 +3453,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="G20" s="68" t="inlineStr">
         <is>
           <t>IP code for dust/water resistance. Source: spec 'IP rating' — must be explicitly printed (e.g. 'IP54', 'IP65'). Cond. K.O.: IP52+ binds for dust/moisture/washdown (F&amp;B, beverage); standard AMRs ≈ IP20. 'None' = no rating stated. NULL RULE: null if no IP code is explicitly stated. Warehouse type, AGV type, and storage environment do NOT imply an IP rating — a VNA high-bay warehouse is NOT necessarily IP65.</t>
         </is>
@@ -3337,13 +3463,18 @@
           <t>KO_IF_NEQ</t>
         </is>
       </c>
+      <c r="Q20" s="64" t="inlineStr">
+        <is>
+          <t>Welche Schutzklasse (IP-Klasse) ist am Betriebsort erforderlich? (z. B. IP54 für Spritzwasserschutz)</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>004857ec-af13-4850-a69d-b6ca79a59618</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="33.75" customHeight="1" s="57">
+    <row r="21" ht="15" customHeight="1" s="57">
       <c r="A21" s="19" t="inlineStr">
         <is>
           <t>cleanroom_class</t>
@@ -3354,7 +3485,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C21" s="28" t="inlineStr">
+      <c r="C21" s="69" t="inlineStr">
         <is>
           <t>None | ISO 1–9</t>
         </is>
@@ -3369,7 +3500,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="70" t="inlineStr">
         <is>
           <t>Cleanroom certification, if any. Source: 'cleanroom version'. Cond. K.O.: binds only for pharma/semiconductor/sterile F&amp;B. 'None' = no cleanroom rating. NULL RULE: output 'None' or null unless the document explicitly states a cleanroom ISO class (e.g. 'ISO 7', 'cleanroom version'). Do NOT infer from words like 'clean', 'hygiene', or 'food-grade'.</t>
         </is>
@@ -3379,13 +3510,18 @@
           <t>KO_IF_NEQ</t>
         </is>
       </c>
+      <c r="Q21" s="64" t="inlineStr">
+        <is>
+          <t>Gibt es Reinraumanforderungen am Betriebsort? (ISO-Klasse; nur ausfüllen wenn Reinraum vorhanden)</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>fb32d20a-02cf-4fa3-9355-8674d59f308b</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="33.75" customHeight="1" s="57">
+    <row r="22" ht="15" customHeight="1" s="57">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>max_gradient_pct</t>
@@ -3396,7 +3532,7 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="C22" s="24" t="n"/>
+      <c r="C22" s="67" t="n"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>%</t>
@@ -3412,7 +3548,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="G22" s="68" t="inlineStr">
         <is>
           <t>Max ramp gradient the loaded unit handles. Source: spec 'gradeability' — must appear as an explicit % value. The value represents the steepest ramp gradient (%) the loaded vehicle must climb: 10 % ≈ 5.7° incline; most flat indoor warehouse floors have 0 % gradient and this field should be null. Cond. K.O.: binds only where the site has ramps/dock inclines. NULL RULE: null unless a slope or gradient percentage is explicitly stated in the document. Do NOT apply typical industry values (e.g. '5%') when the document is silent on gradients.</t>
         </is>
@@ -3428,13 +3564,18 @@
       <c r="N22" t="n">
         <v>30</v>
       </c>
+      <c r="Q22" s="64" t="inlineStr">
+        <is>
+          <t>Wie steil ist die steilste Fahrstrecke im Betriebsbereich? (% Steigung; z. B. 1,5 für eine 1,5-%-Rampe)</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>3b3c2e34-e8b7-402e-8ffe-f68c493a98f5</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="33.75" customHeight="1" s="57">
+    <row r="23" ht="15" customHeight="1" s="57">
       <c r="A23" s="19" t="inlineStr">
         <is>
           <t>floor_flatness_req</t>
@@ -3445,7 +3586,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C23" s="28" t="inlineStr">
+      <c r="C23" s="69" t="inlineStr">
         <is>
           <t>Standard (FM2) | High (FM1) | Very High (F-number) | None stated</t>
         </is>
@@ -3460,7 +3601,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="70" t="inlineStr">
         <is>
           <t>Floor flatness the system requires for safe operation/high-lift. Source: install requirements — must name a standard or value. Cond. K.O.: binds when the site floor is below spec → costly grinding. NULL RULE: null unless a floor quality standard (DIN 15185, FM number, FF number, etc.) or explicit flatness value is named. Do NOT infer from VNA or high-bay context.</t>
         </is>
@@ -3470,20 +3611,28 @@
           <t>KO_IF_GT</t>
         </is>
       </c>
+      <c r="Q23" s="64" t="inlineStr">
+        <is>
+          <t>Gibt es besondere Anforderungen an die Bodenqualität oder -ebenheit?</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>370e78f7-7291-48c3-a90f-6b710d81cd3b</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="15.75" customHeight="1" s="57">
+    <row r="24" ht="15" customHeight="1" s="57">
       <c r="A24" s="62" t="inlineStr">
         <is>
           <t>── ACCURACY</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="33.75" customHeight="1" s="57">
+      <c r="C24" s="64" t="n"/>
+      <c r="G24" s="64" t="n"/>
+      <c r="Q24" s="64" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="57">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>stop_accuracy_mm</t>
@@ -3494,7 +3643,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C25" s="24" t="n"/>
+      <c r="C25" s="67" t="n"/>
       <c r="D25" t="inlineStr">
         <is>
           <t>mm</t>
@@ -3510,7 +3659,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="G25" s="68" t="inlineStr">
         <is>
           <t>General docking/stop positioning accuracy at a target (e.g. ±5–10 mm on premium units). Source: spec 'positioning / stop accuracy'. Tighter = reliable hand-off. (moved here; forklift adds detailed pick/drop accuracy on top)</t>
         </is>
@@ -3529,20 +3678,28 @@
       <c r="L25" t="n">
         <v>30</v>
       </c>
+      <c r="Q25" s="64" t="inlineStr">
+        <is>
+          <t>Wie präzise muss das AGV an Übergabe- oder Aufnahmepunkten positionieren? (mm zulässige Abweichung)</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>7c2bd9ed-70e2-40fb-bb32-1304621fdeb5</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="57">
+    <row r="26" ht="15" customHeight="1" s="57">
       <c r="A26" s="62" t="inlineStr">
         <is>
           <t>── POWER</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="33.75" customHeight="1" s="57">
+      <c r="C26" s="64" t="n"/>
+      <c r="G26" s="64" t="n"/>
+      <c r="Q26" s="64" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="57">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>battery_type</t>
@@ -3553,7 +3710,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C27" s="24" t="inlineStr">
+      <c r="C27" s="67" t="inlineStr">
         <is>
           <t>Li-Ion | LiFePO4 | Lead-Acid | Hydrogen FC</t>
         </is>
@@ -3568,18 +3725,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G27" s="68" t="inlineStr">
         <is>
           <t>Energy storage technology. Source: 'battery'. Li-Ion/LiFePO4 = opportunity charging, no battery room; Lead-Acid = swap rooms. (consolidated here for all types)</t>
         </is>
       </c>
+      <c r="Q27" s="64" t="inlineStr">
+        <is>
+          <t>Welcher Batterietyp ist bevorzugt oder erforderlich?</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>60cd7189-d343-42db-aa3d-6788fd73ab34</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="33.75" customHeight="1" s="57">
+    <row r="28" ht="15" customHeight="1" s="57">
       <c r="A28" s="19" t="inlineStr">
         <is>
           <t>battery_runtime_h</t>
@@ -3590,7 +3752,7 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="C28" s="28" t="n"/>
+      <c r="C28" s="69" t="n"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>hours</t>
@@ -3606,7 +3768,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="70" t="inlineStr">
         <is>
           <t>Operating hours per charge. Source: 'runtime / operating time'. Pair with charge_time &amp; autonomous_charging for true uptime. (consolidated)</t>
         </is>
@@ -3625,13 +3787,18 @@
       <c r="O28" t="b">
         <v>1</v>
       </c>
+      <c r="Q28" s="64" t="inlineStr">
+        <is>
+          <t>Wie viele Stunden Betriebszeit pro Ladung werden mindestens benötigt? (h)</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>c93c2b2c-350f-4858-b2f8-172ead5b99d3</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="33.75" customHeight="1" s="57">
+    <row r="29" ht="15" customHeight="1" s="57">
       <c r="A29" s="16" t="inlineStr">
         <is>
           <t>charge_time_min</t>
@@ -3642,7 +3809,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C29" s="24" t="n"/>
+      <c r="C29" s="67" t="n"/>
       <c r="D29" t="inlineStr">
         <is>
           <t>min</t>
@@ -3658,18 +3825,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G29" s="18" t="inlineStr">
+      <c r="G29" s="68" t="inlineStr">
         <is>
           <t>Recharge / fast-charge duration. Source: 'charging time' (e.g. Geek+ ~10 min opportunity; Locus Vector ~60 min full). Short charge + auto-charging ≈ continuous run. (consolidated)</t>
         </is>
       </c>
+      <c r="Q29" s="64" t="inlineStr">
+        <is>
+          <t>Wie lange darf ein vollständiger Ladevorgang maximal dauern? (min)</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>e2b8a10f-5e90-4de9-93f0-3bba7a52f6fa</t>
         </is>
       </c>
     </row>
-    <row r="30" ht="33.75" customHeight="1" s="57">
+    <row r="30" ht="15" customHeight="1" s="57">
       <c r="A30" s="19" t="inlineStr">
         <is>
           <t>autonomous_charging</t>
@@ -3680,7 +3852,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C30" s="28" t="n"/>
+      <c r="C30" s="69" t="n"/>
       <c r="E30" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -3691,7 +3863,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G30" s="21" t="inlineStr">
+      <c r="G30" s="70" t="inlineStr">
         <is>
           <t>Self-charging / auto opportunity-charging or auto battery-swap without operator. Source: 'automatic charging'. Enables 24/7 unattended operation. (consolidated here for all types)</t>
         </is>
@@ -3707,13 +3879,18 @@
       <c r="O30" t="b">
         <v>1</v>
       </c>
+      <c r="Q30" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AGV eigenständig zur Ladestation fahren und automatisch laden?</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>6e19998f-2ee7-441f-b8c9-f2c48220c459</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="33.75" customHeight="1" s="57">
+    <row r="31" ht="15" customHeight="1" s="57">
       <c r="A31" s="16" t="inlineStr">
         <is>
           <t>battery_swap_capable</t>
@@ -3724,7 +3901,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C31" s="24" t="n"/>
+      <c r="C31" s="67" t="n"/>
       <c r="E31" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -3735,25 +3912,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G31" s="18" t="inlineStr">
+      <c r="G31" s="68" t="inlineStr">
         <is>
           <t>Supports quick manual battery hot-swap (e.g. MiR). Source: 'battery swap'. Alternative to charging dwell for very high duty cycles. (consolidated)</t>
         </is>
       </c>
+      <c r="Q31" s="64" t="inlineStr">
+        <is>
+          <t>Ist ein schneller manueller Akkuwechsel statt Laden gewünscht?</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>0512f334-04ce-4a64-84c3-f6e0f2eada9e</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="15.75" customHeight="1" s="57">
+    <row r="32" ht="15" customHeight="1" s="57">
       <c r="A32" s="62" t="inlineStr">
         <is>
           <t>── SAFETY &amp; CERTIFICATION</t>
         </is>
       </c>
-    </row>
-    <row r="33" ht="33.75" customHeight="1" s="57">
+      <c r="C32" s="64" t="n"/>
+      <c r="G32" s="64" t="n"/>
+      <c r="Q32" s="64" t="n"/>
+    </row>
+    <row r="33" ht="15" customHeight="1" s="57">
       <c r="A33" s="16" t="inlineStr">
         <is>
           <t>safety_standard</t>
@@ -3764,7 +3949,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C33" s="24" t="inlineStr">
+      <c r="C33" s="67" t="inlineStr">
         <is>
           <t>None | ISO 3691-4 | EN 1525 (legacy) | ANSI/ITSDF B56.5 | UL 3100</t>
         </is>
@@ -3779,7 +3964,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G33" s="18" t="inlineStr">
+      <c r="G33" s="68" t="inlineStr">
         <is>
           <t>Declared driverless-truck SAFETY standards only. Source: 'certification / compliance'. ISO 3691-4 is the current EU AGV/AMR safety norm — its presence raises trust. (Removed CE = conformity marking, and IEC 62443 = cybersecurity — neither is a safety standard.)</t>
         </is>
@@ -3792,13 +3977,18 @@
           <t>nonempty</t>
         </is>
       </c>
+      <c r="Q33" s="64" t="inlineStr">
+        <is>
+          <t>Welche Sicherheitsnormen müssen erfüllt sein? (z. B. EN ISO 3691-4)</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>05e8ead4-bc7f-4209-af5d-d4ac5e9417ee</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="33.75" customHeight="1" s="57">
+    <row r="34" ht="15" customHeight="1" s="57">
       <c r="A34" s="19" t="inlineStr">
         <is>
           <t>functional_safety_level</t>
@@ -3809,7 +3999,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C34" s="28" t="inlineStr">
+      <c r="C34" s="69" t="inlineStr">
         <is>
           <t>None | PLd | PLe | SIL 2 | SIL 3</t>
         </is>
@@ -3824,7 +4014,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G34" s="21" t="inlineStr">
+      <c r="G34" s="70" t="inlineStr">
         <is>
           <t>Performance Level (ISO 13849) of the safety function. Source: safety datasheet. Higher PL = safer human-robot coexistence in shared aisles.</t>
         </is>
@@ -3837,13 +4027,18 @@
           <t>nonempty</t>
         </is>
       </c>
+      <c r="Q34" s="64" t="inlineStr">
+        <is>
+          <t>Welches funktionale Sicherheitsniveau ist gefordert? (z. B. PLd, SIL2)</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>88596a40-f85b-4361-90aa-ca3e16456a85</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="33.75" customHeight="1" s="57">
+    <row r="35" ht="15" customHeight="1" s="57">
       <c r="A35" s="16" t="inlineStr">
         <is>
           <t>safety_coverage</t>
@@ -3854,7 +4049,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C35" s="24" t="inlineStr">
+      <c r="C35" s="67" t="inlineStr">
         <is>
           <t>Single plane (2D) | Limited 3D (e.g. waterfall) | Full 3D</t>
         </is>
@@ -3869,25 +4064,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G35" s="18" t="inlineStr">
+      <c r="G35" s="68" t="inlineStr">
         <is>
           <t>What volume the safety sensors monitor: floor-level 2D scan, partial 3D ('waterfall' front field), or full 3D. Source: 'safety scanner / 3D camera'. Full 3D detects overhanging/low obstacles → fewer collisions.</t>
         </is>
       </c>
+      <c r="Q35" s="64" t="inlineStr">
+        <is>
+          <t>Welche Bereiche rund um das Fahrzeug müssen durch Sicherheitssensorik abgedeckt werden?</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>ba6fa567-5b42-46fb-a2cf-b9d0bc986d1a</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="15.75" customHeight="1" s="57">
+    <row r="36" ht="15" customHeight="1" s="57">
       <c r="A36" s="62" t="inlineStr">
         <is>
           <t>── FLEET &amp; INTEGRATION</t>
         </is>
       </c>
-    </row>
-    <row r="37" ht="33.75" customHeight="1" s="57">
+      <c r="C36" s="64" t="n"/>
+      <c r="G36" s="64" t="n"/>
+      <c r="Q36" s="64" t="n"/>
+    </row>
+    <row r="37" ht="15" customHeight="1" s="57">
       <c r="A37" s="16" t="inlineStr">
         <is>
           <t>fleet_management_system</t>
@@ -3898,7 +4101,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C37" s="24" t="inlineStr">
+      <c r="C37" s="67" t="inlineStr">
         <is>
           <t>Proprietary | Open API | VDA 5050 compatible | Third-party WMS native</t>
         </is>
@@ -3913,7 +4116,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G37" s="18" t="inlineStr">
+      <c r="G37" s="68" t="inlineStr">
         <is>
           <t>Architecture of the fleet controller. Source: 'fleet manager / software'. Implies lock-in vs. interoperability. NULL RULE: output null unless the tender explicitly names a required fleet-controller architecture (one of the allowed values). Do NOT infer from the mere presence of a WMS, fleet software, or VDA 5050 mention — those are separate fields.</t>
         </is>
@@ -3923,13 +4126,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q37" s="64" t="inlineStr">
+        <is>
+          <t>Gibt es ein bestehendes Flottenleitsystem, das kompatibel sein muss?</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
           <t>04fb859e-054a-4360-bf75-af62c03d73c9</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="33.75" customHeight="1" s="57">
+    <row r="38" ht="15" customHeight="1" s="57">
       <c r="A38" s="19" t="inlineStr">
         <is>
           <t>fleet_control_architecture</t>
@@ -3940,7 +4148,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C38" s="28" t="inlineStr">
+      <c r="C38" s="69" t="inlineStr">
         <is>
           <t>Centralized | Decentralized/Swarm | Hybrid</t>
         </is>
@@ -3955,18 +4163,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G38" s="21" t="inlineStr">
+      <c r="G38" s="70" t="inlineStr">
         <is>
           <t>Central server vs. on-board swarm logic (e.g. AGILOX X-SWARM). Source: 'centralized control / swarm'. Decentralized = no server, simpler scaling &amp; failover.</t>
         </is>
       </c>
+      <c r="Q38" s="64" t="inlineStr">
+        <is>
+          <t>Welche Steuerungsarchitektur ist für die Flotte vorgesehen? (z. B. zentralisiert, dezentralisiert)</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>b8c12d22-1c46-4c2d-96b4-ec2c06d16c99</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="33.75" customHeight="1" s="57">
+    <row r="39" ht="15" customHeight="1" s="57">
       <c r="A39" s="16" t="inlineStr">
         <is>
           <t>vda5050_compatible</t>
@@ -3977,7 +4190,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C39" s="24" t="n"/>
+      <c r="C39" s="67" t="n"/>
       <c r="E39" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -3988,7 +4201,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G39" s="18" t="inlineStr">
+      <c r="G39" s="68" t="inlineStr">
         <is>
           <t>Supports VDA 5050 (open AGV↔master-control interface standard). Source: 'VDA 5050 ready' or 'VDA-5050'. Cond. K.O.: trending to a hard requirement for large EU multi-vendor tenders. NULL RULE: null unless the document literally contains 'VDA 5050' or 'VDA-5050'. Do NOT infer from fleet management, MES/WMS integration, or system openness requirements.</t>
         </is>
@@ -4009,13 +4222,18 @@
       <c r="O39" t="b">
         <v>1</v>
       </c>
+      <c r="Q39" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AGV den VDA-5050-Standard für Schnittstellen unterstützen?</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
           <t>1830f69a-d29d-4a51-944f-32b621922117</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="33.75" customHeight="1" s="57">
+    <row r="40" ht="15" customHeight="1" s="57">
       <c r="A40" s="19" t="inlineStr">
         <is>
           <t>max_fleet_size</t>
@@ -4026,7 +4244,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C40" s="28" t="n"/>
+      <c r="C40" s="69" t="n"/>
       <c r="D40" t="inlineStr">
         <is>
           <t># units</t>
@@ -4042,18 +4260,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G40" s="21" t="inlineStr">
+      <c r="G40" s="70" t="inlineStr">
         <is>
           <t>Max vehicles in one managed fleet. Source: 'fleet / scalability'. Implies growth headroom for phased/peak rollouts. (consolidated)</t>
         </is>
       </c>
+      <c r="Q40" s="64" t="inlineStr">
+        <is>
+          <t>Wie viele AGVs sollen gleichzeitig im Einsatz sein?</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
           <t>e8e1e6a0-0cd9-4685-a8e7-e59ccc64d635</t>
         </is>
       </c>
     </row>
-    <row r="41" ht="33.75" customHeight="1" s="57">
+    <row r="41" ht="15" customHeight="1" s="57">
       <c r="A41" s="16" t="inlineStr">
         <is>
           <t>multi_fleet_capable</t>
@@ -4064,7 +4287,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C41" s="24" t="n"/>
+      <c r="C41" s="67" t="n"/>
       <c r="E41" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -4075,18 +4298,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G41" s="18" t="inlineStr">
+      <c r="G41" s="68" t="inlineStr">
         <is>
           <t>Interoperates with other vendors' robots (open / VDA 5050 fleet). Source: 'mixed fleet'. Avoids vendor lock-in. (consolidated)</t>
         </is>
       </c>
+      <c r="Q41" s="64" t="inlineStr">
+        <is>
+          <t>Müssen AGVs verschiedener Hersteller im selben Bereich kooperieren können?</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>3222f9f6-d19a-4a6a-9365-dd55ee59ba85</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="33.75" customHeight="1" s="57">
+    <row r="42" ht="15" customHeight="1" s="57">
       <c r="A42" s="19" t="inlineStr">
         <is>
           <t>integration_capability</t>
@@ -4097,7 +4325,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C42" s="28" t="inlineStr">
+      <c r="C42" s="69" t="inlineStr">
         <is>
           <t>None | SAP | WMS | ERP | MES | REST API | MQTT | OPC-UA | Modbus</t>
         </is>
@@ -4112,18 +4340,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G42" s="21" t="inlineStr">
+      <c r="G42" s="70" t="inlineStr">
         <is>
           <t>System integrations required by the tender. Extract all mentioned: SAP, WMS, ERP, MES, REST API, MQTT, OPC-UA, Modbus, etc. List comma-separated. null if none mentioned.</t>
         </is>
       </c>
+      <c r="Q42" s="64" t="inlineStr">
+        <is>
+          <t>Mit welchen bestehenden Systemen muss das AGV integriert werden? (WMS, ERP, MES)</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>96328930-c387-438f-82a1-8fd17fbded91</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="33.75" customHeight="1" s="57">
+    <row r="43" ht="15" customHeight="1" s="57">
       <c r="A43" s="16" t="inlineStr">
         <is>
           <t>installation_process</t>
@@ -4134,7 +4367,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C43" s="24" t="inlineStr">
+      <c r="C43" s="67" t="inlineStr">
         <is>
           <t>Supplier only | Client</t>
         </is>
@@ -4149,18 +4382,23 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G43" s="18" t="inlineStr">
+      <c r="G43" s="68" t="inlineStr">
         <is>
           <t>Who may physically install/commission on site. Source: 'commissioning / deployment'. Client-installable = faster, cheaper rollout &amp; expansion.</t>
         </is>
       </c>
+      <c r="Q43" s="64" t="inlineStr">
+        <is>
+          <t>Gibt es besondere Anforderungen an den Installationsprozess des AGV-Systems?</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
           <t>c348cf0d-97ef-4b47-8358-853ea980f00d</t>
         </is>
       </c>
     </row>
-    <row r="44" ht="33.75" customHeight="1" s="57">
+    <row r="44" ht="15" customHeight="1" s="57">
       <c r="A44" s="19" t="inlineStr">
         <is>
           <t>modification_process</t>
@@ -4171,7 +4409,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C44" s="28" t="inlineStr">
+      <c r="C44" s="69" t="inlineStr">
         <is>
           <t>Supplier only | Supplier limited | Client: All</t>
         </is>
@@ -4186,25 +4424,33 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G44" s="21" t="inlineStr">
+      <c r="G44" s="70" t="inlineStr">
         <is>
           <t>Who may change routes/stations/layout AFTER go-live. Source: 'teach-in / map editing'. 'Supplier limited' = supplier does it but with a constrained/quick-change service; 'Client: All' = full operational autonomy. (renamed per request)</t>
         </is>
       </c>
+      <c r="Q44" s="64" t="inlineStr">
+        <is>
+          <t>Wie einfach müssen spätere Anpassungen oder Erweiterungen möglich sein?</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
           <t>9babddb2-3951-4b4b-9c61-c80a0257a2b9</t>
         </is>
       </c>
     </row>
-    <row r="45" ht="15.75" customHeight="1" s="57">
+    <row r="45" ht="15" customHeight="1" s="57">
       <c r="A45" s="62" t="inlineStr">
         <is>
           <t>── STATIONS</t>
         </is>
       </c>
-    </row>
-    <row r="46" ht="33.75" customHeight="1" s="57">
+      <c r="C45" s="64" t="n"/>
+      <c r="G45" s="64" t="n"/>
+      <c r="Q45" s="64" t="n"/>
+    </row>
+    <row r="46" ht="15" customHeight="1" s="57">
       <c r="A46" s="16" t="inlineStr">
         <is>
           <t>station_applications</t>
@@ -4215,7 +4461,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C46" s="24" t="inlineStr">
+      <c r="C46" s="67" t="inlineStr">
         <is>
           <t>Floor | Conveyor | Machine cell | Gravity rack | Pushback rack | Drive-in rack | Standard rack | Shuttle rack | Mobile rack | Workstation | Dock</t>
         </is>
@@ -4230,7 +4476,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G46" s="18" t="inlineStr">
+      <c r="G46" s="68" t="inlineStr">
         <is>
           <t>Pick/drop station types the AGV must serve. Extract all mentioned: Floor, Conveyor, Machine cell, Gravity rack, Pushback rack, Drive-in rack. If any conveyor station mentioned → include 'Conveyor'. List comma-separated.</t>
         </is>
@@ -4240,20 +4486,28 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q46" s="64" t="inlineStr">
+        <is>
+          <t>Welche speziellen Stationsanwendungen werden benötigt? (z. B. Ladestation, Übergabestation)</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr">
         <is>
           <t>f9edb5e9-d78d-4717-83d4-8f050fc181a9</t>
         </is>
       </c>
     </row>
-    <row r="47" ht="15.75" customHeight="1" s="57">
+    <row r="47" ht="15" customHeight="1" s="57">
       <c r="A47" s="62" t="inlineStr">
         <is>
           <t>── COMMERCIAL</t>
         </is>
       </c>
-    </row>
-    <row r="48" ht="33.75" customHeight="1" s="57">
+      <c r="C47" s="64" t="n"/>
+      <c r="G47" s="64" t="n"/>
+      <c r="Q47" s="64" t="n"/>
+    </row>
+    <row r="48" ht="15" customHeight="1" s="57">
       <c r="A48" s="16" t="inlineStr">
         <is>
           <t>reference_count</t>
@@ -4264,7 +4518,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C48" s="24" t="n"/>
+      <c r="C48" s="67" t="n"/>
       <c r="D48" t="inlineStr">
         <is>
           <t># projects</t>
@@ -4280,7 +4534,7 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G48" s="18" t="inlineStr">
+      <c r="G48" s="68" t="inlineStr">
         <is>
           <t>Completed reference installs. Source: 'references / case studies' or ask supplier. Proxy for maturity; blank = unknown (NOT zero).</t>
         </is>
@@ -4299,13 +4553,18 @@
       <c r="O48" t="b">
         <v>1</v>
       </c>
+      <c r="Q48" s="64" t="inlineStr">
+        <is>
+          <t>Anzahl der Referenzprojekte des Anbieters (wird automatisch befüllt)</t>
+        </is>
+      </c>
       <c r="R48" t="inlineStr">
         <is>
           <t>7d329711-2bad-4b69-823f-dcc3ca1c8ade</t>
         </is>
       </c>
     </row>
-    <row r="49" ht="33.75" customHeight="1" s="57">
+    <row r="49" ht="15" customHeight="1" s="57">
       <c r="A49" s="19" t="inlineStr">
         <is>
           <t>lead_time_weeks</t>
@@ -4316,7 +4575,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C49" s="28" t="n"/>
+      <c r="C49" s="69" t="n"/>
       <c r="D49" t="inlineStr">
         <is>
           <t>weeks</t>
@@ -4332,7 +4591,7 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G49" s="21" t="inlineStr">
+      <c r="G49" s="70" t="inlineStr">
         <is>
           <t>Typical order-to-commissioning time. Source: sales-provided (rarely on web). Shorter = better; leave blank if unverified.</t>
         </is>
@@ -4354,13 +4613,18 @@
       <c r="O49" t="b">
         <v>1</v>
       </c>
+      <c r="Q49" s="64" t="inlineStr">
+        <is>
+          <t>Wie viele Wochen Vorlaufzeit bis zur Inbetriebnahme sind akzeptabel?</t>
+        </is>
+      </c>
       <c r="R49" t="inlineStr">
         <is>
           <t>62344aff-cb9d-40c2-9329-a85b34e1d62a</t>
         </is>
       </c>
     </row>
-    <row r="50" ht="33.75" customHeight="1" s="57">
+    <row r="50" ht="15" customHeight="1" s="57">
       <c r="A50" s="16" t="inlineStr">
         <is>
           <t>service_coverage</t>
@@ -4371,7 +4635,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C50" s="24" t="inlineStr">
+      <c r="C50" s="67" t="inlineStr">
         <is>
           <t>None | DACH | EU | Global</t>
         </is>
@@ -4386,7 +4650,7 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G50" s="18" t="inlineStr">
+      <c r="G50" s="68" t="inlineStr">
         <is>
           <t>Geographic service &amp; support reach. Source: 'locations / service network'. Cond. K.O.: hard filter when the buyer needs fast on-site SLA in a specific region. 'None' = no own network stated. NULL RULE: output null unless the tender explicitly demands a service/support region. Do NOT infer coverage from the document language or buyer location.</t>
         </is>
@@ -4399,13 +4663,18 @@
       <c r="O50" t="b">
         <v>1</v>
       </c>
+      <c r="Q50" s="64" t="inlineStr">
+        <is>
+          <t>In welchen Ländern oder Regionen ist Service und Support erforderlich?</t>
+        </is>
+      </c>
       <c r="R50" t="inlineStr">
         <is>
           <t>7ca18941-1522-4b3d-a34e-38fb11dad36b</t>
         </is>
       </c>
     </row>
-    <row r="51" ht="33.75" customHeight="1" s="57">
+    <row r="51" ht="15" customHeight="1" s="57">
       <c r="A51" s="19" t="inlineStr">
         <is>
           <t>min_fleet_size</t>
@@ -4416,7 +4685,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C51" s="28" t="n"/>
+      <c r="C51" s="69" t="n"/>
       <c r="D51" t="inlineStr">
         <is>
           <t># units</t>
@@ -4432,18 +4701,23 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G51" s="21" t="inlineStr">
+      <c r="G51" s="70" t="inlineStr">
         <is>
           <t>Smallest sensible deployment. Source: sales/solution pages. High minimums exclude small first-time buyers.</t>
         </is>
       </c>
+      <c r="Q51" s="64" t="inlineStr">
+        <is>
+          <t>Wie viele AGVs werden mindestens benötigt?</t>
+        </is>
+      </c>
       <c r="R51" t="inlineStr">
         <is>
           <t>660e8f14-5ca7-4808-bfea-64c35479acba</t>
         </is>
       </c>
     </row>
-    <row r="52" ht="33.75" customHeight="1" s="57">
+    <row r="52" ht="15" customHeight="1" s="57">
       <c r="A52" s="16" t="inlineStr">
         <is>
           <t>typical_project_value_eur</t>
@@ -4454,7 +4728,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C52" s="24" t="inlineStr">
+      <c r="C52" s="67" t="inlineStr">
         <is>
           <t>&lt;50k | 50–250k | 250k–1M | &gt;1M</t>
         </is>
@@ -4469,25 +4743,33 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G52" s="18" t="inlineStr">
+      <c r="G52" s="68" t="inlineStr">
         <is>
           <t>Typical total project value band. Source: inferred from references/sales. Budget-fit orientation.</t>
         </is>
       </c>
+      <c r="Q52" s="64" t="inlineStr">
+        <is>
+          <t>Welches Budget steht für das AGV-Projekt zur Verfügung? (EUR)</t>
+        </is>
+      </c>
       <c r="R52" t="inlineStr">
         <is>
           <t>9f4b2836-0d81-4441-8eb0-bf079dd6a4d9</t>
         </is>
       </c>
     </row>
-    <row r="53" ht="15.75" customHeight="1" s="57">
+    <row r="53" ht="15" customHeight="1" s="57">
       <c r="A53" s="62" t="inlineStr">
         <is>
           <t>── CONTEXT</t>
         </is>
       </c>
-    </row>
-    <row r="54" ht="33.75" customHeight="1" s="57">
+      <c r="C53" s="64" t="n"/>
+      <c r="G53" s="64" t="n"/>
+      <c r="Q53" s="64" t="n"/>
+    </row>
+    <row r="54" ht="15" customHeight="1" s="57">
       <c r="A54" s="16" t="inlineStr">
         <is>
           <t>manual_usage</t>
@@ -4498,7 +4780,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C54" s="24" t="n"/>
+      <c r="C54" s="67" t="n"/>
       <c r="E54" s="31" t="inlineStr">
         <is>
           <t>Context</t>
@@ -4509,18 +4791,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G54" s="18" t="inlineStr">
+      <c r="G54" s="68" t="inlineStr">
         <is>
           <t>Can be driven manually (operator on board / walkie) as fallback. Source: 'manual / semi-automatic mode'. Redundancy reassurance for first-time automation buyers.</t>
         </is>
       </c>
+      <c r="Q54" s="64" t="inlineStr">
+        <is>
+          <t>Soll das Fahrzeug auch manuell bedienbar sein?</t>
+        </is>
+      </c>
       <c r="R54" t="inlineStr">
         <is>
           <t>16867284-4633-4de6-a1f3-0d10181630d4</t>
         </is>
       </c>
     </row>
-    <row r="55" ht="33.75" customHeight="1" s="57">
+    <row r="55" ht="15" customHeight="1" s="57">
       <c r="A55" s="19" t="inlineStr">
         <is>
           <t>industries_served</t>
@@ -4531,7 +4818,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C55" s="28" t="inlineStr">
+      <c r="C55" s="69" t="inlineStr">
         <is>
           <t>None | Automotive | F&amp;B | Pharma | E-Commerce | General Manufacturing | 3PL | Retail</t>
         </is>
@@ -4546,18 +4833,23 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G55" s="21" t="inlineStr">
+      <c r="G55" s="70" t="inlineStr">
         <is>
           <t>Verticals with live references. Source: 'industries / case studies'. Weigh F&amp;B references for the target market.</t>
         </is>
       </c>
+      <c r="Q55" s="64" t="inlineStr">
+        <is>
+          <t>In welcher Branche wird das AGV eingesetzt?</t>
+        </is>
+      </c>
       <c r="R55" t="inlineStr">
         <is>
           <t>64e57189-87ab-4b62-9b62-8b10aecf143c</t>
         </is>
       </c>
     </row>
-    <row r="56" ht="33.75" customHeight="1" s="57">
+    <row r="56" ht="15" customHeight="1" s="57">
       <c r="A56" s="16" t="inlineStr">
         <is>
           <t>distribution_model</t>
@@ -4568,7 +4860,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C56" s="24" t="inlineStr">
+      <c r="C56" s="67" t="inlineStr">
         <is>
           <t>Direct | Dealer Network | Integrator only | License Platform</t>
         </is>
@@ -4583,25 +4875,33 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G56" s="18" t="inlineStr">
+      <c r="G56" s="68" t="inlineStr">
         <is>
           <t>How the product reaches the customer. Source: 'partners / dealers / where to buy'. Tells the buyer WHO they actually contract with. (NB: lives on the Product layer L2, not the base model.)</t>
         </is>
       </c>
+      <c r="Q56" s="64" t="inlineStr">
+        <is>
+          <t>Wie wird das AGV vertrieben bzw. geliefert?</t>
+        </is>
+      </c>
       <c r="R56" t="inlineStr">
         <is>
           <t>e3577e52-3cdf-4975-8754-97352919eb3e</t>
         </is>
       </c>
     </row>
-    <row r="57">
+    <row r="57" ht="15" customHeight="1" s="57">
       <c r="A57" s="38" t="inlineStr">
         <is>
           <t>── COMPANY / PRODUCT FIELDS (matched from companies + products tables)</t>
         </is>
       </c>
-    </row>
-    <row r="58" ht="350" customHeight="1" s="57">
+      <c r="C57" s="64" t="n"/>
+      <c r="G57" s="64" t="n"/>
+      <c r="Q57" s="64" t="n"/>
+    </row>
+    <row r="58" ht="15" customHeight="1" s="57">
       <c r="A58" s="39" t="inlineStr">
         <is>
           <t>agv_type</t>
@@ -4612,7 +4912,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C58" s="39" t="inlineStr">
+      <c r="C58" s="71" t="inlineStr">
         <is>
           <t>Forklift AGV | Tugger AGV | Mobile AMR</t>
         </is>
@@ -4627,7 +4927,7 @@
           <t>Product</t>
         </is>
       </c>
-      <c r="G58" s="42" t="inlineStr">
+      <c r="G58" s="71" t="inlineStr">
         <is>
           <t>AGV/AMR category. Output exactly one of the allowed values. Hard K.O.: Forklift AGV never matches Tugger or AMR.</t>
         </is>
@@ -4642,13 +4942,18 @@
           <t>display</t>
         </is>
       </c>
+      <c r="Q58" s="64" t="inlineStr">
+        <is>
+          <t>Welcher AGV-Typ ist erforderlich? (wird automatisch aus der Ausschreibung erkannt)</t>
+        </is>
+      </c>
       <c r="R58" t="inlineStr">
         <is>
           <t>325dd61d-f828-4639-a128-fd5e1a1a3728</t>
         </is>
       </c>
     </row>
-    <row r="59" ht="409.6" customHeight="1" s="57">
+    <row r="59" ht="15" customHeight="1" s="57">
       <c r="A59" s="43" t="inlineStr">
         <is>
           <t>country</t>
@@ -4659,7 +4964,7 @@
           <t>ISO 3166 (2-letter)</t>
         </is>
       </c>
-      <c r="C59" s="43" t="inlineStr">
+      <c r="C59" s="72" t="inlineStr">
         <is>
           <t>DE | AT | CH | …</t>
         </is>
@@ -4674,7 +4979,7 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="G59" s="45" t="inlineStr">
+      <c r="G59" s="72" t="inlineStr">
         <is>
           <t>HQ country of the selling company. Used as Cond. K.O. when buyer requires domestic or regional supplier. NULL RULE: output null unless the tender explicitly requires a domestic or specific-country supplier. Do NOT infer from buyer address or document language.</t>
         </is>
@@ -4684,13 +4989,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q59" s="64" t="inlineStr">
+        <is>
+          <t>In welchem Land befindet sich der Betriebsort?</t>
+        </is>
+      </c>
       <c r="R59" t="inlineStr">
         <is>
           <t>d220b0c4-b012-44d1-8caa-8cce800904de</t>
         </is>
       </c>
     </row>
-    <row r="60" ht="256" customHeight="1" s="57">
+    <row r="60" ht="15" customHeight="1" s="57">
       <c r="A60" s="39" t="inlineStr">
         <is>
           <t>employee_count_range</t>
@@ -4701,7 +5011,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C60" s="39" t="inlineStr">
+      <c r="C60" s="71" t="inlineStr">
         <is>
           <t>&lt;50 | 50–250 | 250–1000 | &gt;1000</t>
         </is>
@@ -4716,18 +5026,23 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="G60" s="42" t="inlineStr">
+      <c r="G60" s="71" t="inlineStr">
         <is>
           <t>Headcount band of the company. Proxy for project capacity and financial stability.</t>
         </is>
       </c>
+      <c r="Q60" s="64" t="inlineStr">
+        <is>
+          <t>Mitarbeiteranzahl des Herstellers (wird automatisch befüllt)</t>
+        </is>
+      </c>
       <c r="R60" t="inlineStr">
         <is>
           <t>cd5d42f2-9e0c-421a-a683-9ec754e23661</t>
         </is>
       </c>
     </row>
-    <row r="61" ht="304" customHeight="1" s="57">
+    <row r="61" ht="15" customHeight="1" s="57">
       <c r="A61" s="43" t="inlineStr">
         <is>
           <t>certifications_generic</t>
@@ -4738,7 +5053,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C61" s="43" t="inlineStr">
+      <c r="C61" s="72" t="inlineStr">
         <is>
           <t>ISO 9001 | ISO 14001 | ISO 45001 | CE | …</t>
         </is>
@@ -4753,18 +5068,23 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="G61" s="45" t="inlineStr">
+      <c r="G61" s="72" t="inlineStr">
         <is>
           <t>Company-level quality and compliance certifications. Supplements product-level safety_standard.</t>
         </is>
       </c>
+      <c r="Q61" s="64" t="inlineStr">
+        <is>
+          <t>Welche Zertifizierungen muss der Hersteller nachweisen? (z. B. ISO 9001)</t>
+        </is>
+      </c>
       <c r="R61" t="inlineStr">
         <is>
           <t>da18d0c0-fc3b-4400-8a3a-2d3c02467615</t>
         </is>
       </c>
     </row>
-    <row r="62" ht="395" customHeight="1" s="57">
+    <row r="62" ht="15" customHeight="1" s="57">
       <c r="A62" s="39" t="inlineStr">
         <is>
           <t>languages_spoken</t>
@@ -4775,7 +5095,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C62" s="39" t="inlineStr">
+      <c r="C62" s="71" t="inlineStr">
         <is>
           <t>DE | EN | FR | ES | ZH | …</t>
         </is>
@@ -4790,7 +5110,7 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="G62" s="42" t="inlineStr">
+      <c r="G62" s="71" t="inlineStr">
         <is>
           <t>Support languages required. Output 2-letter ISO 639-1 codes only (DE, EN, FR, ES, ZH), comma-separated. null = not stated.</t>
         </is>
@@ -4800,13 +5120,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q62" s="64" t="inlineStr">
+        <is>
+          <t>Welche Sprache(n) muss der Hersteller für Support und Dokumentation beherrschen?</t>
+        </is>
+      </c>
       <c r="R62" t="inlineStr">
         <is>
           <t>f4b07ccf-cc19-413c-9cea-2b6c2fc3c7ad</t>
         </is>
       </c>
     </row>
-    <row r="63" ht="240" customHeight="1" s="57">
+    <row r="63" ht="15" customHeight="1" s="57">
       <c r="A63" s="43" t="inlineStr">
         <is>
           <t>hq_city</t>
@@ -4817,7 +5142,7 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="C63" s="43" t="n"/>
+      <c r="C63" s="72" t="n"/>
       <c r="E63" s="47" t="inlineStr">
         <is>
           <t>Context</t>
@@ -4828,18 +5153,23 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="G63" s="45" t="inlineStr">
+      <c r="G63" s="72" t="inlineStr">
         <is>
           <t>City of headquarters. Context only — helps buyer assess geographic proximity.</t>
         </is>
       </c>
+      <c r="Q63" s="64" t="inlineStr">
+        <is>
+          <t>Hauptsitz des Herstellers (wird automatisch befüllt)</t>
+        </is>
+      </c>
       <c r="R63" t="inlineStr">
         <is>
           <t>1b74765a-4dca-4216-905d-469f7f846a5e</t>
         </is>
       </c>
     </row>
-    <row r="64" ht="256" customHeight="1" s="57">
+    <row r="64" ht="15" customHeight="1" s="57">
       <c r="A64" s="39" t="inlineStr">
         <is>
           <t>founding_year</t>
@@ -4850,7 +5180,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C64" s="39" t="n"/>
+      <c r="C64" s="71" t="n"/>
       <c r="E64" s="47" t="inlineStr">
         <is>
           <t>Context</t>
@@ -4861,9 +5191,14 @@
           <t>Company</t>
         </is>
       </c>
-      <c r="G64" s="42" t="inlineStr">
+      <c r="G64" s="71" t="inlineStr">
         <is>
           <t>Year founded. Context only — indicative of market maturity and stability.</t>
+        </is>
+      </c>
+      <c r="Q64" s="64" t="inlineStr">
+        <is>
+          <t>Gründungsjahr des Herstellers (wird automatisch befüllt)</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -4900,16 +5235,24 @@
   <dimension ref="A1:R31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="57" min="1" max="1"/>
-    <col width="13" customWidth="1" style="57" min="2" max="2"/>
-    <col width="30" customWidth="1" style="57" min="3" max="3"/>
-    <col width="10" customWidth="1" style="57" min="4" max="4"/>
-    <col width="13" customWidth="1" style="57" min="5" max="5"/>
-    <col width="7" customWidth="1" style="57" min="6" max="6"/>
-    <col width="60" customWidth="1" style="57" min="7" max="7"/>
-    <col width="51.6640625" customWidth="1" style="57" min="8" max="8"/>
+    <col width="30" customWidth="1" style="57" min="1" max="1"/>
+    <col width="14" customWidth="1" style="57" min="2" max="2"/>
+    <col width="28" customWidth="1" style="57" min="3" max="3"/>
+    <col width="8" customWidth="1" style="57" min="4" max="4"/>
+    <col width="12" customWidth="1" style="57" min="5" max="5"/>
+    <col width="10" customWidth="1" style="57" min="6" max="6"/>
+    <col width="50" customWidth="1" style="57" min="7" max="7"/>
+    <col width="20" customWidth="1" style="57" min="8" max="8"/>
+    <col width="10" customWidth="1" style="57" min="9" max="9"/>
     <col width="16" customWidth="1" style="57" min="10" max="10"/>
-    <col width="34" customWidth="1" style="57" min="11" max="11"/>
+    <col width="13" customWidth="1" style="57" min="11" max="11"/>
+    <col width="13" customWidth="1" style="57" min="12" max="12"/>
+    <col width="13" customWidth="1" style="57" min="13" max="13"/>
+    <col width="13" customWidth="1" style="57" min="14" max="14"/>
+    <col width="13" customWidth="1" style="57" min="15" max="15"/>
+    <col width="14" customWidth="1" style="57" min="16" max="16"/>
+    <col width="52" customWidth="1" style="57" min="17" max="17"/>
+    <col width="12" customWidth="1" style="57" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="57">
@@ -4918,107 +5261,113 @@
           <t>Forklift-specific fields only (universal fields live in SHARED). Pick/drop accuracy ordered lateral·depth·angle. ● = changed/added by Claude. Combine with SHARED.</t>
         </is>
       </c>
+      <c r="C1" s="64" t="n"/>
+      <c r="G1" s="64" t="n"/>
+      <c r="Q1" s="64" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="57">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>Allowed Values</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="66" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="65" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>LLM Hint</t>
         </is>
       </c>
-      <c r="H2" s="51" t="inlineStr">
+      <c r="H2" s="66" t="inlineStr">
         <is>
           <t>Matching Operator</t>
         </is>
       </c>
-      <c r="I2" s="51" t="inlineStr">
+      <c r="I2" s="66" t="inlineStr">
         <is>
           <t>Scoring Weight</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="66" t="inlineStr">
         <is>
           <t>Score Function</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="66" t="inlineStr">
         <is>
           <t>Score Threshold A</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="66" t="inlineStr">
         <is>
           <t>Score Threshold B</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="66" t="inlineStr">
         <is>
           <t>Plausibility Min</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="66" t="inlineStr">
         <is>
           <t>Plausibility Max</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="66" t="inlineStr">
         <is>
           <t>result_card</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="66" t="inlineStr">
         <is>
           <t>Display Mode</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="66" t="inlineStr">
         <is>
           <t>UI Hint</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="66" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="57">
+    <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="62" t="inlineStr">
         <is>
           <t>── MAST &amp; LIFTING</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="33.75" customHeight="1" s="57">
+      <c r="C3" s="64" t="n"/>
+      <c r="G3" s="64" t="n"/>
+      <c r="Q3" s="64" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>lifting_height_mm</t>
@@ -5029,7 +5378,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C4" s="24" t="n"/>
+      <c r="C4" s="67" t="n"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>m</t>
@@ -5045,7 +5394,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="68" t="inlineStr">
         <is>
           <t>AGV fork lift height in METERS — the height the forks travel, NOT building height, rack height or storage height. Source: 'Hubhöhe / lift height / fork height' in the AGV specification. If only building or rack height is stated → null. NULL RULE: null unless the document explicitly states a required AGV lift height as a technical specification with its own value and unit. Do NOT confuse with transfer station height, conveyor height, rack height, or building height — these are site dimensions, not AGV specifications. Do NOT compute, derive, or estimate the lift height from any other stated quantity — pallet height, stack height, number of storage levels, or rack capacity are design inputs, not AGV lift specifications. A lift height obtained by calculation rather than read directly from an AGV specification has no source sentence and must be output as null.</t>
         </is>
@@ -5064,13 +5413,18 @@
       <c r="O4" t="b">
         <v>1</v>
       </c>
+      <c r="Q4" s="64" t="inlineStr">
+        <is>
+          <t>Bis zu welcher Höhe muss das Gerät Lasten anheben? Maximale Entnahmehöhe im Regal angeben (mm; z. B. 10.000 mm = 10 m für Hochregal).</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>fe2f41c5-b630-4b4f-b6e7-2388eded0882</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="33.75" customHeight="1" s="57">
+    <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>min_total_height_mm</t>
@@ -5081,7 +5435,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n"/>
+      <c r="C5" s="69" t="n"/>
       <c r="D5" t="inlineStr">
         <is>
           <t>mm</t>
@@ -5097,7 +5451,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="70" t="inlineStr">
         <is>
           <t>Lowest overall vehicle height (mast collapsed). Source: dimensions. Cond. K.O.: binds where doors/sprinklers/mezzanines limit clearance.</t>
         </is>
@@ -5113,13 +5467,18 @@
       <c r="N5" t="n">
         <v>5000</v>
       </c>
+      <c r="Q5" s="64" t="inlineStr">
+        <is>
+          <t>Wie hoch sind die niedrigsten Durchfahrten oder Türen im Betriebsbereich? (mm)</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>c5ed2418-76d6-4065-84b6-0f6204353a0a</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="33.75" customHeight="1" s="57">
+    <row r="6" ht="15" customHeight="1" s="57">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>special_fork_option</t>
@@ -5130,7 +5489,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>Telescopic | Side-Shift | Clamp</t>
         </is>
@@ -5145,7 +5504,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="68" t="inlineStr">
         <is>
           <t>Non-standard fork or attachment type required by the tender. NULL RULE — READ FIRST: null by default. Only output a value if the tender document EXPLICITLY names a non-standard attachment type — i.e. 'telescopic forks', 'side-shift', or 'clamp'. Standard forks are the default for all forklifts and must NOT be extracted as a requirement. Rotating forks are the default for VNA/narrow-aisle turret trucks and are resolved from the vehicle classification, not from this field. If the document does not explicitly name Telescopic, Side-Shift, or Clamp — output null. A null value never disqualifies any supplier; a wrong value eliminates qualified suppliers.</t>
         </is>
@@ -5155,13 +5514,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q6" s="64" t="inlineStr">
+        <is>
+          <t>Wird eine spezielle Gabelausführung benötigt? (z. B. Seitenschieber, Klammergreifer)</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>39d6919b-5de1-465e-949e-c63f0adc1ad6</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="33.75" customHeight="1" s="57">
+    <row r="7" ht="15" customHeight="1" s="57">
       <c r="A7" s="19" t="inlineStr">
         <is>
           <t>fork_spread</t>
@@ -5172,7 +5536,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="69" t="inlineStr">
         <is>
           <t>None | Manual | Auto</t>
         </is>
@@ -5187,7 +5551,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="70" t="inlineStr">
         <is>
           <t>Can fork width adjust to different pallet widths, and how? Source: 'fork adjustment / auto fork width'. Cond. K.O.: 'Auto' becomes required only when the buyer runs mixed pallet widths.</t>
         </is>
@@ -5197,13 +5561,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q7" s="64" t="inlineStr">
+        <is>
+          <t>Welcher Gabelabstand ist für die Ladungsträger erforderlich? (mm)</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>74521426-7c35-4c9b-8141-48d5ef9d7b1b</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="33.75" customHeight="1" s="57">
+    <row r="8" ht="15" customHeight="1" s="57">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>mast_type</t>
@@ -5214,7 +5583,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C8" s="24" t="inlineStr">
+      <c r="C8" s="67" t="inlineStr">
         <is>
           <t>Simplex | Duplex | Triplex | Quadruplex</t>
         </is>
@@ -5229,18 +5598,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G8" s="68" t="inlineStr">
         <is>
           <t>Mast stage count. Source: spec. Per your note: does not gate execution — kept as Context.</t>
         </is>
       </c>
+      <c r="Q8" s="64" t="inlineStr">
+        <is>
+          <t>Welcher Masttyp ist vorgesehen? (z. B. Duplex, Triplex, Vierstufig)</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>4d63ba57-5e22-4517-bbc6-7f28432203be</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="33.75" customHeight="1" s="57">
+    <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="19" t="inlineStr">
         <is>
           <t>min_aisle_width_mm</t>
@@ -5251,7 +5625,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C9" s="28" t="n"/>
+      <c r="C9" s="69" t="n"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>m</t>
@@ -5267,7 +5641,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="70" t="inlineStr">
         <is>
           <t>Minimum working aisle width available in the facility, in METERS. ONLY extract if the document explicitly states an aisle, corridor, or rack-to-rack width. Source terms: 'Gangbreite', 'aisle width', 'working aisle', 'corridor width'. If no explicit width is stated anywhere in the document → output null. Do NOT infer or estimate a width from the warehouse type, the forklift category, or any typical or standard value — absence of a stated width means null, never a guess. If the figure is given in mm, divide by 1000. Do NOT confuse aisle width with lift height, rack height, vehicle height, or transfer-station height.</t>
         </is>
@@ -5286,13 +5660,18 @@
       <c r="O9" t="b">
         <v>1</v>
       </c>
+      <c r="Q9" s="64" t="inlineStr">
+        <is>
+          <t>Wie breit sind die schmalsten Fahrwege in Ihrer Anlage? Das AGV muss in dieser Gangbreite fahren können (mm).</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>efb0b0c7-e938-4d5a-8c2d-d31282da22a0</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="33.75" customHeight="1" s="57">
+    <row r="10" ht="15" customHeight="1" s="57">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>vna_capable</t>
@@ -5303,7 +5682,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C10" s="24" t="n"/>
+      <c r="C10" s="67" t="n"/>
       <c r="E10" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -5314,7 +5693,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="68" t="inlineStr">
         <is>
           <t>VNA / very narrow aisle operation required. true/false. Source: 'VNA', aisle &lt; 2 m with high-bay racking. If true, required_drive_type must be 'VNA Turret'.</t>
         </is>
@@ -5329,20 +5708,28 @@
           <t>display</t>
         </is>
       </c>
+      <c r="Q10" s="64" t="inlineStr">
+        <is>
+          <t>Ist VNA-Fähigkeit (Schmalgangbetrieb) erforderlich — oder explizit nicht gewünscht?</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>ccf99b97-919c-474f-94c8-6e46eba7360d</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="57">
+    <row r="11" ht="15" customHeight="1" s="57">
       <c r="A11" s="62" t="inlineStr">
         <is>
           <t>── DRIVE</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="33.75" customHeight="1" s="57">
+      <c r="C11" s="64" t="n"/>
+      <c r="G11" s="64" t="n"/>
+      <c r="Q11" s="64" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="57">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>drive_type</t>
@@ -5353,7 +5740,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C12" s="24" t="inlineStr">
+      <c r="C12" s="67" t="inlineStr">
         <is>
           <t>Counterbalanced | Reach Truck | Straddle Stacker | Pallet Mover | VNA Turret</t>
         </is>
@@ -5368,7 +5755,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="68" t="inlineStr">
         <is>
           <t>Forklift drive category — describes the physical build of the forklift mechanism. There are five types:
 - Counterbalanced (Gegengewichtsstapler): rear counterweight, no front support legs, forks fully exposed. Can pick pallets directly from the floor and mate with closed conveyors. Wide aisles (≥3 m).
@@ -5380,20 +5767,28 @@
         </is>
       </c>
       <c r="H12" s="52" t="n"/>
+      <c r="Q12" s="64" t="inlineStr">
+        <is>
+          <t>Welcher Antriebstyp ist vorgesehen? (z. B. Gegengewichtstapler, Schubmast, VNA)</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>b74a9cab-fb2e-4a93-ac33-fe6b0bbd1c1a</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="15.75" customHeight="1" s="57">
+    <row r="13" ht="15" customHeight="1" s="57">
       <c r="A13" s="62" t="inlineStr">
         <is>
           <t>── PICK &amp; DROP (order: lateral · depth · angle)</t>
         </is>
       </c>
-    </row>
-    <row r="14" ht="33.75" customHeight="1" s="57">
+      <c r="C13" s="64" t="n"/>
+      <c r="G13" s="64" t="n"/>
+      <c r="Q13" s="64" t="n"/>
+    </row>
+    <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="16" t="inlineStr">
         <is>
           <t>drop_accuracy_lat_mm</t>
@@ -5404,7 +5799,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C14" s="24" t="n"/>
+      <c r="C14" s="67" t="n"/>
       <c r="D14" t="inlineStr">
         <is>
           <t>mm</t>
@@ -5420,7 +5815,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G14" s="18" t="inlineStr">
+      <c r="G14" s="68" t="inlineStr">
         <is>
           <t>Placement accuracy LATERALLY (sideways) at drop. Source: 'positioning accuracy' or sales. Drives rack-opening tolerance; tighter = denser racking, higher score.</t>
         </is>
@@ -5436,13 +5831,18 @@
       <c r="K14" t="n">
         <v>20</v>
       </c>
+      <c r="Q14" s="64" t="inlineStr">
+        <is>
+          <t>Wie präzise muss das AMR Lasten seitlich absetzen? (mm laterale Abweichung)</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>c9dcda6f-50ac-4e87-8d66-bec0cd0f05ce</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="33.75" customHeight="1" s="57">
+    <row r="15" ht="15" customHeight="1" s="57">
       <c r="A15" s="19" t="inlineStr">
         <is>
           <t>drop_accuracy_dep_mm</t>
@@ -5453,7 +5853,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C15" s="28" t="n"/>
+      <c r="C15" s="69" t="n"/>
       <c r="D15" t="inlineStr">
         <is>
           <t>mm</t>
@@ -5469,18 +5869,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G15" s="21" t="inlineStr">
+      <c r="G15" s="70" t="inlineStr">
         <is>
           <t>Placement accuracy in DEPTH at drop. Source: as above. Tighter = less damage &amp; denser storage. (reordered to lat·dep·angle)</t>
         </is>
       </c>
+      <c r="Q15" s="64" t="inlineStr">
+        <is>
+          <t>Wie präzise muss das AMR Lasten in der Tiefe absetzen? (mm)</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>443cf07f-782f-4c66-bb81-15ba033ffc69</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="33.75" customHeight="1" s="57">
+    <row r="16" ht="15" customHeight="1" s="57">
       <c r="A16" s="16" t="inlineStr">
         <is>
           <t>drop_accuracy_angle_deg</t>
@@ -5491,7 +5896,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C16" s="24" t="n"/>
+      <c r="C16" s="67" t="n"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>°</t>
@@ -5507,18 +5912,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G16" s="18" t="inlineStr">
+      <c r="G16" s="68" t="inlineStr">
         <is>
           <t>Angular placement accuracy at drop. Source: as above. Skew tolerance for conveyor/rack hand-off.</t>
         </is>
       </c>
+      <c r="Q16" s="64" t="inlineStr">
+        <is>
+          <t>Wie präzise muss das AMR Lasten winkelgenau absetzen? (Grad)</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>d7b23f4b-dcfe-4396-bd8e-7954420f0d1b</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="33.75" customHeight="1" s="57">
+    <row r="17" ht="15" customHeight="1" s="57">
       <c r="A17" s="19" t="inlineStr">
         <is>
           <t>pick_req_accuracy_lat_mm</t>
@@ -5529,7 +5939,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C17" s="28" t="n"/>
+      <c r="C17" s="69" t="n"/>
       <c r="D17" t="inlineStr">
         <is>
           <t>mm</t>
@@ -5545,7 +5955,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G17" s="21" t="inlineStr">
+      <c r="G17" s="70" t="inlineStr">
         <is>
           <t>How precisely a pallet must be PRE-positioned (laterally) for the truck to pick it. Source: integration spec. Loose tolerance = forgiving of sloppy upstream placement, easier deployment.</t>
         </is>
@@ -5561,13 +5971,18 @@
       <c r="K17" t="n">
         <v>20</v>
       </c>
+      <c r="Q17" s="64" t="inlineStr">
+        <is>
+          <t>Welche seitliche Präzision ist bei der Lastaufnahme erforderlich? (mm)</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>85b7c020-0cd3-4485-8281-3b8ee605b2e2</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="33.75" customHeight="1" s="57">
+    <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="16" t="inlineStr">
         <is>
           <t>pick_req_accuracy_dep_mm</t>
@@ -5578,7 +5993,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C18" s="24" t="n"/>
+      <c r="C18" s="67" t="n"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>mm</t>
@@ -5594,18 +6009,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G18" s="18" t="inlineStr">
+      <c r="G18" s="68" t="inlineStr">
         <is>
           <t>Required pre-position accuracy in DEPTH to pick. Source: as above.</t>
         </is>
       </c>
+      <c r="Q18" s="64" t="inlineStr">
+        <is>
+          <t>Welche Tiefenpräzision ist bei der Kommissionierung erforderlich? (mm)</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>43641d9b-0424-4cc8-af67-1daa55954f8a</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="33.75" customHeight="1" s="57">
+    <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="19" t="inlineStr">
         <is>
           <t>pick_req_accuracy_angle_deg</t>
@@ -5616,7 +6036,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C19" s="28" t="n"/>
+      <c r="C19" s="69" t="n"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>°</t>
@@ -5632,25 +6052,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="70" t="inlineStr">
         <is>
           <t>Required pre-position ANGLE accuracy to pick. Source: as above. Tolerant handling reduces upstream constraints.</t>
         </is>
       </c>
+      <c r="Q19" s="64" t="inlineStr">
+        <is>
+          <t>Welche Winkelpräzision ist bei der Kommissionierung erforderlich? (Grad)</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>340057db-8dd0-4cb7-8e01-23ae7a5fe893</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="15.75" customHeight="1" s="57">
+    <row r="20" ht="15" customHeight="1" s="57">
       <c r="A20" s="62" t="inlineStr">
         <is>
           <t>── HANDLING CAPABILITY</t>
         </is>
       </c>
-    </row>
-    <row r="21" ht="33.75" customHeight="1" s="57">
+      <c r="C20" s="64" t="n"/>
+      <c r="G20" s="64" t="n"/>
+      <c r="Q20" s="64" t="n"/>
+    </row>
+    <row r="21" ht="15" customHeight="1" s="57">
       <c r="A21" s="16" t="inlineStr">
         <is>
           <t>forks_free_floating</t>
@@ -5661,7 +6089,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C21" s="24" t="n"/>
+      <c r="C21" s="67" t="n"/>
       <c r="E21" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -5672,7 +6100,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G21" s="18" t="inlineStr">
+      <c r="G21" s="68" t="inlineStr">
         <is>
           <t>Single forks with NO support legs/structure under the load (true counterbalance free-lift). Source: drive_type=Counterbalanced + 'free lift'. Required to pick closed-bottom pallets on the floor and mate with closed conveyors — straddle/reach trucks fail here. Cond. K.O.: decisive only when the buyer has closed pallets/conveyors.</t>
         </is>
@@ -5682,13 +6110,18 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="Q21" s="64" t="inlineStr">
+        <is>
+          <t>Müssen die Gabeln seitenverschiebbar oder schwimmend gelagert sein?</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>f418a304-e6d0-4cbe-9d57-f049bfbd3a17</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="33.75" customHeight="1" s="57">
+    <row r="22" ht="15" customHeight="1" s="57">
       <c r="A22" s="19" t="inlineStr">
         <is>
           <t>stacking_capability</t>
@@ -5699,7 +6132,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C22" s="28" t="n"/>
+      <c r="C22" s="69" t="n"/>
       <c r="E22" s="25" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -5710,7 +6143,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G22" s="21" t="inlineStr">
+      <c r="G22" s="70" t="inlineStr">
         <is>
           <t>Can stack &amp; de-stack pallets (vertical), vs. floor-to-floor transport only. Source: 'stacking'. Filter for storage vs. pure transport tenders.</t>
         </is>
@@ -5721,13 +6154,18 @@
         </is>
       </c>
       <c r="I22" s="50" t="n"/>
+      <c r="Q22" s="64" t="inlineStr">
+        <is>
+          <t>Muss das Gerät Lasten übereinander stapeln können?</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>dcf086e5-18d5-4023-a595-a4a9ba61cf8a</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="33.75" customHeight="1" s="57">
+    <row r="23" ht="15" customHeight="1" s="57">
       <c r="A23" s="16" t="inlineStr">
         <is>
           <t>load_detection</t>
@@ -5738,7 +6176,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C23" s="24" t="inlineStr">
+      <c r="C23" s="67" t="inlineStr">
         <is>
           <t>None | Camera/Vision | Laser/LiDAR profiling | RFID | Barcode/DataMatrix | Mechanical/Tactile | Predefined coordinates | Other</t>
         </is>
@@ -5753,18 +6191,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G23" s="18" t="inlineStr">
+      <c r="G23" s="68" t="inlineStr">
         <is>
           <t>How the truck identifies/verifies the pallet &amp; target slot before handling. Source: 'load / pallet detection / vision'. Better detection tolerates imperfect placement &amp; prevents mis-picks.</t>
         </is>
       </c>
+      <c r="Q23" s="64" t="inlineStr">
+        <is>
+          <t>Wie soll die Lastaufnahme erkannt werden?</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>ba89e614-9c33-4ff2-a555-e85945b78ac4</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="33.75" customHeight="1" s="57">
+    <row r="24" ht="15" customHeight="1" s="57">
       <c r="A24" s="19" t="inlineStr">
         <is>
           <t>barcode_readers</t>
@@ -5775,7 +6218,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C24" s="28" t="n"/>
+      <c r="C24" s="69" t="n"/>
       <c r="E24" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -5786,7 +6229,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G24" s="21" t="inlineStr">
+      <c r="G24" s="70" t="inlineStr">
         <is>
           <t>Reads barcodes/DataMatrix and acts on the data (confirm SKU/location). Source: 'barcode / scanning'. Cond. K.O.: hard requirement when the buyer explicitly demands barcode verification; otherwise scores as an enhancement. (template case for Cond. K.O.)</t>
         </is>
@@ -5796,13 +6239,18 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="Q24" s="64" t="inlineStr">
+        <is>
+          <t>Sind integrierte Barcode-Scanner für die Lastidentifikation erforderlich?</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>400f837a-ef34-4c65-bb37-acb8b21fafc9</t>
         </is>
       </c>
     </row>
-    <row r="25" ht="33.75" customHeight="1" s="57">
+    <row r="25" ht="15" customHeight="1" s="57">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>stock_line_scanning</t>
@@ -5813,7 +6261,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C25" s="24" t="n"/>
+      <c r="C25" s="67" t="n"/>
       <c r="E25" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -5824,25 +6272,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G25" s="18" t="inlineStr">
+      <c r="G25" s="68" t="inlineStr">
         <is>
           <t>Scans a storage line to auto-find the next free slot or next pallet to pick. Source: 'inventory scanning / slotting'. Enables autonomous put-away/retrieval logic.</t>
         </is>
       </c>
+      <c r="Q25" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AGV Bestände im Regal automatisch scannen können?</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>d0bda96d-6948-4b20-a16a-3a0e3537fc0a</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="15.75" customHeight="1" s="57">
+    <row r="26" ht="15" customHeight="1" s="57">
       <c r="A26" s="62" t="inlineStr">
         <is>
           <t>── TRAILER / DOCK</t>
         </is>
       </c>
-    </row>
-    <row r="27" ht="33.75" customHeight="1" s="57">
+      <c r="C26" s="64" t="n"/>
+      <c r="G26" s="64" t="n"/>
+      <c r="Q26" s="64" t="n"/>
+    </row>
+    <row r="27" ht="15" customHeight="1" s="57">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>trailer_loading</t>
@@ -5853,7 +6309,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C27" s="24" t="n"/>
+      <c r="C27" s="67" t="n"/>
       <c r="E27" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -5864,7 +6320,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G27" s="68" t="inlineStr">
         <is>
           <t>Autonomously LOADS trailers/trucks at the dock. Source: 'automatic truck loading'. Cond. K.O.: decisive only for dock-automation tenders.</t>
         </is>
@@ -5874,13 +6330,18 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="Q27" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AGV Lasten in Lkw-Trailer einfahren und beladen können?</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>ca8a2e5f-ebf1-49dd-a41c-3ccf270fbb73</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="33.75" customHeight="1" s="57">
+    <row r="28" ht="15" customHeight="1" s="57">
       <c r="A28" s="19" t="inlineStr">
         <is>
           <t>trailer_unloading</t>
@@ -5891,7 +6352,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C28" s="28" t="n"/>
+      <c r="C28" s="69" t="n"/>
       <c r="E28" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -5902,7 +6363,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="70" t="inlineStr">
         <is>
           <t>Autonomously UNLOADS trailers/trucks. Source: same. Cond. K.O.: decisive only for dock-automation tenders.</t>
         </is>
@@ -5912,20 +6373,28 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="Q28" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AGV Lasten aus Lkw-Trailern entnehmen können?</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>94438838-9fb6-46e2-ba04-1d31b6ac40aa</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="15.75" customHeight="1" s="57">
+    <row r="29" ht="15" customHeight="1" s="57">
       <c r="A29" s="62" t="inlineStr">
         <is>
           <t>── AGV (RAIL/WIRE) ONLY</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="33.75" customHeight="1" s="57">
+      <c r="C29" s="64" t="n"/>
+      <c r="G29" s="64" t="n"/>
+      <c r="Q29" s="64" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="57">
       <c r="A30" s="16" t="inlineStr">
         <is>
           <t>guidance</t>
@@ -5936,7 +6405,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C30" s="24" t="inlineStr">
+      <c r="C30" s="67" t="inlineStr">
         <is>
           <t>None | Rail | Wire</t>
         </is>
@@ -5951,7 +6420,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G30" s="18" t="inlineStr">
+      <c r="G30" s="68" t="inlineStr">
         <is>
           <t>Physical guidance for rail/wire-guided VNA trucks (distinct from free-nav AGVs). Source: VNA spec. 'None' for free-roaming units.</t>
         </is>
@@ -5961,13 +6430,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q30" s="64" t="inlineStr">
+        <is>
+          <t>Welches Führungskonzept soll das Regalfahrzeug im VNA-Bereich nutzen?</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>e2205c93-10d2-45ce-af50-86c300a56b82</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="33.75" customHeight="1" s="57">
+    <row r="31" ht="15" customHeight="1" s="57">
       <c r="A31" s="19" t="inlineStr">
         <is>
           <t>busbar_compatible</t>
@@ -5978,7 +6452,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C31" s="28" t="n"/>
+      <c r="C31" s="69" t="n"/>
       <c r="E31" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -5989,9 +6463,14 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="70" t="inlineStr">
         <is>
           <t>Draws power / charges via in-aisle busbar instead of battery cycling. Source: VNA power spec. Enables continuous high-duty VNA operation.</t>
+        </is>
+      </c>
+      <c r="Q31" s="64" t="inlineStr">
+        <is>
+          <t>Ist ein Stromversorgungssystem über Schienenschleifer (Busbar) vorgesehen?</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -6024,16 +6503,24 @@
   <dimension ref="A1:R20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="57" min="1" max="1"/>
-    <col width="13" customWidth="1" style="57" min="2" max="2"/>
-    <col width="30" customWidth="1" style="57" min="3" max="3"/>
-    <col width="10" customWidth="1" style="57" min="4" max="4"/>
-    <col width="13" customWidth="1" style="57" min="5" max="5"/>
-    <col width="7" customWidth="1" style="57" min="6" max="6"/>
-    <col width="60" customWidth="1" style="57" min="7" max="7"/>
-    <col width="56.1640625" customWidth="1" style="57" min="8" max="8"/>
+    <col width="30" customWidth="1" style="57" min="1" max="1"/>
+    <col width="14" customWidth="1" style="57" min="2" max="2"/>
+    <col width="28" customWidth="1" style="57" min="3" max="3"/>
+    <col width="8" customWidth="1" style="57" min="4" max="4"/>
+    <col width="12" customWidth="1" style="57" min="5" max="5"/>
+    <col width="10" customWidth="1" style="57" min="6" max="6"/>
+    <col width="50" customWidth="1" style="57" min="7" max="7"/>
+    <col width="20" customWidth="1" style="57" min="8" max="8"/>
+    <col width="10" customWidth="1" style="57" min="9" max="9"/>
     <col width="16" customWidth="1" style="57" min="10" max="10"/>
-    <col width="34" customWidth="1" style="57" min="11" max="11"/>
+    <col width="13" customWidth="1" style="57" min="11" max="11"/>
+    <col width="13" customWidth="1" style="57" min="12" max="12"/>
+    <col width="13" customWidth="1" style="57" min="13" max="13"/>
+    <col width="13" customWidth="1" style="57" min="14" max="14"/>
+    <col width="13" customWidth="1" style="57" min="15" max="15"/>
+    <col width="14" customWidth="1" style="57" min="16" max="16"/>
+    <col width="52" customWidth="1" style="57" min="17" max="17"/>
+    <col width="12" customWidth="1" style="57" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="57">
@@ -6042,107 +6529,113 @@
           <t>Tugger-specific fields, deepened from Vecna / DS Automotion / LKE research — trailer compatibility &amp; steering tech, aisle width, turning radius, auto-hitch + tolerance. ● = added by Claude. Combine with SHARED. v0.7: auto_hitch → Cond. K.O.; tugger_min_aisle_width_mm added.</t>
         </is>
       </c>
+      <c r="C1" s="64" t="n"/>
+      <c r="G1" s="64" t="n"/>
+      <c r="Q1" s="64" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="57">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>Allowed Values</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="66" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="65" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>LLM Hint</t>
         </is>
       </c>
-      <c r="H2" s="51" t="inlineStr">
+      <c r="H2" s="66" t="inlineStr">
         <is>
           <t>Matching Operator</t>
         </is>
       </c>
-      <c r="I2" s="51" t="inlineStr">
+      <c r="I2" s="66" t="inlineStr">
         <is>
           <t>Scoring Weight</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="66" t="inlineStr">
         <is>
           <t>Score Function</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="66" t="inlineStr">
         <is>
           <t>Score Threshold A</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="66" t="inlineStr">
         <is>
           <t>Score Threshold B</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="66" t="inlineStr">
         <is>
           <t>Plausibility Min</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="66" t="inlineStr">
         <is>
           <t>Plausibility Max</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="66" t="inlineStr">
         <is>
           <t>result_card</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="66" t="inlineStr">
         <is>
           <t>Display Mode</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="66" t="inlineStr">
         <is>
           <t>UI Hint</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="66" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="57">
+    <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="62" t="inlineStr">
         <is>
           <t>── TOWING</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="33.75" customHeight="1" s="57">
+      <c r="C3" s="64" t="n"/>
+      <c r="G3" s="64" t="n"/>
+      <c r="Q3" s="64" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>towing_capacity_kg</t>
@@ -6153,7 +6646,7 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="C4" s="24" t="n"/>
+      <c r="C4" s="67" t="n"/>
       <c r="D4" t="inlineStr">
         <is>
           <t>kg</t>
@@ -6169,7 +6662,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="68" t="inlineStr">
         <is>
           <t>Total towed load in kg. [TUGGER ONLY] — output null unless required_agv_type is 'Tugger AGV'. Source: 'Schleppkraft / towing capacity'.</t>
         </is>
@@ -6185,13 +6678,18 @@
       <c r="N4" t="n">
         <v>100000</v>
       </c>
+      <c r="Q4" s="64" t="inlineStr">
+        <is>
+          <t>Wie hoch ist das maximale Gesamtgewicht des Anhängerzuges? (kg; Summe aller Anhänger inkl. Ladung)</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>730de80f-ba52-44bf-bfb8-dc72b2b701c3</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="33.75" customHeight="1" s="57">
+    <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>max_trailers</t>
@@ -6202,7 +6700,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n"/>
+      <c r="C5" s="69" t="n"/>
       <c r="D5" t="inlineStr">
         <is>
           <t># trailers</t>
@@ -6218,7 +6716,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="70" t="inlineStr">
         <is>
           <t>Number of trailers per train. [TUGGER ONLY] null for other vehicle types.</t>
         </is>
@@ -6234,13 +6732,18 @@
       <c r="N5" t="n">
         <v>50</v>
       </c>
+      <c r="Q5" s="64" t="inlineStr">
+        <is>
+          <t>Wie viele Anhänger müssen gleichzeitig gezogen werden können?</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>c34f69c9-4cb7-4df1-9fe0-d2afb5dde2ba</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="33.75" customHeight="1" s="57">
+    <row r="6" ht="15" customHeight="1" s="57">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>coupling_type</t>
@@ -6251,7 +6754,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C6" s="24" t="inlineStr">
+      <c r="C6" s="67" t="inlineStr">
         <is>
           <t>Automatic | Manual | Pintle Hook | Towbar</t>
         </is>
@@ -6266,7 +6769,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="68" t="inlineStr">
         <is>
           <t>Trailer attachment method. Output from allowed values only, comma-separated if multiple. null = not stated. NULL RULE: output null unless the tender explicitly names a coupling method. Do NOT default to 'Automatic' or infer from 'auto_hitch'.</t>
         </is>
@@ -6276,13 +6779,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q6" s="64" t="inlineStr">
+        <is>
+          <t>Welche Kupplungsart verwenden die vorhandenen oder geplanten Anhänger?</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>2a06e565-eb70-44e8-b362-bd057cfd9a7a</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="33.75" customHeight="1" s="57">
+    <row r="7" ht="15" customHeight="1" s="57">
       <c r="A7" s="19" t="inlineStr">
         <is>
           <t>auto_hitch</t>
@@ -6293,7 +6801,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C7" s="28" t="n"/>
+      <c r="C7" s="69" t="n"/>
       <c r="E7" s="48" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -6304,7 +6812,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="70" t="inlineStr">
         <is>
           <t>Automatic trailer coupling without manual intervention. true/false. [TUGGER ONLY] null for other vehicle types.</t>
         </is>
@@ -6322,13 +6830,18 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="Q7" s="64" t="inlineStr">
+        <is>
+          <t>Muss der Tugger Anhänger automatisch ankuppeln können?</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>745ac03b-c39f-4ce3-af99-d7e3e19343ae</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="33.75" customHeight="1" s="57">
+    <row r="8" ht="15" customHeight="1" s="57">
       <c r="A8" s="16" t="inlineStr">
         <is>
           <t>auto_hitch_position_tolerance_mm</t>
@@ -6339,7 +6852,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C8" s="24" t="n"/>
+      <c r="C8" s="67" t="n"/>
       <c r="D8" t="inlineStr">
         <is>
           <t>mm</t>
@@ -6355,18 +6868,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G8" s="18" t="inlineStr">
+      <c r="G8" s="68" t="inlineStr">
         <is>
           <t>How far a cart may be mis-parked and still be auto-hitched. Source: rarely published — ask supplier (mechanism: the tugger approaches the cart and the hitch self-engages within a capture window; wider window = more forgiving of human cart placement). Larger tolerance = easier real-world operation.</t>
         </is>
       </c>
+      <c r="Q8" s="64" t="inlineStr">
+        <is>
+          <t>Welche Positioniertoleranz ist beim automatischen Ankuppeln akzeptabel? (mm)</t>
+        </is>
+      </c>
       <c r="R8" t="inlineStr">
         <is>
           <t>77406f3e-7a53-48f6-80c1-3384598edc35</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="33.75" customHeight="1" s="57">
+    <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="19" t="inlineStr">
         <is>
           <t>train_configuration</t>
@@ -6377,7 +6895,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C9" s="28" t="inlineStr">
+      <c r="C9" s="69" t="inlineStr">
         <is>
           <t>B-frame | C-frame | Underride/Mouse | Tugger + trailers</t>
         </is>
@@ -6392,18 +6910,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G9" s="21" t="inlineStr">
+      <c r="G9" s="70" t="inlineStr">
         <is>
           <t>Mechanical train concept. Source: product family (e.g. STILL LiftRunner B-/C-frame). Implies load/unload ergonomics &amp; which trolleys fit.</t>
         </is>
       </c>
+      <c r="Q9" s="64" t="inlineStr">
+        <is>
+          <t>Welche Zuganordnung ist vorgesehen? (z. B. Anhänger in Reihe, Karussellanordnung)</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>ec8bb86e-40a5-4d69-8c57-7c6dd38b43af</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="33.75" customHeight="1" s="57">
+    <row r="10" ht="15" customHeight="1" s="57">
       <c r="A10" s="16" t="inlineStr">
         <is>
           <t>load_transfer</t>
@@ -6414,7 +6937,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C10" s="24" t="inlineStr">
+      <c r="C10" s="67" t="inlineStr">
         <is>
           <t>Manual | Automatic roller | Lift | Pull-out frame</t>
         </is>
@@ -6429,25 +6952,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G10" s="18" t="inlineStr">
+      <c r="G10" s="68" t="inlineStr">
         <is>
           <t>How load moves on/off trailers at stations. Source: 'automatic load transfer'. Automatic transfer removes the last manual touch.</t>
         </is>
       </c>
+      <c r="Q10" s="64" t="inlineStr">
+        <is>
+          <t>Wie soll die Lastübergabe am Anhänger erfolgen?</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>9d0f802b-7041-4343-858e-e0ac14b0fac6</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="15.75" customHeight="1" s="57">
+    <row r="11" ht="15" customHeight="1" s="57">
       <c r="A11" s="62" t="inlineStr">
         <is>
           <t>── TRAILER / CART</t>
         </is>
       </c>
-    </row>
-    <row r="12" ht="33.75" customHeight="1" s="57">
+      <c r="C11" s="64" t="n"/>
+      <c r="G11" s="64" t="n"/>
+      <c r="Q11" s="64" t="n"/>
+    </row>
+    <row r="12" ht="15" customHeight="1" s="57">
       <c r="A12" s="16" t="inlineStr">
         <is>
           <t>trailer_compatibility</t>
@@ -6458,7 +6989,7 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="C12" s="24" t="n"/>
+      <c r="C12" s="67" t="n"/>
       <c r="E12" s="31" t="inlineStr">
         <is>
           <t>Context</t>
@@ -6469,18 +7000,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G12" s="18" t="inlineStr">
+      <c r="G12" s="68" t="inlineStr">
         <is>
           <t>Which trailer/cart makes &amp; models the tugger is qualified to pull (e.g. K.Hartwall, STILL LiftRunner, LKE, FlexQube, in-house carts). Source: 'compatible carts / partners' or reference photos. Tells the buyer whether existing carts can be reused.</t>
         </is>
       </c>
+      <c r="Q12" s="64" t="inlineStr">
+        <is>
+          <t>Welche Anhängertypen sollen verwendet werden?</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>8609905f-24b8-4eea-8005-e7b4893ef261</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33.75" customHeight="1" s="57">
+    <row r="13" ht="15" customHeight="1" s="57">
       <c r="A13" s="19" t="inlineStr">
         <is>
           <t>trailer_steering_technology</t>
@@ -6491,7 +7027,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C13" s="28" t="inlineStr">
+      <c r="C13" s="69" t="inlineStr">
         <is>
           <t>Passive caster | Dual-steer | Center-steer | Quad-steer (all-wheel) | Tracking drawbar / virtual coupling | Forced/positive axle steer | Manual only</t>
         </is>
@@ -6506,7 +7042,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G13" s="21" t="inlineStr">
+      <c r="G13" s="70" t="inlineStr">
         <is>
           <t>How the pulled trailers steer/track. Source: cart datasheet. Self-steering tiers (quad-steer, tracking drawbar/virtual coupling, forced axle steer) follow the tugger's exact path with little 'snaking' → tighter aisles &amp; safer; passive caster carts off-track more and may need wider aisles; 'Manual only' = no tracking aid. Better tracking = higher score and narrower aisle need.</t>
         </is>
@@ -6519,20 +7055,28 @@
           <t>nonempty</t>
         </is>
       </c>
+      <c r="Q13" s="64" t="inlineStr">
+        <is>
+          <t>Welche Lenktechnologie verwenden die Anhänger? (z. B. passive Lenkung, aktive Lenkung)</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>c6bfa5fc-0307-4230-b575-78291116d28a</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="15.75" customHeight="1" s="57">
+    <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="62" t="inlineStr">
         <is>
           <t>── ROUTING &amp; MANEUVERING</t>
         </is>
       </c>
-    </row>
-    <row r="15" ht="33.75" customHeight="1" s="57">
+      <c r="C14" s="64" t="n"/>
+      <c r="G14" s="64" t="n"/>
+      <c r="Q14" s="64" t="n"/>
+    </row>
+    <row r="15" ht="15" customHeight="1" s="57">
       <c r="A15" s="16" t="inlineStr">
         <is>
           <t>route_type</t>
@@ -6543,7 +7087,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C15" s="24" t="inlineStr">
+      <c r="C15" s="67" t="inlineStr">
         <is>
           <t>Fixed Route | Flexible Route | Fully Dynamic</t>
         </is>
@@ -6558,7 +7102,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G15" s="18" t="inlineStr">
+      <c r="G15" s="68" t="inlineStr">
         <is>
           <t>Routing mode. Output exactly one allowed value. Fixed Route = predefined milk-run loop; Flexible Route = semi-dynamic; Fully Dynamic = on-demand point-to-point.</t>
         </is>
@@ -6568,13 +7112,18 @@
           <t>KO_IF_NEQ</t>
         </is>
       </c>
+      <c r="Q15" s="64" t="inlineStr">
+        <is>
+          <t>Welche Art von Fahrstrecke ist geplant? (feste Route oder flexible Route)</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>9ff0e3bc-521b-4dc9-b7e8-9350ced25969</t>
         </is>
       </c>
     </row>
-    <row r="16" ht="33.75" customHeight="1" s="57">
+    <row r="16" ht="15" customHeight="1" s="57">
       <c r="A16" s="19" t="inlineStr">
         <is>
           <t>route_programming</t>
@@ -6585,7 +7134,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C16" s="28" t="inlineStr">
+      <c r="C16" s="69" t="inlineStr">
         <is>
           <t>Teach-in | Map-based | Mixed</t>
         </is>
@@ -6600,18 +7149,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="70" t="inlineStr">
         <is>
           <t>How routes are created/edited. Source: 'teach-in / mapping'. Map-based + client-editable = cheap to change (ties to modification_process).</t>
         </is>
       </c>
+      <c r="Q16" s="64" t="inlineStr">
+        <is>
+          <t>Wie sollen Fahrrouten programmiert oder angepasst werden?</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>f636b9aa-947c-4df0-b406-03a34a5eac71</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="33.75" customHeight="1" s="57">
+    <row r="17" ht="15" customHeight="1" s="57">
       <c r="A17" s="16" t="inlineStr">
         <is>
           <t>intersection_management</t>
@@ -6622,7 +7176,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C17" s="24" t="n"/>
+      <c r="C17" s="67" t="n"/>
       <c r="E17" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -6633,18 +7187,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G17" s="18" t="inlineStr">
+      <c r="G17" s="68" t="inlineStr">
         <is>
           <t>Autonomous negotiation of crossings/merges with other traffic. Source: 'traffic management'. Implies throughput &amp; safety in shared corridors.</t>
         </is>
       </c>
+      <c r="Q17" s="64" t="inlineStr">
+        <is>
+          <t>Wie sollen Kreuzungssituationen zwischen mehreren AGVs gehandhabt werden?</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>9fb72751-a4de-4468-b406-372f7a5bb2e8</t>
         </is>
       </c>
     </row>
-    <row r="18" ht="33.75" customHeight="1" s="57">
+    <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="19" t="inlineStr">
         <is>
           <t>min_aisle_width_mm</t>
@@ -6655,7 +7214,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C18" s="28" t="n"/>
+      <c r="C18" s="69" t="n"/>
       <c r="D18" t="inlineStr">
         <is>
           <t>m</t>
@@ -6671,7 +7230,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G18" s="21" t="inlineStr">
+      <c r="G18" s="70" t="inlineStr">
         <is>
           <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If doc states mm (e.g. 2700 mm) → divide by 1000 → 2.7. Hard filter; decisive for VNA. WARNING: Do NOT confuse aisle width with other dimensions. Source terms: 'Gangbreite', 'aisle width', 'working aisle'. If no explicit aisle width is stated → output null.</t>
         </is>
@@ -6687,13 +7246,18 @@
       <c r="N18" t="n">
         <v>5</v>
       </c>
+      <c r="Q18" s="64" t="inlineStr">
+        <is>
+          <t>Wie breit sind die schmalsten Fahrwege in Ihrer Anlage? Das AGV muss in dieser Gangbreite fahren können (mm).</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>1fbf91de-a1fc-4512-bc80-92c44c11c9b4</t>
         </is>
       </c>
     </row>
-    <row r="19" ht="33.75" customHeight="1" s="57">
+    <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="16" t="inlineStr">
         <is>
           <t>turning_radius_mm</t>
@@ -6704,7 +7268,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C19" s="24" t="n"/>
+      <c r="C19" s="67" t="n"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>mm</t>
@@ -6720,7 +7284,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G19" s="18" t="inlineStr">
+      <c r="G19" s="68" t="inlineStr">
         <is>
           <t>Tugger turning radius (tractor alone). Source: spec 'turning radius' (e.g. Vecna ATG ≈ 2,900 mm / 9'6"). Hard filter for tight bends &amp; dock turns.</t>
         </is>
@@ -6736,13 +7300,18 @@
       <c r="N19" t="n">
         <v>20000</v>
       </c>
+      <c r="Q19" s="64" t="inlineStr">
+        <is>
+          <t>Wie viel Platz steht in Kurven zur Verfügung? (mm; der Wenderadius des Fahrzeugs muss kleiner sein)</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>7664d132-1de2-4f01-8a99-013968f58919</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="409.6" customHeight="1" s="57">
+    <row r="20" ht="15" customHeight="1" s="57">
       <c r="A20" s="39" t="inlineStr">
         <is>
           <t>tugger_min_aisle_width_mm</t>
@@ -6753,7 +7322,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C20" s="39" t="n"/>
+      <c r="C20" s="71" t="n"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>m</t>
@@ -6769,7 +7338,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G20" s="42" t="inlineStr">
+      <c r="G20" s="71" t="inlineStr">
         <is>
           <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If doc states mm (e.g. 2700 mm) → divide by 1000 → 2.7. Hard filter; decisive for VNA.</t>
         </is>
@@ -6784,6 +7353,11 @@
       </c>
       <c r="N20" t="n">
         <v>5</v>
+      </c>
+      <c r="Q20" s="64" t="inlineStr">
+        <is>
+          <t>Wie breit sind die schmalsten Durchfahrten im gesamten Fahrtbereich des Tuggers inkl. Anhänger? (mm)</t>
+        </is>
       </c>
       <c r="R20" t="inlineStr">
         <is>
@@ -6812,16 +7386,24 @@
   <dimension ref="A1:R44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
-    <col width="24" customWidth="1" style="57" min="1" max="1"/>
-    <col width="13" customWidth="1" style="57" min="2" max="2"/>
-    <col width="30" customWidth="1" style="57" min="3" max="3"/>
-    <col width="10" customWidth="1" style="57" min="4" max="4"/>
-    <col width="13" customWidth="1" style="57" min="5" max="5"/>
-    <col width="7" customWidth="1" style="57" min="6" max="6"/>
-    <col width="60" customWidth="1" style="57" min="7" max="7"/>
-    <col width="53.83203125" customWidth="1" style="57" min="8" max="8"/>
+    <col width="30" customWidth="1" style="57" min="1" max="1"/>
+    <col width="14" customWidth="1" style="57" min="2" max="2"/>
+    <col width="28" customWidth="1" style="57" min="3" max="3"/>
+    <col width="8" customWidth="1" style="57" min="4" max="4"/>
+    <col width="12" customWidth="1" style="57" min="5" max="5"/>
+    <col width="10" customWidth="1" style="57" min="6" max="6"/>
+    <col width="50" customWidth="1" style="57" min="7" max="7"/>
+    <col width="20" customWidth="1" style="57" min="8" max="8"/>
+    <col width="10" customWidth="1" style="57" min="9" max="9"/>
     <col width="16" customWidth="1" style="57" min="10" max="10"/>
-    <col width="34" customWidth="1" style="57" min="11" max="11"/>
+    <col width="13" customWidth="1" style="57" min="11" max="11"/>
+    <col width="13" customWidth="1" style="57" min="12" max="12"/>
+    <col width="13" customWidth="1" style="57" min="13" max="13"/>
+    <col width="13" customWidth="1" style="57" min="14" max="14"/>
+    <col width="13" customWidth="1" style="57" min="15" max="15"/>
+    <col width="14" customWidth="1" style="57" min="16" max="16"/>
+    <col width="52" customWidth="1" style="57" min="17" max="17"/>
+    <col width="12" customWidth="1" style="57" min="18" max="18"/>
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="57">
@@ -6830,107 +7412,113 @@
           <t>Unified free-navigating AMR sheet — merges the former Undercarriage + Goods-to-Person + Picking subtypes into ONE category (same hardware, different workflow). The workflow is now a PROPERTY (workflow_capability, grid_required, rotation_capable, picking_mechanism), not a hard category. Overlapping throughput fields consolidated into throughput_picks_per_hour + throughput_basis. ● = added/changed by Claude. Combine with SHARED.</t>
         </is>
       </c>
+      <c r="C1" s="64" t="n"/>
+      <c r="G1" s="64" t="n"/>
+      <c r="Q1" s="64" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="57">
-      <c r="A2" s="9" t="inlineStr">
+      <c r="A2" s="65" t="inlineStr">
         <is>
           <t>Field Name</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="65" t="inlineStr">
         <is>
           <t>Data Type</t>
         </is>
       </c>
-      <c r="C2" s="9" t="inlineStr">
+      <c r="C2" s="65" t="inlineStr">
         <is>
           <t>Allowed Values</t>
         </is>
       </c>
-      <c r="D2" t="inlineStr">
+      <c r="D2" s="66" t="inlineStr">
         <is>
           <t>Unit</t>
         </is>
       </c>
-      <c r="E2" s="9" t="inlineStr">
+      <c r="E2" s="65" t="inlineStr">
         <is>
           <t>Level</t>
         </is>
       </c>
-      <c r="F2" s="9" t="inlineStr">
+      <c r="F2" s="65" t="inlineStr">
         <is>
           <t>Entity</t>
         </is>
       </c>
-      <c r="G2" s="9" t="inlineStr">
+      <c r="G2" s="65" t="inlineStr">
         <is>
           <t>LLM Hint</t>
         </is>
       </c>
-      <c r="H2" s="51" t="inlineStr">
+      <c r="H2" s="66" t="inlineStr">
         <is>
           <t>Matching Operator</t>
         </is>
       </c>
-      <c r="I2" s="51" t="inlineStr">
+      <c r="I2" s="66" t="inlineStr">
         <is>
           <t>Scoring Weight</t>
         </is>
       </c>
-      <c r="J2" t="inlineStr">
+      <c r="J2" s="66" t="inlineStr">
         <is>
           <t>Score Function</t>
         </is>
       </c>
-      <c r="K2" t="inlineStr">
+      <c r="K2" s="66" t="inlineStr">
         <is>
           <t>Score Threshold A</t>
         </is>
       </c>
-      <c r="L2" t="inlineStr">
+      <c r="L2" s="66" t="inlineStr">
         <is>
           <t>Score Threshold B</t>
         </is>
       </c>
-      <c r="M2" t="inlineStr">
+      <c r="M2" s="66" t="inlineStr">
         <is>
           <t>Plausibility Min</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="N2" s="66" t="inlineStr">
         <is>
           <t>Plausibility Max</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
+      <c r="O2" s="66" t="inlineStr">
         <is>
           <t>result_card</t>
         </is>
       </c>
-      <c r="P2" t="inlineStr">
+      <c r="P2" s="66" t="inlineStr">
         <is>
           <t>Display Mode</t>
         </is>
       </c>
-      <c r="Q2" t="inlineStr">
+      <c r="Q2" s="66" t="inlineStr">
         <is>
           <t>UI Hint</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="R2" s="66" t="inlineStr">
         <is>
           <t>UUID</t>
         </is>
       </c>
     </row>
-    <row r="3" ht="15.75" customHeight="1" s="57">
+    <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="62" t="inlineStr">
         <is>
           <t>── WORKFLOW MODE (property-based — replaces the old Undercarriage / G2P / Picking split)</t>
         </is>
       </c>
-    </row>
-    <row r="4" ht="33.75" customHeight="1" s="57">
+      <c r="C3" s="64" t="n"/>
+      <c r="G3" s="64" t="n"/>
+      <c r="Q3" s="64" t="n"/>
+    </row>
+    <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="16" t="inlineStr">
         <is>
           <t>workflow_capability</t>
@@ -6941,7 +7529,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C4" s="24" t="inlineStr">
+      <c r="C4" s="67" t="inlineStr">
         <is>
           <t>Transport | Goods-to-Person | Picking support</t>
         </is>
@@ -6956,7 +7544,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G4" s="18" t="inlineStr">
+      <c r="G4" s="68" t="inlineStr">
         <is>
           <t>AMR workflow function. [AMR ONLY] null for other types. Output from allowed values, comma-separated. NULL RULE: output null unless the tender explicitly specifies the AMR workflow (Transport, Goods-to-Person, Picking support). Do NOT infer from general automation context.</t>
         </is>
@@ -6966,13 +7554,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q4" s="64" t="inlineStr">
+        <is>
+          <t>Welche Arbeitsabläufe soll das AMR unterstützen?</t>
+        </is>
+      </c>
       <c r="R4" t="inlineStr">
         <is>
           <t>8da77114-fbe9-4e21-a0d3-e03edfce5588</t>
         </is>
       </c>
     </row>
-    <row r="5" ht="33.75" customHeight="1" s="57">
+    <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="19" t="inlineStr">
         <is>
           <t>grid_required</t>
@@ -6983,7 +7576,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C5" s="28" t="n"/>
+      <c r="C5" s="69" t="n"/>
       <c r="E5" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -6994,7 +7587,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G5" s="21" t="inlineStr">
+      <c r="G5" s="70" t="inlineStr">
         <is>
           <t>Requires fixed storage grid. [AMR ONLY] true/false. null for other types. NULL RULE: output null unless the tender explicitly requires a fixed storage grid (e.g. AutoStore-style). Do NOT infer from 'racking' or 'shelving'.</t>
         </is>
@@ -7004,13 +7597,18 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="Q5" s="64" t="inlineStr">
+        <is>
+          <t>Ist ein physisches Gittersystem (z. B. Lagerroboter-Raster) Teil der Lösung?</t>
+        </is>
+      </c>
       <c r="R5" t="inlineStr">
         <is>
           <t>a7753133-3bc8-4ec7-b14a-7b328556ca8c</t>
         </is>
       </c>
     </row>
-    <row r="6" ht="33.75" customHeight="1" s="57">
+    <row r="6" ht="15" customHeight="1" s="57">
       <c r="A6" s="16" t="inlineStr">
         <is>
           <t>rotation_capable</t>
@@ -7021,7 +7619,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C6" s="24" t="n"/>
+      <c r="C6" s="67" t="n"/>
       <c r="E6" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -7032,7 +7630,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G6" s="18" t="inlineStr">
+      <c r="G6" s="68" t="inlineStr">
         <is>
           <t>Can rotate the carried rack/pod in place to present a chosen face (hallmark of G2P). Source: 'shelf rotation / spin'. rotation_capable + grid_required ≈ goods-to-person; both false ≈ pure transport.</t>
         </is>
@@ -7045,13 +7643,18 @@
           <t>bool</t>
         </is>
       </c>
+      <c r="Q6" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AMR Lasten während der Fahrt drehen können?</t>
+        </is>
+      </c>
       <c r="R6" t="inlineStr">
         <is>
           <t>9a1ce2ba-f680-4a5a-b6c3-494952729061</t>
         </is>
       </c>
     </row>
-    <row r="7" ht="33.75" customHeight="1" s="57">
+    <row r="7" ht="15" customHeight="1" s="57">
       <c r="A7" s="19" t="inlineStr">
         <is>
           <t>picking_mechanism</t>
@@ -7062,7 +7665,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C7" s="28" t="inlineStr">
+      <c r="C7" s="69" t="inlineStr">
         <is>
           <t>None | Human-assisted (cart follower) | Autonomous arm | Conveyor-integrated | Bin-transfer</t>
         </is>
@@ -7077,7 +7680,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G7" s="21" t="inlineStr">
+      <c r="G7" s="70" t="inlineStr">
         <is>
           <t>Picking method. [AMR ONLY] null for other types. Output from allowed values. NULL RULE: output null unless the tender explicitly names a picking method. Do NOT infer from generic 'picking' mentions.</t>
         </is>
@@ -7087,20 +7690,28 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q7" s="64" t="inlineStr">
+        <is>
+          <t>Welcher Mechanismus soll das AMR zum Greifen oder Kommissionieren verwenden?</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>6d332b7e-0da6-4638-bf67-37bf54424603</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="15.75" customHeight="1" s="57">
+    <row r="8" ht="15" customHeight="1" s="57">
       <c r="A8" s="62" t="inlineStr">
         <is>
           <t>── LOAD HANDLING &amp; LIFT</t>
         </is>
       </c>
-    </row>
-    <row r="9" ht="33.75" customHeight="1" s="57">
+      <c r="C8" s="64" t="n"/>
+      <c r="G8" s="64" t="n"/>
+      <c r="Q8" s="64" t="n"/>
+    </row>
+    <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="16" t="inlineStr">
         <is>
           <t>lift_height_mm</t>
@@ -7111,7 +7722,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C9" s="24" t="n"/>
+      <c r="C9" s="67" t="n"/>
       <c r="D9" t="inlineStr">
         <is>
           <t>mm</t>
@@ -7127,7 +7738,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G9" s="18" t="inlineStr">
+      <c r="G9" s="68" t="inlineStr">
         <is>
           <t>Lift stroke to raise the cart/rack/pod off the floor. Source: spec 'lifting height/stroke'. Implies whether it clears the carrier underside; filter vs. carrier leg height. (0 for non-lifting transport tops.)</t>
         </is>
@@ -7143,13 +7754,18 @@
       <c r="N9" t="n">
         <v>15000</v>
       </c>
+      <c r="Q9" s="64" t="inlineStr">
+        <is>
+          <t>Bis zu welcher Höhe muss das AMR Lasten oder Regale anheben? (mm)</t>
+        </is>
+      </c>
       <c r="R9" t="inlineStr">
         <is>
           <t>1df6b905-0a76-4103-bb48-62cecd0e7e51</t>
         </is>
       </c>
     </row>
-    <row r="10" ht="33.75" customHeight="1" s="57">
+    <row r="10" ht="15" customHeight="1" s="57">
       <c r="A10" s="19" t="inlineStr">
         <is>
           <t>min_ground_clearance_mm</t>
@@ -7160,7 +7776,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C10" s="28" t="n"/>
+      <c r="C10" s="69" t="n"/>
       <c r="D10" t="inlineStr">
         <is>
           <t>mm</t>
@@ -7176,7 +7792,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G10" s="21" t="inlineStr">
+      <c r="G10" s="70" t="inlineStr">
         <is>
           <t>Robot height / clearance needed to drive UNDER the carrier (undercarriage workflows). Source: vehicle height spec. Must be less than the carrier's underside gap — classic undercarriage K.O.</t>
         </is>
@@ -7192,13 +7808,18 @@
       <c r="N10" t="n">
         <v>300</v>
       </c>
+      <c r="Q10" s="64" t="inlineStr">
+        <is>
+          <t>Wie viel Bodenfreiheit wird mindestens benötigt? (mm; z. B. für Bodenunebenheiten oder Schwellen)</t>
+        </is>
+      </c>
       <c r="R10" t="inlineStr">
         <is>
           <t>6a6f5ac8-5147-4664-a0d8-fea186f667d0</t>
         </is>
       </c>
     </row>
-    <row r="11" ht="33.75" customHeight="1" s="57">
+    <row r="11" ht="15" customHeight="1" s="57">
       <c r="A11" s="16" t="inlineStr">
         <is>
           <t>rack_pin_compatible</t>
@@ -7209,7 +7830,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C11" s="24" t="n"/>
+      <c r="C11" s="67" t="n"/>
       <c r="E11" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -7220,7 +7841,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G11" s="18" t="inlineStr">
+      <c r="G11" s="68" t="inlineStr">
         <is>
           <t>Engages standard rack/shelf pin systems (Geek+/Quicktron style). Source: 'shelf/rack compatibility'. Cond. K.O.: binds when the buyer reuses existing movable shelving.</t>
         </is>
@@ -7230,13 +7851,18 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="Q11" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AMR mit pin-kompatiblen Lagerregalen arbeiten können?</t>
+        </is>
+      </c>
       <c r="R11" t="inlineStr">
         <is>
           <t>74c64993-f70f-4b5b-bf7e-68fe325d6577</t>
         </is>
       </c>
     </row>
-    <row r="12" ht="33.75" customHeight="1" s="57">
+    <row r="12" ht="15" customHeight="1" s="57">
       <c r="A12" s="19" t="inlineStr">
         <is>
           <t>free_lift_open_closed_pallet</t>
@@ -7247,7 +7873,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C12" s="28" t="n"/>
+      <c r="C12" s="69" t="n"/>
       <c r="E12" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -7258,7 +7884,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G12" s="21" t="inlineStr">
+      <c r="G12" s="70" t="inlineStr">
         <is>
           <t>Handles BOTH open and closed-bottom pallets (e.g. AGILOX OCF free-lift). Source: 'open/closed pallet'. Cond. K.O.: mirrors the forklift closed-pallet case; binds only when the buyer has closed pallets.</t>
         </is>
@@ -7268,13 +7894,18 @@
           <t>KO_BOOL_REQUIRED</t>
         </is>
       </c>
+      <c r="Q12" s="64" t="inlineStr">
+        <is>
+          <t>Muss das AMR Paletten ohne Gabelöffnungen (Vollpaletten) aufnehmen können?</t>
+        </is>
+      </c>
       <c r="R12" t="inlineStr">
         <is>
           <t>4c8451ee-6cac-4d5e-a72e-19fc89bcb813</t>
         </is>
       </c>
     </row>
-    <row r="13" ht="33.75" customHeight="1" s="57">
+    <row r="13" ht="15" customHeight="1" s="57">
       <c r="A13" s="16" t="inlineStr">
         <is>
           <t>top_module_type</t>
@@ -7285,7 +7916,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C13" s="24" t="inlineStr">
+      <c r="C13" s="67" t="inlineStr">
         <is>
           <t>None | Lift | Hook | Shelf Carrier | Conveyor | Roller | Cobot arm | Custom</t>
         </is>
@@ -7300,18 +7931,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G13" s="18" t="inlineStr">
+      <c r="G13" s="68" t="inlineStr">
         <is>
           <t>Interchangeable top modules the platform accepts (e.g. MiR Hook/Shelf-Lift/Pallet-Lift; UR cobot). Source: 'top modules / accessories'. More modules = one platform covers more workflows.</t>
         </is>
       </c>
+      <c r="Q13" s="64" t="inlineStr">
+        <is>
+          <t>Welches Aufbaumodul ist erforderlich? (z. B. Förderband, Hubtisch, Greifarme)</t>
+        </is>
+      </c>
       <c r="R13" t="inlineStr">
         <is>
           <t>6f771137-7364-4d36-abbb-f4a9ac4abe41</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="33.75" customHeight="1" s="57">
+    <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="19" t="inlineStr">
         <is>
           <t>cart_pickup_height_range_mm</t>
@@ -7322,7 +7958,7 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="C14" s="28" t="n"/>
+      <c r="C14" s="69" t="n"/>
       <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -7333,25 +7969,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G14" s="21" t="inlineStr">
+      <c r="G14" s="70" t="inlineStr">
         <is>
           <t>Range of cart/carrier heights the hook/lift can collect without modifying existing carts. Source: 'hook / cart' spec. Wider range = reuse of existing fleet.</t>
         </is>
       </c>
+      <c r="Q14" s="64" t="inlineStr">
+        <is>
+          <t>In welchem Höhenbereich muss das AMR Wagen oder Ladungsträger aufnehmen? (mm)</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>30487671-8cec-427a-8026-4b7d6e0a82a4</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="15.75" customHeight="1" s="57">
+    <row r="15" ht="15" customHeight="1" s="57">
       <c r="A15" s="62" t="inlineStr">
         <is>
           <t>── MOVEMENT</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="33.75" customHeight="1" s="57">
+      <c r="C15" s="64" t="n"/>
+      <c r="G15" s="64" t="n"/>
+      <c r="Q15" s="64" t="n"/>
+    </row>
+    <row r="16" ht="15" customHeight="1" s="57">
       <c r="A16" s="19" t="inlineStr">
         <is>
           <t>min_turning_radius_mm</t>
@@ -7362,7 +8006,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C16" s="28" t="n"/>
+      <c r="C16" s="69" t="n"/>
       <c r="D16" t="inlineStr">
         <is>
           <t>mm</t>
@@ -7378,7 +8022,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G16" s="21" t="inlineStr">
+      <c r="G16" s="70" t="inlineStr">
         <is>
           <t>Min turning radius (0 if omnidirectional). Source: spec. Filter vs. aisle/turn geometry; combine with footprint.</t>
         </is>
@@ -7394,23 +8038,34 @@
       <c r="N16" t="n">
         <v>20000</v>
       </c>
+      <c r="Q16" s="64" t="inlineStr">
+        <is>
+          <t>Wie viel Platz steht für Drehbewegungen zur Verfügung? (mm; der Wendekreis des AMR muss kleiner sein)</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>384a66e5-19c1-48df-bcc0-509d676dbaf8</t>
         </is>
       </c>
     </row>
-    <row r="17" ht="33.75" customHeight="1" s="57">
+    <row r="17" ht="15" customHeight="1" s="57">
       <c r="A17" s="62" t="inlineStr">
         <is>
           <t>── PICK &amp; DROP ACCURACY (order: lateral · depth · angle)</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="15.75" customHeight="1" s="57">
+      <c r="C17" s="64" t="n"/>
+      <c r="G17" s="64" t="n"/>
+      <c r="Q17" s="64" t="n"/>
+    </row>
+    <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="16" t="n"/>
-    </row>
-    <row r="19" ht="33.75" customHeight="1" s="57">
+      <c r="C18" s="64" t="n"/>
+      <c r="G18" s="64" t="n"/>
+      <c r="Q18" s="64" t="n"/>
+    </row>
+    <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="19" t="inlineStr">
         <is>
           <t>pick_req_accuracy_dep_mm</t>
@@ -7421,7 +8076,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C19" s="28" t="n"/>
+      <c r="C19" s="69" t="n"/>
       <c r="D19" t="inlineStr">
         <is>
           <t>mm</t>
@@ -7437,18 +8092,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G19" s="21" t="inlineStr">
+      <c r="G19" s="70" t="inlineStr">
         <is>
           <t>Required pre-park accuracy in DEPTH to engage the carrier. Source: as above.</t>
         </is>
       </c>
+      <c r="Q19" s="64" t="inlineStr">
+        <is>
+          <t>Welche Tiefenpräzision ist bei der Kommissionierung erforderlich? (mm)</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>281c147d-8631-4e35-92a8-037bebca89d7</t>
         </is>
       </c>
     </row>
-    <row r="20" ht="33.75" customHeight="1" s="57">
+    <row r="20" ht="15" customHeight="1" s="57">
       <c r="A20" s="16" t="inlineStr">
         <is>
           <t>pick_req_accuracy_angle_deg</t>
@@ -7459,7 +8119,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C20" s="24" t="n"/>
+      <c r="C20" s="67" t="n"/>
       <c r="D20" t="inlineStr">
         <is>
           <t>°</t>
@@ -7475,18 +8135,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G20" s="18" t="inlineStr">
+      <c r="G20" s="68" t="inlineStr">
         <is>
           <t>Required pre-park ANGLE accuracy to engage. Source: as above. Tighter angle need = stricter parking discipline upstream.</t>
         </is>
       </c>
+      <c r="Q20" s="64" t="inlineStr">
+        <is>
+          <t>Welche Winkelpräzision ist bei der Kommissionierung erforderlich? (Grad)</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>646f14fe-cda9-47db-b8b8-d548a793a938</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="33.75" customHeight="1" s="57">
+    <row r="21" ht="15" customHeight="1" s="57">
       <c r="A21" s="19" t="inlineStr">
         <is>
           <t>drop_accuracy_lat_mm</t>
@@ -7497,7 +8162,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C21" s="28" t="n"/>
+      <c r="C21" s="69" t="n"/>
       <c r="D21" t="inlineStr">
         <is>
           <t>mm</t>
@@ -7513,18 +8178,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G21" s="21" t="inlineStr">
+      <c r="G21" s="70" t="inlineStr">
         <is>
           <t>Placement accuracy LATERALLY when the robot sets a carrier down at a defined position/marker. Source: spec 'positioning accuracy'. Matters when the dropped carrier must be re-acquired later. (added — was missing for AMR)</t>
         </is>
       </c>
+      <c r="Q21" s="64" t="inlineStr">
+        <is>
+          <t>Wie präzise muss das AMR Lasten seitlich absetzen? (mm laterale Abweichung)</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>73ee007a-8afa-4a1f-a59c-38a03582a1e3</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="33.75" customHeight="1" s="57">
+    <row r="22" ht="15" customHeight="1" s="57">
       <c r="A22" s="16" t="inlineStr">
         <is>
           <t>drop_accuracy_dep_mm</t>
@@ -7535,7 +8205,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C22" s="24" t="n"/>
+      <c r="C22" s="67" t="n"/>
       <c r="D22" t="inlineStr">
         <is>
           <t>mm</t>
@@ -7551,18 +8221,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G22" s="18" t="inlineStr">
+      <c r="G22" s="68" t="inlineStr">
         <is>
           <t>Placement accuracy in DEPTH at drop. Source: as above.</t>
         </is>
       </c>
+      <c r="Q22" s="64" t="inlineStr">
+        <is>
+          <t>Wie präzise muss das AMR Lasten in der Tiefe absetzen? (mm)</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>401ff126-934a-4b8d-a57e-a4dcc481fb23</t>
         </is>
       </c>
     </row>
-    <row r="23" ht="33.75" customHeight="1" s="57">
+    <row r="23" ht="15" customHeight="1" s="57">
       <c r="A23" s="19" t="inlineStr">
         <is>
           <t>drop_accuracy_angle_deg</t>
@@ -7573,7 +8248,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C23" s="28" t="n"/>
+      <c r="C23" s="69" t="n"/>
       <c r="D23" t="inlineStr">
         <is>
           <t>°</t>
@@ -7589,25 +8264,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G23" s="21" t="inlineStr">
+      <c r="G23" s="70" t="inlineStr">
         <is>
           <t>Angular placement accuracy at drop. Source: as above.</t>
         </is>
       </c>
+      <c r="Q23" s="64" t="inlineStr">
+        <is>
+          <t>Wie präzise muss das AMR Lasten winkelgenau absetzen? (Grad)</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>b7f20be0-e007-4d72-a0e1-0e19675fbc98</t>
         </is>
       </c>
     </row>
-    <row r="24" ht="33.75" customHeight="1" s="57">
+    <row r="24" ht="15" customHeight="1" s="57">
       <c r="A24" s="62" t="inlineStr">
         <is>
           <t>── STORAGE / G2P LAYOUT</t>
         </is>
       </c>
-    </row>
-    <row r="25" ht="15.75" customHeight="1" s="57">
+      <c r="C24" s="64" t="n"/>
+      <c r="G24" s="64" t="n"/>
+      <c r="Q24" s="64" t="n"/>
+    </row>
+    <row r="25" ht="15" customHeight="1" s="57">
       <c r="A25" s="16" t="inlineStr">
         <is>
           <t>storage_system_type</t>
@@ -7618,7 +8301,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C25" t="inlineStr">
+      <c r="C25" s="64" t="inlineStr">
         <is>
           <t>Bin-to-Person | Tote-to-Person | Shelf-to-Person | Pallet-to-Person</t>
         </is>
@@ -7633,7 +8316,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G25" t="inlineStr">
+      <c r="G25" s="64" t="inlineStr">
         <is>
           <t>Goods-to-Person storage paradigm the AMR is designed to operate within. Source: system overview, 'goods-to-person', 'G2P', storage compatibility section. Output ONLY from allowed values (Bin-to-Person, Tote-to-Person, Shelf-to-Person, Pallet-to-Person). Cond. K.O.: binds when tender specifies an existing or planned storage infrastructure the AMR must integrate with.</t>
         </is>
@@ -7643,13 +8326,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q25" s="64" t="inlineStr">
+        <is>
+          <t>Welches Lagersystem soll das AMR bedienen?</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>16c5389a-65d5-44b1-a07d-597bbaa12851</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="33.75" customHeight="1" s="57">
+    <row r="26" ht="15" customHeight="1" s="57">
       <c r="A26" s="19" t="inlineStr">
         <is>
           <t>shelf_height_mm</t>
@@ -7660,7 +8348,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C26" s="28" t="n"/>
+      <c r="C26" s="69" t="n"/>
       <c r="D26" t="inlineStr">
         <is>
           <t>mm</t>
@@ -7676,7 +8364,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G26" s="21" t="inlineStr">
+      <c r="G26" s="70" t="inlineStr">
         <is>
           <t>Max shelf/rack/pod height handled (Geek+ ~2.8 m; RoboShuttle ~11 m). Source: spec. Cond. K.O.: binds for G2P vs. building height; density driver.</t>
         </is>
@@ -7692,13 +8380,18 @@
       <c r="N26" t="n">
         <v>15000</v>
       </c>
+      <c r="Q26" s="64" t="inlineStr">
+        <is>
+          <t>Wie hoch sind die Lagerregale, die das AMR bedienen soll? (mm)</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>40b295f1-a133-4d9a-8e1d-91833c7da653</t>
         </is>
       </c>
     </row>
-    <row r="27" ht="33.75" customHeight="1" s="57">
+    <row r="27" ht="15" customHeight="1" s="57">
       <c r="A27" s="16" t="inlineStr">
         <is>
           <t>shelf_footprint_mm</t>
@@ -7709,7 +8402,7 @@
           <t>Text</t>
         </is>
       </c>
-      <c r="C27" s="24" t="n"/>
+      <c r="C27" s="67" t="n"/>
       <c r="E27" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -7720,7 +8413,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G27" s="18" t="inlineStr">
+      <c r="G27" s="68" t="inlineStr">
         <is>
           <t>Pod/shelf footprint the robot drives under (e.g. 880×880, 1020×1020). Source: spec 'shelf size'. Cond. K.O.: binds when matching existing shelving dimensions.</t>
         </is>
@@ -7730,13 +8423,18 @@
           <t>KO_IF_NEQ</t>
         </is>
       </c>
+      <c r="Q27" s="64" t="inlineStr">
+        <is>
+          <t>Wie groß ist der Grundriss der Lagereinheiten? (mm)</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>63afacee-60c5-4129-b852-628263f39066</t>
         </is>
       </c>
     </row>
-    <row r="28" ht="33.75" customHeight="1" s="57">
+    <row r="28" ht="15" customHeight="1" s="57">
       <c r="A28" s="19" t="inlineStr">
         <is>
           <t>min_grid_area_m2</t>
@@ -7747,7 +8445,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C28" s="28" t="n"/>
+      <c r="C28" s="69" t="n"/>
       <c r="D28" t="inlineStr">
         <is>
           <t>m²</t>
@@ -7763,25 +8461,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G28" s="21" t="inlineStr">
+      <c r="G28" s="70" t="inlineStr">
         <is>
           <t>Smallest sensible storage field for a G2P deployment. Source: solution/sales. Entry-footprint orientation.</t>
         </is>
       </c>
+      <c r="Q28" s="64" t="inlineStr">
+        <is>
+          <t>Wie groß ist die minimale Lagerfläche für das AMR-System? (m²)</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>5f36df82-a7a1-46ea-a0e5-0671f3923d06</t>
         </is>
       </c>
     </row>
-    <row r="29" ht="33.75" customHeight="1" s="57">
+    <row r="29" ht="15" customHeight="1" s="57">
       <c r="A29" s="62" t="inlineStr">
         <is>
           <t>── THROUGHPUT &amp; PICKING</t>
         </is>
       </c>
-    </row>
-    <row r="30" ht="15.75" customHeight="1" s="57">
+      <c r="C29" s="64" t="n"/>
+      <c r="G29" s="64" t="n"/>
+      <c r="Q29" s="64" t="n"/>
+    </row>
+    <row r="30" ht="15" customHeight="1" s="57">
       <c r="A30" s="16" t="inlineStr">
         <is>
           <t>throughput_picks_per_hour</t>
@@ -7792,6 +8498,7 @@
           <t>Integer</t>
         </is>
       </c>
+      <c r="C30" s="64" t="n"/>
       <c r="D30" t="inlineStr">
         <is>
           <t>picks/h</t>
@@ -7807,7 +8514,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G30" t="inlineStr">
+      <c r="G30" s="64" t="inlineStr">
         <is>
           <t>Maximum throughput in picks per hour as a single integer — the rated capacity of the system. Source: datasheet throughput / performance section.</t>
         </is>
@@ -7832,13 +8539,18 @@
       <c r="N30" t="n">
         <v>1000</v>
       </c>
+      <c r="Q30" s="64" t="inlineStr">
+        <is>
+          <t>Wie viele Kommissionierungen pro Stunde sind mindestens erforderlich?</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>31d98668-22b6-46f9-9b8d-894d9293e2c7</t>
         </is>
       </c>
     </row>
-    <row r="31" ht="33.75" customHeight="1" s="57">
+    <row r="31" ht="15" customHeight="1" s="57">
       <c r="A31" s="19" t="inlineStr">
         <is>
           <t>throughput_basis</t>
@@ -7849,7 +8561,7 @@
           <t>Dropdown</t>
         </is>
       </c>
-      <c r="C31" s="28" t="inlineStr">
+      <c r="C31" s="69" t="inlineStr">
         <is>
           <t>Per station | Per robot | Per system</t>
         </is>
@@ -7864,18 +8576,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G31" s="21" t="inlineStr">
+      <c r="G31" s="70" t="inlineStr">
         <is>
           <t>What throughput_picks_per_hour refers to. Source: read the fine print of the vendor KPI. Essential to disambiguate G2P (per-station) vs picking (per-robot) numbers. (new — fixes the per-station/per-robot confusion)</t>
         </is>
       </c>
+      <c r="Q31" s="64" t="inlineStr">
+        <is>
+          <t>Auf welcher Basis wird der Durchsatz gemessen?</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>e66dbd99-39c8-4935-aa5f-0a6d49e41197</t>
         </is>
       </c>
     </row>
-    <row r="32" ht="33.75" customHeight="1" s="57">
+    <row r="32" ht="15" customHeight="1" s="57">
       <c r="A32" s="16" t="inlineStr">
         <is>
           <t>concurrent_robots_per_station</t>
@@ -7886,7 +8603,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C32" s="24" t="n"/>
+      <c r="C32" s="67" t="n"/>
       <c r="D32" t="inlineStr">
         <is>
           <t># robots</t>
@@ -7902,18 +8619,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G32" s="18" t="inlineStr">
+      <c r="G32" s="68" t="inlineStr">
         <is>
           <t>How many robots queue/serve one G2P station at once. Source: solution spec. Implies station utilization &amp; peak throughput.</t>
         </is>
       </c>
+      <c r="Q32" s="64" t="inlineStr">
+        <is>
+          <t>Wie viele AMRs müssen gleichzeitig an einer Station arbeiten können?</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>e1b69ffc-31e1-40fb-8a5e-bd5d7f00e2c8</t>
         </is>
       </c>
     </row>
-    <row r="33" ht="33.75" customHeight="1" s="57">
+    <row r="33" ht="15" customHeight="1" s="57">
       <c r="A33" s="19" t="inlineStr">
         <is>
           <t>order_lines_per_run</t>
@@ -7924,7 +8646,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C33" s="28" t="n"/>
+      <c r="C33" s="69" t="n"/>
       <c r="D33" t="inlineStr">
         <is>
           <t># lines</t>
@@ -7940,18 +8662,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G33" s="21" t="inlineStr">
+      <c r="G33" s="70" t="inlineStr">
         <is>
           <t>Order lines per robot run before returning to a station (picking workflows). Source: solution spec. Travel efficiency / batch depth.</t>
         </is>
       </c>
+      <c r="Q33" s="64" t="inlineStr">
+        <is>
+          <t>Wie viele Auftragspositionen sollen pro Fahrt abgearbeitet werden?</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>6f0b43c1-d999-4bfa-a17c-ea4540e149bb</t>
         </is>
       </c>
     </row>
-    <row r="34" ht="33.75" customHeight="1" s="57">
+    <row r="34" ht="15" customHeight="1" s="57">
       <c r="A34" s="16" t="inlineStr">
         <is>
           <t>task_interleaving</t>
@@ -7962,7 +8689,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C34" s="24" t="n"/>
+      <c r="C34" s="67" t="n"/>
       <c r="E34" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -7973,18 +8700,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G34" s="18" t="inlineStr">
+      <c r="G34" s="68" t="inlineStr">
         <is>
           <t>Mixes pick + put-away + replenishment + returns in one run (Locus Origin). Source: 'task interleaving'. Higher asset utilization.</t>
         </is>
       </c>
+      <c r="Q34" s="64" t="inlineStr">
+        <is>
+          <t>Sollen AMRs verschiedene Aufgabentypen im Wechsel abarbeiten können?</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>71cb3acf-5a23-4f7f-8abc-9488803a5584</t>
         </is>
       </c>
     </row>
-    <row r="35" ht="33.75" customHeight="1" s="57">
+    <row r="35" ht="15" customHeight="1" s="57">
       <c r="A35" s="19" t="inlineStr">
         <is>
           <t>storage_density_factor</t>
@@ -7995,7 +8727,7 @@
           <t>Float</t>
         </is>
       </c>
-      <c r="C35" s="28" t="n"/>
+      <c r="C35" s="69" t="n"/>
       <c r="D35" t="inlineStr">
         <is>
           <t>× vs. manual</t>
@@ -8011,18 +8743,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G35" s="21" t="inlineStr">
+      <c r="G35" s="70" t="inlineStr">
         <is>
           <t>Storage density vs. conventional shelving (Geek+ claims ~2.5×). Source: solution marketing — treat as a vendor claim.</t>
         </is>
       </c>
+      <c r="Q35" s="64" t="inlineStr">
+        <is>
+          <t>Wie wichtig ist eine hohe Lagerplatzdichte für Ihr System?</t>
+        </is>
+      </c>
       <c r="R35" t="inlineStr">
         <is>
           <t>002a11fb-19eb-42a2-810f-6848f7d86a06</t>
         </is>
       </c>
     </row>
-    <row r="36" ht="33.75" customHeight="1" s="57">
+    <row r="36" ht="15" customHeight="1" s="57">
       <c r="A36" s="16" t="inlineStr">
         <is>
           <t>ergonomic_height_adjustable</t>
@@ -8033,7 +8770,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C36" s="24" t="n"/>
+      <c r="C36" s="67" t="n"/>
       <c r="E36" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -8044,18 +8781,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G36" s="18" t="inlineStr">
+      <c r="G36" s="68" t="inlineStr">
         <is>
           <t>Pick/put height adjusts to operator ergonomics (picking workflows). Source: 'ergonomic / adjustable'. Sustains pick rate.</t>
         </is>
       </c>
+      <c r="Q36" s="64" t="inlineStr">
+        <is>
+          <t>Muss die Arbeitshöhe für Mitarbeiter ergonomisch anpassbar sein?</t>
+        </is>
+      </c>
       <c r="R36" t="inlineStr">
         <is>
           <t>e5eb0e99-54a4-4c8b-82ae-f0a4e4c8f2c1</t>
         </is>
       </c>
     </row>
-    <row r="37" ht="33.75" customHeight="1" s="57">
+    <row r="37" ht="15" customHeight="1" s="57">
       <c r="A37" s="19" t="inlineStr">
         <is>
           <t>onboard_ui</t>
@@ -8066,7 +8808,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C37" s="28" t="n"/>
+      <c r="C37" s="69" t="n"/>
       <c r="E37" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -8077,18 +8819,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G37" s="21" t="inlineStr">
+      <c r="G37" s="70" t="inlineStr">
         <is>
           <t>Onboard screen guiding the worker (Locus Origin). Source: 'onboard display / UI'. Speeds training &amp; cuts errors.</t>
         </is>
       </c>
+      <c r="Q37" s="64" t="inlineStr">
+        <is>
+          <t>Ist ein Display oder Bedienpanel am Fahrzeug erforderlich?</t>
+        </is>
+      </c>
       <c r="R37" t="inlineStr">
         <is>
           <t>09ca5135-a860-4236-844e-d2b47e8db98d</t>
         </is>
       </c>
     </row>
-    <row r="38" ht="33.75" customHeight="1" s="57">
+    <row r="38" ht="15" customHeight="1" s="57">
       <c r="A38" s="16" t="inlineStr">
         <is>
           <t>multi_language_display</t>
@@ -8099,7 +8846,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C38" s="24" t="n"/>
+      <c r="C38" s="67" t="n"/>
       <c r="E38" s="31" t="inlineStr">
         <is>
           <t>Context</t>
@@ -8110,18 +8857,23 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G38" s="18" t="inlineStr">
+      <c r="G38" s="68" t="inlineStr">
         <is>
           <t>Onboard UI supports multiple languages. Source: 'multi-language'. Relevant for diverse workforces.</t>
         </is>
       </c>
+      <c r="Q38" s="64" t="inlineStr">
+        <is>
+          <t>Muss die Anzeige am Fahrzeug mehrsprachig sein?</t>
+        </is>
+      </c>
       <c r="R38" t="inlineStr">
         <is>
           <t>27965aae-7b51-4704-b14a-3e19ae1a1b7c</t>
         </is>
       </c>
     </row>
-    <row r="39" ht="33.75" customHeight="1" s="57">
+    <row r="39" ht="15" customHeight="1" s="57">
       <c r="A39" s="19" t="inlineStr">
         <is>
           <t>gamification</t>
@@ -8132,7 +8884,7 @@
           <t>Boolean</t>
         </is>
       </c>
-      <c r="C39" s="28" t="n"/>
+      <c r="C39" s="69" t="n"/>
       <c r="E39" s="31" t="inlineStr">
         <is>
           <t>Context</t>
@@ -8143,25 +8895,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G39" s="21" t="inlineStr">
+      <c r="G39" s="70" t="inlineStr">
         <is>
           <t>Optional worker gamification/incentive features (Locus). Source: 'gamification'. Soft productivity lever.</t>
         </is>
       </c>
+      <c r="Q39" s="64" t="inlineStr">
+        <is>
+          <t>Sind spielerische Motivationselemente für Mitarbeiter gewünscht?</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
           <t>c2e9dbf0-0ec5-4434-82bf-6bb5879ef70e</t>
         </is>
       </c>
     </row>
-    <row r="40" ht="33.75" customHeight="1" s="57">
+    <row r="40" ht="15" customHeight="1" s="57">
       <c r="A40" s="62" t="inlineStr">
         <is>
           <t>── CONTAINER (picking workflows)</t>
         </is>
       </c>
-    </row>
-    <row r="41" ht="15.75" customHeight="1" s="57">
+      <c r="C40" s="64" t="n"/>
+      <c r="G40" s="64" t="n"/>
+      <c r="Q40" s="64" t="n"/>
+    </row>
+    <row r="41" ht="15" customHeight="1" s="57">
       <c r="A41" s="16" t="inlineStr">
         <is>
           <t>onboard_container_type</t>
@@ -8172,7 +8932,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C41" t="inlineStr">
+      <c r="C41" s="64" t="inlineStr">
         <is>
           <t>Tote | Bin | Pallet | Shelf | None</t>
         </is>
@@ -8187,7 +8947,7 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G41" t="inlineStr">
+      <c r="G41" s="64" t="inlineStr">
         <is>
           <t>Physical carrier type the AMR transports on its deck or platform. Source: spec 'payload type', 'transports', 'carries', solution overview. Output ONLY from allowed values (Tote, Bin, Pallet, Shelf, None — use None for robots that tow or interact with fixed shelving without carrying). Cond. K.O.: binds when tender specifies which container types must be handled.</t>
         </is>
@@ -8197,13 +8957,18 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q41" s="64" t="inlineStr">
+        <is>
+          <t>Welcher Behältertyp soll auf dem AMR transportiert werden?</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>4a9b0aa5-8303-49e5-96dc-87ae6d179f1b</t>
         </is>
       </c>
     </row>
-    <row r="42" ht="33.75" customHeight="1" s="57">
+    <row r="42" ht="15" customHeight="1" s="57">
       <c r="A42" s="19" t="inlineStr">
         <is>
           <t>onboard_container_count</t>
@@ -8214,7 +8979,7 @@
           <t>Integer</t>
         </is>
       </c>
-      <c r="C42" s="28" t="n"/>
+      <c r="C42" s="69" t="n"/>
       <c r="D42" t="inlineStr">
         <is>
           <t># containers</t>
@@ -8230,25 +8995,33 @@
           <t>Base Model</t>
         </is>
       </c>
-      <c r="G42" s="21" t="inlineStr">
+      <c r="G42" s="70" t="inlineStr">
         <is>
           <t>Simultaneous containers carried (multi-order/batch picking). Source: spec/config. More = batch efficiency.</t>
         </is>
       </c>
+      <c r="Q42" s="64" t="inlineStr">
+        <is>
+          <t>Wie viele Behälter soll das AMR gleichzeitig transportieren?</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>51472385-d742-4e72-a91f-b480738c48ed</t>
         </is>
       </c>
     </row>
-    <row r="43" ht="33.75" customHeight="1" s="57">
+    <row r="43" ht="15" customHeight="1" s="57">
       <c r="A43" s="62" t="inlineStr">
         <is>
           <t>── WMS</t>
         </is>
       </c>
-    </row>
-    <row r="44" ht="15.75" customHeight="1" s="57">
+      <c r="C43" s="64" t="n"/>
+      <c r="G43" s="64" t="n"/>
+      <c r="Q43" s="64" t="n"/>
+    </row>
+    <row r="44" ht="15" customHeight="1" s="57">
       <c r="A44" s="16" t="inlineStr">
         <is>
           <t>wms_integration_native</t>
@@ -8259,7 +9032,7 @@
           <t>Multi-Select</t>
         </is>
       </c>
-      <c r="C44" t="inlineStr">
+      <c r="C44" s="64" t="inlineStr">
         <is>
           <t>SAP EWM | Oracle WMS | Microsoft Dynamics 365 | Custom API | REST API</t>
         </is>
@@ -8274,12 +9047,18 @@
           <t>Base Model</t>
         </is>
       </c>
+      <c r="G44" s="64" t="n"/>
       <c r="I44" t="n">
         <v>8</v>
       </c>
       <c r="J44" t="inlineStr">
         <is>
           <t>nonempty</t>
+        </is>
+      </c>
+      <c r="Q44" s="64" t="inlineStr">
+        <is>
+          <t>Ist eine direkte native Integration mit dem Warehouse-Management-System erforderlich?</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -2596,8 +2596,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -2787,7 +2787,7 @@
       </c>
       <c r="Q4" s="64" t="inlineStr">
         <is>
-          <t>Welche Navigationsart ist vorgesehen oder erlaubt? (z. B. Natural Feature/SLAM, Magnetband, QR-Code)</t>
+          <t>What navigation type is intended or allowed? (e.g. Natural Feature/SLAM, magnetic tape, QR code)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -2830,7 +2830,7 @@
       </c>
       <c r="Q5" s="64" t="inlineStr">
         <is>
-          <t>Ist die Installation von Infrastruktur akzeptabel? (z. B. Leitdrähte, Reflektoren, QR-Codes)</t>
+          <t>Is installation of infrastructure (guide wires, reflectors, QR codes) acceptable or explicitly not desired?</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -2881,7 +2881,7 @@
       </c>
       <c r="Q6" s="64" t="inlineStr">
         <is>
-          <t>Wird Außenbetrieb benötigt?</t>
+          <t>Is outdoor operation required?</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -2919,7 +2919,7 @@
       </c>
       <c r="Q7" s="64" t="inlineStr">
         <is>
-          <t>Kann das AGV Hindernissen eigenständig ausweichen ohne anzuhalten?</t>
+          <t>Can the AGV autonomously navigate around obstacles?</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -2957,7 +2957,7 @@
       </c>
       <c r="Q8" s="64" t="inlineStr">
         <is>
-          <t>Muss das AGV in alle Richtungen ohne Wenden fahren können (omnidirektional)?</t>
+          <t>Must the AGV be able to move in all directions without turning (omnidirectional)?</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -3024,7 +3024,7 @@
       </c>
       <c r="Q10" s="64" t="inlineStr">
         <is>
-          <t>Wie hoch ist die maximale Nutzlast pro Ladungsträger? Das AGV muss mindestens dieses Gewicht tragen können (kg).</t>
+          <t>What is the maximum load weight per carrier? The AGV must be able to carry at least this weight.</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -3071,7 +3071,7 @@
       </c>
       <c r="Q11" s="64" t="inlineStr">
         <is>
-          <t>Welche Ladungsträgertypen werden transportiert? (z. B. Europalette, Gitterbox, Behälter — alle zutreffenden auswählen)</t>
+          <t>What type of load carriers will be transported? (e.g. Euro pallet, wire mesh box, container)</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -3114,7 +3114,7 @@
       </c>
       <c r="Q12" s="64" t="inlineStr">
         <is>
-          <t>Muss das AGV mehrere Ladungsträger gleichzeitig transportieren können?</t>
+          <t>Must the AGV be able to transport multiple load carriers simultaneously?</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -3170,7 +3170,7 @@
       </c>
       <c r="Q14" s="64" t="inlineStr">
         <is>
-          <t>Wie schnell soll das AGV maximal fahren? (m/s; z. B. 1,5 m/s)</t>
+          <t>What maximum speed should the AGV achieve? (m/s)</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -3213,7 +3213,7 @@
       </c>
       <c r="Q15" s="64" t="inlineStr">
         <is>
-          <t>Wie lang ist das Fahrzeug? (mm; nur zur Information)</t>
+          <t>Vehicle length. (mm; for reference only)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -3256,7 +3256,7 @@
       </c>
       <c r="Q16" s="64" t="inlineStr">
         <is>
-          <t>Wie breit ist das Fahrzeug? (mm; nur zur Information)</t>
+          <t>Vehicle width. (mm; for reference only)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -3310,7 +3310,7 @@
       </c>
       <c r="Q17" s="64" t="inlineStr">
         <is>
-          <t>Wie kalt wird es am Betriebsort mindestens? (°C; z. B. –20 °C für Tiefkühlbereich)</t>
+          <t>What is the minimum temperature at the operating site? (°C; e.g. -20°C for cold storage)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -3364,7 +3364,7 @@
       </c>
       <c r="Q18" s="64" t="inlineStr">
         <is>
-          <t>Wie warm wird es am Betriebsort maximal? (°C; z. B. 30 °C für Produktionshalle)</t>
+          <t>What is the maximum temperature at the operating site? (°C; e.g. 30°C for production hall)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -3418,7 +3418,7 @@
       </c>
       <c r="Q19" s="64" t="inlineStr">
         <is>
-          <t>Wie hoch ist die maximale relative Luftfeuchtigkeit am Betriebsort? (%)</t>
+          <t>What is the maximum relative humidity at the operating site? (%)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -3465,7 +3465,7 @@
       </c>
       <c r="Q20" s="64" t="inlineStr">
         <is>
-          <t>Welche Schutzklasse (IP-Klasse) ist am Betriebsort erforderlich? (z. B. IP54 für Spritzwasserschutz)</t>
+          <t>What ingress protection rating (IP class) is required at the operating site? (e.g. IP54 for splash water protection)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -3512,7 +3512,7 @@
       </c>
       <c r="Q21" s="64" t="inlineStr">
         <is>
-          <t>Gibt es Reinraumanforderungen am Betriebsort? (ISO-Klasse; nur ausfüllen wenn Reinraum vorhanden)</t>
+          <t>Are there cleanroom requirements at the operating site? (ISO class; only fill in if cleanroom is present)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -3566,7 +3566,7 @@
       </c>
       <c r="Q22" s="64" t="inlineStr">
         <is>
-          <t>Wie steil ist die steilste Fahrstrecke im Betriebsbereich? (% Steigung; z. B. 1,5 für eine 1,5-%-Rampe)</t>
+          <t>How steep is the steepest driving route in the operating area? (% gradient; e.g. 1.5 for a 1.5% ramp)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -3613,7 +3613,7 @@
       </c>
       <c r="Q23" s="64" t="inlineStr">
         <is>
-          <t>Gibt es besondere Anforderungen an die Bodenqualität oder -ebenheit?</t>
+          <t>Are there special requirements for floor quality or flatness?</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -3680,7 +3680,7 @@
       </c>
       <c r="Q25" s="64" t="inlineStr">
         <is>
-          <t>Wie präzise muss das AGV an Übergabe- oder Aufnahmepunkten positionieren? (mm zulässige Abweichung)</t>
+          <t>How precisely must the AGV position at transfer or pickup points? (mm deviation)</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -3732,7 +3732,7 @@
       </c>
       <c r="Q27" s="64" t="inlineStr">
         <is>
-          <t>Welcher Batterietyp ist bevorzugt oder erforderlich?</t>
+          <t>What battery type is preferred or required?</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -3789,7 +3789,7 @@
       </c>
       <c r="Q28" s="64" t="inlineStr">
         <is>
-          <t>Wie viele Stunden Betriebszeit pro Ladung werden mindestens benötigt? (h)</t>
+          <t>How many hours of operating time per charge are required as a minimum? (h)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="Q29" s="64" t="inlineStr">
         <is>
-          <t>Wie lange darf ein vollständiger Ladevorgang maximal dauern? (min)</t>
+          <t>What is the maximum acceptable duration of a full charging cycle? (min)</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -3881,7 +3881,7 @@
       </c>
       <c r="Q30" s="64" t="inlineStr">
         <is>
-          <t>Muss das AGV eigenständig zur Ladestation fahren und automatisch laden?</t>
+          <t>Must the AGV autonomously navigate to the charging station and charge itself?</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -3919,7 +3919,7 @@
       </c>
       <c r="Q31" s="64" t="inlineStr">
         <is>
-          <t>Ist ein schneller manueller Akkuwechsel statt Laden gewünscht?</t>
+          <t>Is fast manual battery swapping desired instead of charging?</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -3979,7 +3979,7 @@
       </c>
       <c r="Q33" s="64" t="inlineStr">
         <is>
-          <t>Welche Sicherheitsnormen müssen erfüllt sein? (z. B. EN ISO 3691-4)</t>
+          <t>Which safety standards must be met? (e.g. EN ISO 3691-4)</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -4029,7 +4029,7 @@
       </c>
       <c r="Q34" s="64" t="inlineStr">
         <is>
-          <t>Welches funktionale Sicherheitsniveau ist gefordert? (z. B. PLd, SIL2)</t>
+          <t>What functional safety level is required? (e.g. PLd, SIL2)</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -4071,7 +4071,7 @@
       </c>
       <c r="Q35" s="64" t="inlineStr">
         <is>
-          <t>Welche Bereiche rund um das Fahrzeug müssen durch Sicherheitssensorik abgedeckt werden?</t>
+          <t>Which areas must be covered by safety sensors?</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -4128,7 +4128,7 @@
       </c>
       <c r="Q37" s="64" t="inlineStr">
         <is>
-          <t>Gibt es ein bestehendes Flottenleitsystem, das kompatibel sein muss?</t>
+          <t>Is there an existing fleet management system that must be compatible?</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -4170,7 +4170,7 @@
       </c>
       <c r="Q38" s="64" t="inlineStr">
         <is>
-          <t>Welche Steuerungsarchitektur ist für die Flotte vorgesehen? (z. B. zentralisiert, dezentralisiert)</t>
+          <t>What control architecture is intended for the fleet? (centralised, decentralised)</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="Q39" s="64" t="inlineStr">
         <is>
-          <t>Muss das AGV den VDA-5050-Standard für Schnittstellen unterstützen?</t>
+          <t>Must the AGV support the VDA 5050 interface standard?</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="Q40" s="64" t="inlineStr">
         <is>
-          <t>Wie viele AGVs sollen gleichzeitig im Einsatz sein?</t>
+          <t>How many AGVs should be in simultaneous operation?</t>
         </is>
       </c>
       <c r="R40" t="inlineStr">
@@ -4305,7 +4305,7 @@
       </c>
       <c r="Q41" s="64" t="inlineStr">
         <is>
-          <t>Müssen AGVs verschiedener Hersteller im selben Bereich kooperieren können?</t>
+          <t>Must AGVs from different manufacturers be able to coexist in the same area?</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -4347,7 +4347,7 @@
       </c>
       <c r="Q42" s="64" t="inlineStr">
         <is>
-          <t>Mit welchen bestehenden Systemen muss das AGV integriert werden? (WMS, ERP, MES)</t>
+          <t>Which existing systems must the AGV integrate with? (WMS, ERP, MES)</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -4389,7 +4389,7 @@
       </c>
       <c r="Q43" s="64" t="inlineStr">
         <is>
-          <t>Gibt es besondere Anforderungen an den Installationsprozess des AGV-Systems?</t>
+          <t>Are there requirements for the installation process of the AGV system?</t>
         </is>
       </c>
       <c r="R43" t="inlineStr">
@@ -4431,7 +4431,7 @@
       </c>
       <c r="Q44" s="64" t="inlineStr">
         <is>
-          <t>Wie einfach müssen spätere Anpassungen oder Erweiterungen möglich sein?</t>
+          <t>How easy must later modifications or expansions be?</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">
@@ -4488,7 +4488,7 @@
       </c>
       <c r="Q46" s="64" t="inlineStr">
         <is>
-          <t>Welche speziellen Stationsanwendungen werden benötigt? (z. B. Ladestation, Übergabestation)</t>
+          <t>What special station applications are required? (e.g. charging station, transfer station)</t>
         </is>
       </c>
       <c r="R46" t="inlineStr">
@@ -4555,7 +4555,7 @@
       </c>
       <c r="Q48" s="64" t="inlineStr">
         <is>
-          <t>Anzahl der Referenzprojekte des Anbieters (wird automatisch befüllt)</t>
+          <t>Number of reference projects from the supplier. (filled automatically)</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -4615,7 +4615,7 @@
       </c>
       <c r="Q49" s="64" t="inlineStr">
         <is>
-          <t>Wie viele Wochen Vorlaufzeit bis zur Inbetriebnahme sind akzeptabel?</t>
+          <t>How many weeks lead time until commissioning is acceptable?</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -4665,7 +4665,7 @@
       </c>
       <c r="Q50" s="64" t="inlineStr">
         <is>
-          <t>In welchen Ländern oder Regionen ist Service und Support erforderlich?</t>
+          <t>In which countries or regions is service and support required?</t>
         </is>
       </c>
       <c r="R50" t="inlineStr">
@@ -4708,7 +4708,7 @@
       </c>
       <c r="Q51" s="64" t="inlineStr">
         <is>
-          <t>Wie viele AGVs werden mindestens benötigt?</t>
+          <t>How many AGVs are needed as a minimum?</t>
         </is>
       </c>
       <c r="R51" t="inlineStr">
@@ -4750,7 +4750,7 @@
       </c>
       <c r="Q52" s="64" t="inlineStr">
         <is>
-          <t>Welches Budget steht für das AGV-Projekt zur Verfügung? (EUR)</t>
+          <t>What budget is available for the AGV project? (EUR)</t>
         </is>
       </c>
       <c r="R52" t="inlineStr">
@@ -4798,7 +4798,7 @@
       </c>
       <c r="Q54" s="64" t="inlineStr">
         <is>
-          <t>Soll das Fahrzeug auch manuell bedienbar sein?</t>
+          <t>Should the vehicle also be manually operable?</t>
         </is>
       </c>
       <c r="R54" t="inlineStr">
@@ -4840,7 +4840,7 @@
       </c>
       <c r="Q55" s="64" t="inlineStr">
         <is>
-          <t>In welcher Branche wird das AGV eingesetzt?</t>
+          <t>In which industry will the AGV be used?</t>
         </is>
       </c>
       <c r="R55" t="inlineStr">
@@ -4882,7 +4882,7 @@
       </c>
       <c r="Q56" s="64" t="inlineStr">
         <is>
-          <t>Wie wird das AGV vertrieben bzw. geliefert?</t>
+          <t>How is the AGV sold or delivered?</t>
         </is>
       </c>
       <c r="R56" t="inlineStr">
@@ -4944,7 +4944,7 @@
       </c>
       <c r="Q58" s="64" t="inlineStr">
         <is>
-          <t>Welcher AGV-Typ ist erforderlich? (wird automatisch aus der Ausschreibung erkannt)</t>
+          <t>What AGV type is required? (automatically detected from the document)</t>
         </is>
       </c>
       <c r="R58" t="inlineStr">
@@ -4991,7 +4991,7 @@
       </c>
       <c r="Q59" s="64" t="inlineStr">
         <is>
-          <t>In welchem Land befindet sich der Betriebsort?</t>
+          <t>In which country is the operating site located?</t>
         </is>
       </c>
       <c r="R59" t="inlineStr">
@@ -5033,7 +5033,7 @@
       </c>
       <c r="Q60" s="64" t="inlineStr">
         <is>
-          <t>Mitarbeiteranzahl des Herstellers (wird automatisch befüllt)</t>
+          <t>Number of employees at the manufacturer. (filled automatically)</t>
         </is>
       </c>
       <c r="R60" t="inlineStr">
@@ -5075,7 +5075,7 @@
       </c>
       <c r="Q61" s="64" t="inlineStr">
         <is>
-          <t>Welche Zertifizierungen muss der Hersteller nachweisen? (z. B. ISO 9001)</t>
+          <t>Which certifications must the manufacturer hold? (e.g. ISO 9001)</t>
         </is>
       </c>
       <c r="R61" t="inlineStr">
@@ -5122,7 +5122,7 @@
       </c>
       <c r="Q62" s="64" t="inlineStr">
         <is>
-          <t>Welche Sprache(n) muss der Hersteller für Support und Dokumentation beherrschen?</t>
+          <t>Which language(s) must the manufacturer support for service and documentation?</t>
         </is>
       </c>
       <c r="R62" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="Q63" s="64" t="inlineStr">
         <is>
-          <t>Hauptsitz des Herstellers (wird automatisch befüllt)</t>
+          <t>Manufacturer headquarters. (filled automatically)</t>
         </is>
       </c>
       <c r="R63" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="Q64" s="64" t="inlineStr">
         <is>
-          <t>Gründungsjahr des Herstellers (wird automatisch befüllt)</t>
+          <t>Manufacturer founding year. (filled automatically)</t>
         </is>
       </c>
       <c r="R64" t="inlineStr">
@@ -5415,7 +5415,7 @@
       </c>
       <c r="Q4" s="64" t="inlineStr">
         <is>
-          <t>Bis zu welcher Höhe muss das Gerät Lasten anheben? Maximale Entnahmehöhe im Regal angeben (mm; z. B. 10.000 mm = 10 m für Hochregal).</t>
+          <t>How high must the device lift loads? Enter the maximum pick height in the rack. (mm; e.g. 10,000 mm = 10 m for high-bay storage)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -5469,7 +5469,7 @@
       </c>
       <c r="Q5" s="64" t="inlineStr">
         <is>
-          <t>Wie hoch sind die niedrigsten Durchfahrten oder Türen im Betriebsbereich? (mm)</t>
+          <t>What is the height of the lowest doorways or passages in the operating area? (mm)</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -5516,7 +5516,7 @@
       </c>
       <c r="Q6" s="64" t="inlineStr">
         <is>
-          <t>Wird eine spezielle Gabelausführung benötigt? (z. B. Seitenschieber, Klammergreifer)</t>
+          <t>Is a special fork attachment required? (e.g. side-shift, clamp)</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -5563,7 +5563,7 @@
       </c>
       <c r="Q7" s="64" t="inlineStr">
         <is>
-          <t>Welcher Gabelabstand ist für die Ladungsträger erforderlich? (mm)</t>
+          <t>What fork spacing is required for the load carriers? (mm)</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -5605,7 +5605,7 @@
       </c>
       <c r="Q8" s="64" t="inlineStr">
         <is>
-          <t>Welcher Masttyp ist vorgesehen? (z. B. Duplex, Triplex, Vierstufig)</t>
+          <t>What mast type is intended? (e.g. duplex, triplex, quad)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -5662,7 +5662,7 @@
       </c>
       <c r="Q9" s="64" t="inlineStr">
         <is>
-          <t>Wie breit sind die schmalsten Fahrwege in Ihrer Anlage? Das AGV muss in dieser Gangbreite fahren können (mm).</t>
+          <t>How wide are the narrowest aisles in your facility? The AGV must manoeuvre within this width. (mm; e.g. 1,800 mm for narrow-aisle operation)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -5710,7 +5710,7 @@
       </c>
       <c r="Q10" s="64" t="inlineStr">
         <is>
-          <t>Ist VNA-Fähigkeit (Schmalgangbetrieb) erforderlich — oder explizit nicht gewünscht?</t>
+          <t>Is VNA (Very Narrow Aisle) capability required — or explicitly not desired?</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -5769,7 +5769,7 @@
       <c r="H12" s="52" t="n"/>
       <c r="Q12" s="64" t="inlineStr">
         <is>
-          <t>Welcher Antriebstyp ist vorgesehen? (z. B. Gegengewichtstapler, Schubmast, VNA)</t>
+          <t>What drive type is intended? (e.g. counterbalanced, reach truck, VNA)</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -5833,7 +5833,7 @@
       </c>
       <c r="Q14" s="64" t="inlineStr">
         <is>
-          <t>Wie präzise muss das AMR Lasten seitlich absetzen? (mm laterale Abweichung)</t>
+          <t>How precisely must the AMR deposit loads laterally? (mm)</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -5876,7 +5876,7 @@
       </c>
       <c r="Q15" s="64" t="inlineStr">
         <is>
-          <t>Wie präzise muss das AMR Lasten in der Tiefe absetzen? (mm)</t>
+          <t>How precisely must the AMR deposit loads in depth? (mm)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -5919,7 +5919,7 @@
       </c>
       <c r="Q16" s="64" t="inlineStr">
         <is>
-          <t>Wie präzise muss das AMR Lasten winkelgenau absetzen? (Grad)</t>
+          <t>How precisely must the AMR deposit loads angularly? (degrees)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -5973,7 +5973,7 @@
       </c>
       <c r="Q17" s="64" t="inlineStr">
         <is>
-          <t>Welche seitliche Präzision ist bei der Lastaufnahme erforderlich? (mm)</t>
+          <t>What lateral precision is required when picking up loads? (mm)</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -6016,7 +6016,7 @@
       </c>
       <c r="Q18" s="64" t="inlineStr">
         <is>
-          <t>Welche Tiefenpräzision ist bei der Kommissionierung erforderlich? (mm)</t>
+          <t>What depth precision is required during order picking? (mm)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -6059,7 +6059,7 @@
       </c>
       <c r="Q19" s="64" t="inlineStr">
         <is>
-          <t>Welche Winkelpräzision ist bei der Kommissionierung erforderlich? (Grad)</t>
+          <t>What angular precision is required during order picking? (degrees)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -6112,7 +6112,7 @@
       </c>
       <c r="Q21" s="64" t="inlineStr">
         <is>
-          <t>Müssen die Gabeln seitenverschiebbar oder schwimmend gelagert sein?</t>
+          <t>Must the forks be laterally shiftable or free-floating?</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -6156,7 +6156,7 @@
       <c r="I22" s="50" t="n"/>
       <c r="Q22" s="64" t="inlineStr">
         <is>
-          <t>Muss das Gerät Lasten übereinander stapeln können?</t>
+          <t>Must the device be able to stack loads on top of each other?</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -6198,7 +6198,7 @@
       </c>
       <c r="Q23" s="64" t="inlineStr">
         <is>
-          <t>Wie soll die Lastaufnahme erkannt werden?</t>
+          <t>How should load pickup be detected?</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -6241,7 +6241,7 @@
       </c>
       <c r="Q24" s="64" t="inlineStr">
         <is>
-          <t>Sind integrierte Barcode-Scanner für die Lastidentifikation erforderlich?</t>
+          <t>Are integrated barcode scanners for load identification required?</t>
         </is>
       </c>
       <c r="R24" t="inlineStr">
@@ -6279,7 +6279,7 @@
       </c>
       <c r="Q25" s="64" t="inlineStr">
         <is>
-          <t>Muss das AGV Bestände im Regal automatisch scannen können?</t>
+          <t>Must the AGV be able to automatically scan inventory in the racks?</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -6332,7 +6332,7 @@
       </c>
       <c r="Q27" s="64" t="inlineStr">
         <is>
-          <t>Muss das AGV Lasten in Lkw-Trailer einfahren und beladen können?</t>
+          <t>Must the AGV be able to enter and load truck trailers?</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -6375,7 +6375,7 @@
       </c>
       <c r="Q28" s="64" t="inlineStr">
         <is>
-          <t>Muss das AGV Lasten aus Lkw-Trailern entnehmen können?</t>
+          <t>Must the AGV be able to unload from truck trailers?</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -6432,7 +6432,7 @@
       </c>
       <c r="Q30" s="64" t="inlineStr">
         <is>
-          <t>Welches Führungskonzept soll das Regalfahrzeug im VNA-Bereich nutzen?</t>
+          <t>What guidance concept should the racking vehicle use in the VNA aisle?</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -6470,7 +6470,7 @@
       </c>
       <c r="Q31" s="64" t="inlineStr">
         <is>
-          <t>Ist ein Stromversorgungssystem über Schienenschleifer (Busbar) vorgesehen?</t>
+          <t>Is a rail-based power supply system (busbar) planned?</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="Q4" s="64" t="inlineStr">
         <is>
-          <t>Wie hoch ist das maximale Gesamtgewicht des Anhängerzuges? (kg; Summe aller Anhänger inkl. Ladung)</t>
+          <t>What is the maximum total weight of the train? (kg; sum of all trailers including load; e.g. 5,000 kg)</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -6734,7 +6734,7 @@
       </c>
       <c r="Q5" s="64" t="inlineStr">
         <is>
-          <t>Wie viele Anhänger müssen gleichzeitig gezogen werden können?</t>
+          <t>How many trailers must be able to be towed simultaneously?</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -6781,7 +6781,7 @@
       </c>
       <c r="Q6" s="64" t="inlineStr">
         <is>
-          <t>Welche Kupplungsart verwenden die vorhandenen oder geplanten Anhänger?</t>
+          <t>What coupling type do the existing or planned trailers use?</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -6832,7 +6832,7 @@
       </c>
       <c r="Q7" s="64" t="inlineStr">
         <is>
-          <t>Muss der Tugger Anhänger automatisch ankuppeln können?</t>
+          <t>Must the tugger be able to automatically couple trailers?</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -6875,7 +6875,7 @@
       </c>
       <c r="Q8" s="64" t="inlineStr">
         <is>
-          <t>Welche Positioniertoleranz ist beim automatischen Ankuppeln akzeptabel? (mm)</t>
+          <t>What positioning tolerance is acceptable for automatic coupling? (mm)</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -6917,7 +6917,7 @@
       </c>
       <c r="Q9" s="64" t="inlineStr">
         <is>
-          <t>Welche Zuganordnung ist vorgesehen? (z. B. Anhänger in Reihe, Karussellanordnung)</t>
+          <t>What train configuration is intended? (e.g. trailers in line, carousel)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -6959,7 +6959,7 @@
       </c>
       <c r="Q10" s="64" t="inlineStr">
         <is>
-          <t>Wie soll die Lastübergabe am Anhänger erfolgen?</t>
+          <t>How should the load handover at the trailer be performed?</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -7007,7 +7007,7 @@
       </c>
       <c r="Q12" s="64" t="inlineStr">
         <is>
-          <t>Welche Anhängertypen sollen verwendet werden?</t>
+          <t>Which trailer types will be used?</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -7057,7 +7057,7 @@
       </c>
       <c r="Q13" s="64" t="inlineStr">
         <is>
-          <t>Welche Lenktechnologie verwenden die Anhänger? (z. B. passive Lenkung, aktive Lenkung)</t>
+          <t>What steering technology do the trailers use? (e.g. passive steering, active steering)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -7114,7 +7114,7 @@
       </c>
       <c r="Q15" s="64" t="inlineStr">
         <is>
-          <t>Welche Art von Fahrstrecke ist geplant? (feste Route oder flexible Route)</t>
+          <t>What type of route is planned? (fixed route, flexible route)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -7156,7 +7156,7 @@
       </c>
       <c r="Q16" s="64" t="inlineStr">
         <is>
-          <t>Wie sollen Fahrrouten programmiert oder angepasst werden?</t>
+          <t>How should routes be programmed or adjusted?</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -7194,7 +7194,7 @@
       </c>
       <c r="Q17" s="64" t="inlineStr">
         <is>
-          <t>Wie sollen Kreuzungssituationen zwischen mehreren AGVs gehandhabt werden?</t>
+          <t>How should intersection situations between multiple AGVs be handled?</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -7248,7 +7248,7 @@
       </c>
       <c r="Q18" s="64" t="inlineStr">
         <is>
-          <t>Wie breit sind die schmalsten Fahrwege in Ihrer Anlage? Das AGV muss in dieser Gangbreite fahren können (mm).</t>
+          <t>How wide are the narrowest aisles in your facility? The AGV must manoeuvre within this width. (mm; e.g. 1,800 mm for narrow-aisle operation)</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="Q19" s="64" t="inlineStr">
         <is>
-          <t>Wie viel Platz steht in Kurven zur Verfügung? (mm; der Wenderadius des Fahrzeugs muss kleiner sein)</t>
+          <t>How much space is available for cornering? (mm; vehicle turning radius must be smaller)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -7356,7 +7356,7 @@
       </c>
       <c r="Q20" s="64" t="inlineStr">
         <is>
-          <t>Wie breit sind die schmalsten Durchfahrten im gesamten Fahrtbereich des Tuggers inkl. Anhänger? (mm)</t>
+          <t>How wide are the narrowest passages in the entire travel area including trailers? (mm)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -7556,7 +7556,7 @@
       </c>
       <c r="Q4" s="64" t="inlineStr">
         <is>
-          <t>Welche Arbeitsabläufe soll das AMR unterstützen?</t>
+          <t>What workflows should the AMR support?</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -7599,7 +7599,7 @@
       </c>
       <c r="Q5" s="64" t="inlineStr">
         <is>
-          <t>Ist ein physisches Gittersystem (z. B. Lagerroboter-Raster) Teil der Lösung?</t>
+          <t>Is a physical grid system (e.g. storage robot grid) part of the solution?</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -7645,7 +7645,7 @@
       </c>
       <c r="Q6" s="64" t="inlineStr">
         <is>
-          <t>Muss das AMR Lasten während der Fahrt drehen können?</t>
+          <t>Must the AMR be able to rotate loads during travel?</t>
         </is>
       </c>
       <c r="R6" t="inlineStr">
@@ -7692,7 +7692,7 @@
       </c>
       <c r="Q7" s="64" t="inlineStr">
         <is>
-          <t>Welcher Mechanismus soll das AMR zum Greifen oder Kommissionieren verwenden?</t>
+          <t>What mechanism should the AMR use for picking or gripping?</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -7756,7 +7756,7 @@
       </c>
       <c r="Q9" s="64" t="inlineStr">
         <is>
-          <t>Bis zu welcher Höhe muss das AMR Lasten oder Regale anheben? (mm)</t>
+          <t>How high must the AMR lift loads or shelving units? (mm)</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -7810,7 +7810,7 @@
       </c>
       <c r="Q10" s="64" t="inlineStr">
         <is>
-          <t>Wie viel Bodenfreiheit wird mindestens benötigt? (mm; z. B. für Bodenunebenheiten oder Schwellen)</t>
+          <t>What minimum ground clearance is required? (mm; e.g. for floor unevenness)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -7853,7 +7853,7 @@
       </c>
       <c r="Q11" s="64" t="inlineStr">
         <is>
-          <t>Muss das AMR mit pin-kompatiblen Lagerregalen arbeiten können?</t>
+          <t>Must the AMR work with pin-compatible storage racks?</t>
         </is>
       </c>
       <c r="R11" t="inlineStr">
@@ -7896,7 +7896,7 @@
       </c>
       <c r="Q12" s="64" t="inlineStr">
         <is>
-          <t>Muss das AMR Paletten ohne Gabelöffnungen (Vollpaletten) aufnehmen können?</t>
+          <t>Must the AMR be able to pick up pallets without fork openings?</t>
         </is>
       </c>
       <c r="R12" t="inlineStr">
@@ -7938,7 +7938,7 @@
       </c>
       <c r="Q13" s="64" t="inlineStr">
         <is>
-          <t>Welches Aufbaumodul ist erforderlich? (z. B. Förderband, Hubtisch, Greifarme)</t>
+          <t>What top module is required? (e.g. conveyor belt, lifting table, robotic arms)</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
@@ -7976,7 +7976,7 @@
       </c>
       <c r="Q14" s="64" t="inlineStr">
         <is>
-          <t>In welchem Höhenbereich muss das AMR Wagen oder Ladungsträger aufnehmen? (mm)</t>
+          <t>At what height range must the AMR pick up carts or carriers? (mm)</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -8040,7 +8040,7 @@
       </c>
       <c r="Q16" s="64" t="inlineStr">
         <is>
-          <t>Wie viel Platz steht für Drehbewegungen zur Verfügung? (mm; der Wendekreis des AMR muss kleiner sein)</t>
+          <t>How much space is available for turning movements? (mm; turning radius must be smaller)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -8099,7 +8099,7 @@
       </c>
       <c r="Q19" s="64" t="inlineStr">
         <is>
-          <t>Welche Tiefenpräzision ist bei der Kommissionierung erforderlich? (mm)</t>
+          <t>What depth precision is required during order picking? (mm)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="Q20" s="64" t="inlineStr">
         <is>
-          <t>Welche Winkelpräzision ist bei der Kommissionierung erforderlich? (Grad)</t>
+          <t>What angular precision is required during order picking? (degrees)</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">
@@ -8185,7 +8185,7 @@
       </c>
       <c r="Q21" s="64" t="inlineStr">
         <is>
-          <t>Wie präzise muss das AMR Lasten seitlich absetzen? (mm laterale Abweichung)</t>
+          <t>How precisely must the AMR deposit loads laterally? (mm)</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -8228,7 +8228,7 @@
       </c>
       <c r="Q22" s="64" t="inlineStr">
         <is>
-          <t>Wie präzise muss das AMR Lasten in der Tiefe absetzen? (mm)</t>
+          <t>How precisely must the AMR deposit loads in depth? (mm)</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -8271,7 +8271,7 @@
       </c>
       <c r="Q23" s="64" t="inlineStr">
         <is>
-          <t>Wie präzise muss das AMR Lasten winkelgenau absetzen? (Grad)</t>
+          <t>How precisely must the AMR deposit loads angularly? (degrees)</t>
         </is>
       </c>
       <c r="R23" t="inlineStr">
@@ -8328,7 +8328,7 @@
       </c>
       <c r="Q25" s="64" t="inlineStr">
         <is>
-          <t>Welches Lagersystem soll das AMR bedienen?</t>
+          <t>What storage system should the AMR serve?</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -8382,7 +8382,7 @@
       </c>
       <c r="Q26" s="64" t="inlineStr">
         <is>
-          <t>Wie hoch sind die Lagerregale, die das AMR bedienen soll? (mm)</t>
+          <t>How high are the storage racks the AMR should serve? (mm)</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -8425,7 +8425,7 @@
       </c>
       <c r="Q27" s="64" t="inlineStr">
         <is>
-          <t>Wie groß ist der Grundriss der Lagereinheiten? (mm)</t>
+          <t>What is the footprint of the storage units? (mm)</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -8468,7 +8468,7 @@
       </c>
       <c r="Q28" s="64" t="inlineStr">
         <is>
-          <t>Wie groß ist die minimale Lagerfläche für das AMR-System? (m²)</t>
+          <t>What is the minimum storage area for the AMR system? (m²)</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -8541,7 +8541,7 @@
       </c>
       <c r="Q30" s="64" t="inlineStr">
         <is>
-          <t>Wie viele Kommissionierungen pro Stunde sind mindestens erforderlich?</t>
+          <t>How many picks per hour are required as a minimum?</t>
         </is>
       </c>
       <c r="R30" t="inlineStr">
@@ -8583,7 +8583,7 @@
       </c>
       <c r="Q31" s="64" t="inlineStr">
         <is>
-          <t>Auf welcher Basis wird der Durchsatz gemessen?</t>
+          <t>On what basis is throughput measured?</t>
         </is>
       </c>
       <c r="R31" t="inlineStr">
@@ -8626,7 +8626,7 @@
       </c>
       <c r="Q32" s="64" t="inlineStr">
         <is>
-          <t>Wie viele AMRs müssen gleichzeitig an einer Station arbeiten können?</t>
+          <t>How many AMRs must be able to work at one station simultaneously?</t>
         </is>
       </c>
       <c r="R32" t="inlineStr">
@@ -8669,7 +8669,7 @@
       </c>
       <c r="Q33" s="64" t="inlineStr">
         <is>
-          <t>Wie viele Auftragspositionen sollen pro Fahrt abgearbeitet werden?</t>
+          <t>How many order lines should be processed per trip?</t>
         </is>
       </c>
       <c r="R33" t="inlineStr">
@@ -8707,7 +8707,7 @@
       </c>
       <c r="Q34" s="64" t="inlineStr">
         <is>
-          <t>Sollen AMRs verschiedene Aufgabentypen im Wechsel abarbeiten können?</t>
+          <t>Should AMRs be able to alternate between different task types?</t>
         </is>
       </c>
       <c r="R34" t="inlineStr">
@@ -8750,7 +8750,7 @@
       </c>
       <c r="Q35" s="64" t="inlineStr">
         <is>
-          <t>Wie wichtig ist eine hohe Lagerplatzdichte für Ihr System?</t>
+          <t>How important is high storage density for your system?</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -8788,7 +8788,7 @@
       </c>
       <c r="Q36" s="64" t="inlineStr">
         <is>
-          <t>Muss die Arbeitshöhe für Mitarbeiter ergonomisch anpassbar sein?</t>
+          <t>Must the working height be ergonomically adjustable for operators?</t>
         </is>
       </c>
       <c r="R36" t="inlineStr">
@@ -8826,7 +8826,7 @@
       </c>
       <c r="Q37" s="64" t="inlineStr">
         <is>
-          <t>Ist ein Display oder Bedienpanel am Fahrzeug erforderlich?</t>
+          <t>Is a display or control panel on the vehicle required?</t>
         </is>
       </c>
       <c r="R37" t="inlineStr">
@@ -8864,7 +8864,7 @@
       </c>
       <c r="Q38" s="64" t="inlineStr">
         <is>
-          <t>Muss die Anzeige am Fahrzeug mehrsprachig sein?</t>
+          <t>Must the display support multiple languages?</t>
         </is>
       </c>
       <c r="R38" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="Q39" s="64" t="inlineStr">
         <is>
-          <t>Sind spielerische Motivationselemente für Mitarbeiter gewünscht?</t>
+          <t>Are gamification elements for operator motivation desired?</t>
         </is>
       </c>
       <c r="R39" t="inlineStr">
@@ -8959,7 +8959,7 @@
       </c>
       <c r="Q41" s="64" t="inlineStr">
         <is>
-          <t>Welcher Behältertyp soll auf dem AMR transportiert werden?</t>
+          <t>What container type should be transported on the AMR?</t>
         </is>
       </c>
       <c r="R41" t="inlineStr">
@@ -9002,7 +9002,7 @@
       </c>
       <c r="Q42" s="64" t="inlineStr">
         <is>
-          <t>Wie viele Behälter soll das AMR gleichzeitig transportieren?</t>
+          <t>How many containers should the AMR transport simultaneously?</t>
         </is>
       </c>
       <c r="R42" t="inlineStr">
@@ -9058,7 +9058,7 @@
       </c>
       <c r="Q44" s="64" t="inlineStr">
         <is>
-          <t>Ist eine direkte native Integration mit dem Warehouse-Management-System erforderlich?</t>
+          <t>Is a direct native integration with the Warehouse Management System required?</t>
         </is>
       </c>
       <c r="R44" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -2596,9 +2596,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -2640,8 +2640,6 @@
           <t>Fields applying to ALL AGV/AMR subtypes — written into base_model_extensions for every base model. Universal fields are consolidated here: power, gradient, floor flatness, stop accuracy, station applications, fleet size. ● = added/changed by Claude. v0.7: navigation_type + infrastructure_required → Cond. K.O.; Company/Product fields added.. Colour = level (red K.O. · orange Cond. K.O. · yellow Scoring · green Context).</t>
         </is>
       </c>
-      <c r="C1" s="64" t="n"/>
-      <c r="G1" s="64" t="n"/>
       <c r="Q1" s="64" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="57">
@@ -2742,8 +2740,6 @@
           <t>── NAVIGATION &amp; INFRASTRUCTURE</t>
         </is>
       </c>
-      <c r="C3" s="64" t="n"/>
-      <c r="G3" s="64" t="n"/>
       <c r="Q3" s="64" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="57">
@@ -2782,9 +2778,6 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
-      <c r="O4" t="b">
-        <v>1</v>
-      </c>
       <c r="Q4" s="64" t="inlineStr">
         <is>
           <t>What navigation type is intended or allowed? (e.g. Natural Feature/SLAM, magnetic tape, QR code)</t>
@@ -2972,8 +2965,6 @@
           <t>── LOAD HANDLING</t>
         </is>
       </c>
-      <c r="C9" s="64" t="n"/>
-      <c r="G9" s="64" t="n"/>
       <c r="Q9" s="64" t="n"/>
     </row>
     <row r="10" ht="15" customHeight="1" s="57">
@@ -3019,9 +3010,6 @@
       <c r="N10" t="n">
         <v>50000</v>
       </c>
-      <c r="O10" t="b">
-        <v>1</v>
-      </c>
       <c r="Q10" s="64" t="inlineStr">
         <is>
           <t>What is the maximum load weight per carrier? The AGV must be able to carry at least this weight.</t>
@@ -3129,8 +3117,6 @@
           <t>── DIMENSIONS &amp; ENVIRONMENT</t>
         </is>
       </c>
-      <c r="C13" s="64" t="n"/>
-      <c r="G13" s="64" t="n"/>
       <c r="Q13" s="64" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="57">
@@ -3165,9 +3151,6 @@
           <t>Top travel speed (capture rated/unloaded if only one given). Source: spec table. Implies cycle time; check safety-derated speed too.</t>
         </is>
       </c>
-      <c r="O14" t="b">
-        <v>1</v>
-      </c>
       <c r="Q14" s="64" t="inlineStr">
         <is>
           <t>What maximum speed should the AGV achieve? (m/s)</t>
@@ -3628,8 +3611,6 @@
           <t>── ACCURACY</t>
         </is>
       </c>
-      <c r="C24" s="64" t="n"/>
-      <c r="G24" s="64" t="n"/>
       <c r="Q24" s="64" t="n"/>
     </row>
     <row r="25" ht="15" customHeight="1" s="57">
@@ -3695,8 +3676,6 @@
           <t>── POWER</t>
         </is>
       </c>
-      <c r="C26" s="64" t="n"/>
-      <c r="G26" s="64" t="n"/>
       <c r="Q26" s="64" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="57">
@@ -3784,9 +3763,6 @@
       <c r="K28" t="n">
         <v>8</v>
       </c>
-      <c r="O28" t="b">
-        <v>1</v>
-      </c>
       <c r="Q28" s="64" t="inlineStr">
         <is>
           <t>How many hours of operating time per charge are required as a minimum? (h)</t>
@@ -3876,9 +3852,6 @@
           <t>bool</t>
         </is>
       </c>
-      <c r="O30" t="b">
-        <v>1</v>
-      </c>
       <c r="Q30" s="64" t="inlineStr">
         <is>
           <t>Must the AGV autonomously navigate to the charging station and charge itself?</t>
@@ -3934,8 +3907,6 @@
           <t>── SAFETY &amp; CERTIFICATION</t>
         </is>
       </c>
-      <c r="C32" s="64" t="n"/>
-      <c r="G32" s="64" t="n"/>
       <c r="Q32" s="64" t="n"/>
     </row>
     <row r="33" ht="15" customHeight="1" s="57">
@@ -4086,8 +4057,6 @@
           <t>── FLEET &amp; INTEGRATION</t>
         </is>
       </c>
-      <c r="C36" s="64" t="n"/>
-      <c r="G36" s="64" t="n"/>
       <c r="Q36" s="64" t="n"/>
     </row>
     <row r="37" ht="15" customHeight="1" s="57">
@@ -4219,9 +4188,6 @@
           <t>bool_cond</t>
         </is>
       </c>
-      <c r="O39" t="b">
-        <v>1</v>
-      </c>
       <c r="Q39" s="64" t="inlineStr">
         <is>
           <t>Must the AGV support the VDA 5050 interface standard?</t>
@@ -4446,8 +4412,6 @@
           <t>── STATIONS</t>
         </is>
       </c>
-      <c r="C45" s="64" t="n"/>
-      <c r="G45" s="64" t="n"/>
       <c r="Q45" s="64" t="n"/>
     </row>
     <row r="46" ht="15" customHeight="1" s="57">
@@ -4503,8 +4467,6 @@
           <t>── COMMERCIAL</t>
         </is>
       </c>
-      <c r="C47" s="64" t="n"/>
-      <c r="G47" s="64" t="n"/>
       <c r="Q47" s="64" t="n"/>
     </row>
     <row r="48" ht="15" customHeight="1" s="57">
@@ -4550,9 +4512,6 @@
       <c r="K48" t="n">
         <v>20</v>
       </c>
-      <c r="O48" t="b">
-        <v>1</v>
-      </c>
       <c r="Q48" s="64" t="inlineStr">
         <is>
           <t>Number of reference projects from the supplier. (filled automatically)</t>
@@ -4610,9 +4569,6 @@
       <c r="L49" t="n">
         <v>52</v>
       </c>
-      <c r="O49" t="b">
-        <v>1</v>
-      </c>
       <c r="Q49" s="64" t="inlineStr">
         <is>
           <t>How many weeks lead time until commissioning is acceptable?</t>
@@ -4660,9 +4616,6 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
-      <c r="O50" t="b">
-        <v>1</v>
-      </c>
       <c r="Q50" s="64" t="inlineStr">
         <is>
           <t>In which countries or regions is service and support required?</t>
@@ -4765,8 +4718,6 @@
           <t>── CONTEXT</t>
         </is>
       </c>
-      <c r="C53" s="64" t="n"/>
-      <c r="G53" s="64" t="n"/>
       <c r="Q53" s="64" t="n"/>
     </row>
     <row r="54" ht="15" customHeight="1" s="57">
@@ -5261,8 +5212,6 @@
           <t>Forklift-specific fields only (universal fields live in SHARED). Pick/drop accuracy ordered lateral·depth·angle. ● = changed/added by Claude. Combine with SHARED.</t>
         </is>
       </c>
-      <c r="C1" s="64" t="n"/>
-      <c r="G1" s="64" t="n"/>
       <c r="Q1" s="64" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="57">
@@ -5363,8 +5312,6 @@
           <t>── MAST &amp; LIFTING</t>
         </is>
       </c>
-      <c r="C3" s="64" t="n"/>
-      <c r="G3" s="64" t="n"/>
       <c r="Q3" s="64" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="57">
@@ -5410,9 +5357,6 @@
       <c r="N4" t="n">
         <v>30</v>
       </c>
-      <c r="O4" t="b">
-        <v>1</v>
-      </c>
       <c r="Q4" s="64" t="inlineStr">
         <is>
           <t>How high must the device lift loads? Enter the maximum pick height in the rack. (mm; e.g. 10,000 mm = 10 m for high-bay storage)</t>
@@ -5657,9 +5601,6 @@
       <c r="N9" t="n">
         <v>5</v>
       </c>
-      <c r="O9" t="b">
-        <v>1</v>
-      </c>
       <c r="Q9" s="64" t="inlineStr">
         <is>
           <t>How wide are the narrowest aisles in your facility? The AGV must manoeuvre within this width. (mm; e.g. 1,800 mm for narrow-aisle operation)</t>
@@ -5725,8 +5666,6 @@
           <t>── DRIVE</t>
         </is>
       </c>
-      <c r="C11" s="64" t="n"/>
-      <c r="G11" s="64" t="n"/>
       <c r="Q11" s="64" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="57">
@@ -5784,8 +5723,6 @@
           <t>── PICK &amp; DROP (order: lateral · depth · angle)</t>
         </is>
       </c>
-      <c r="C13" s="64" t="n"/>
-      <c r="G13" s="64" t="n"/>
       <c r="Q13" s="64" t="n"/>
     </row>
     <row r="14" ht="15" customHeight="1" s="57">
@@ -6074,8 +6011,6 @@
           <t>── HANDLING CAPABILITY</t>
         </is>
       </c>
-      <c r="C20" s="64" t="n"/>
-      <c r="G20" s="64" t="n"/>
       <c r="Q20" s="64" t="n"/>
     </row>
     <row r="21" ht="15" customHeight="1" s="57">
@@ -6294,8 +6229,6 @@
           <t>── TRAILER / DOCK</t>
         </is>
       </c>
-      <c r="C26" s="64" t="n"/>
-      <c r="G26" s="64" t="n"/>
       <c r="Q26" s="64" t="n"/>
     </row>
     <row r="27" ht="15" customHeight="1" s="57">
@@ -6390,8 +6323,6 @@
           <t>── AGV (RAIL/WIRE) ONLY</t>
         </is>
       </c>
-      <c r="C29" s="64" t="n"/>
-      <c r="G29" s="64" t="n"/>
       <c r="Q29" s="64" t="n"/>
     </row>
     <row r="30" ht="15" customHeight="1" s="57">
@@ -6529,8 +6460,6 @@
           <t>Tugger-specific fields, deepened from Vecna / DS Automotion / LKE research — trailer compatibility &amp; steering tech, aisle width, turning radius, auto-hitch + tolerance. ● = added by Claude. Combine with SHARED. v0.7: auto_hitch → Cond. K.O.; tugger_min_aisle_width_mm added.</t>
         </is>
       </c>
-      <c r="C1" s="64" t="n"/>
-      <c r="G1" s="64" t="n"/>
       <c r="Q1" s="64" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="57">
@@ -6631,8 +6560,6 @@
           <t>── TOWING</t>
         </is>
       </c>
-      <c r="C3" s="64" t="n"/>
-      <c r="G3" s="64" t="n"/>
       <c r="Q3" s="64" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="57">
@@ -6974,8 +6901,6 @@
           <t>── TRAILER / CART</t>
         </is>
       </c>
-      <c r="C11" s="64" t="n"/>
-      <c r="G11" s="64" t="n"/>
       <c r="Q11" s="64" t="n"/>
     </row>
     <row r="12" ht="15" customHeight="1" s="57">
@@ -7072,8 +6997,6 @@
           <t>── ROUTING &amp; MANEUVERING</t>
         </is>
       </c>
-      <c r="C14" s="64" t="n"/>
-      <c r="G14" s="64" t="n"/>
       <c r="Q14" s="64" t="n"/>
     </row>
     <row r="15" ht="15" customHeight="1" s="57">
@@ -7412,8 +7335,6 @@
           <t>Unified free-navigating AMR sheet — merges the former Undercarriage + Goods-to-Person + Picking subtypes into ONE category (same hardware, different workflow). The workflow is now a PROPERTY (workflow_capability, grid_required, rotation_capable, picking_mechanism), not a hard category. Overlapping throughput fields consolidated into throughput_picks_per_hour + throughput_basis. ● = added/changed by Claude. Combine with SHARED.</t>
         </is>
       </c>
-      <c r="C1" s="64" t="n"/>
-      <c r="G1" s="64" t="n"/>
       <c r="Q1" s="64" t="n"/>
     </row>
     <row r="2" ht="30" customHeight="1" s="57">
@@ -7514,8 +7435,6 @@
           <t>── WORKFLOW MODE (property-based — replaces the old Undercarriage / G2P / Picking split)</t>
         </is>
       </c>
-      <c r="C3" s="64" t="n"/>
-      <c r="G3" s="64" t="n"/>
       <c r="Q3" s="64" t="n"/>
     </row>
     <row r="4" ht="15" customHeight="1" s="57">
@@ -7707,8 +7626,6 @@
           <t>── LOAD HANDLING &amp; LIFT</t>
         </is>
       </c>
-      <c r="C8" s="64" t="n"/>
-      <c r="G8" s="64" t="n"/>
       <c r="Q8" s="64" t="n"/>
     </row>
     <row r="9" ht="15" customHeight="1" s="57">
@@ -7991,8 +7908,6 @@
           <t>── MOVEMENT</t>
         </is>
       </c>
-      <c r="C15" s="64" t="n"/>
-      <c r="G15" s="64" t="n"/>
       <c r="Q15" s="64" t="n"/>
     </row>
     <row r="16" ht="15" customHeight="1" s="57">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -904,7 +904,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S11"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1451,6 +1451,58 @@
       <c r="R11" t="inlineStr">
         <is>
           <t>05acd6db-ed2e-46e3-a3e6-ebddcaeea044</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>agv_type</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>@SCOPE_CANONICAL_NAMES</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>K.O.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Product</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>AGV/AMR category. Output exactly one of the allowed values. Hard K.O.: Forklift AGV never matches Tugger or AMR.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>KO_IF_NEQ</t>
+        </is>
+      </c>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>display</t>
+        </is>
+      </c>
+      <c r="Q12" t="inlineStr">
+        <is>
+          <t>What AGV type is required? (automatically detected from the document)</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>325dd61d-f828-4639-a128-fd5e1a1a3728</t>
         </is>
       </c>
     </row>
@@ -4149,7 +4201,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H6"/>
+  <dimension ref="A1:N7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4193,6 +4245,36 @@
           <t>classification_keywords</t>
         </is>
       </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>canonical_name</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>keywords</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>variants</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
+        <is>
+          <t>vna_applicable</t>
+        </is>
+      </c>
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>scoring_bucket</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>vna_hint</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -4269,6 +4351,43 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>* "VNA" → AGV stores/retrieves in very narrow aisles (&lt;2m), lifts to tall racking (&gt;8m), high-bay warehouse. ONLY classify as VNA if the tender explicitly requires VNA capability for the AGVs being procured. If VNA racking is mentioned as existing infrastructure, historical context, or out-of-scope aisles not covered by this tender — do NOT classify as VNA. Signals: aisle&lt;2m, lift&gt;8m, high-bay, VNA keyword
+* "Very Narrow Aisle" → Same as VNA
+* "Reach Truck" → AGV picks/places in medium-width racking aisles (2–3m), lift 4–8m. Signals: 2–3m aisle, racking, lift 4–8m
+* "Counterbalanced" → AGV transports pallets on wide aisles (≥3m) or open floor between fixed transfer stations, floor-level pickup/deposit. USE THIS for heavy pallet transport (&gt;1000 kg) in F&amp;B, food production, or manufacturing environments — even when MES or OPC-UA integration is mentioned. The presence of filling lines or MES does NOT imply Mobile AMR if payload is heavy. Signals: ≥3m aisle, floor transport, transfer stations, warehouse/logistics, heavy pallet (&gt;1000 kg)
+* "Forklift" → Generic forklift AGV</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>Forklift AGV</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>vna, very narrow aisle, reach truck, schmalgangstapler, counterbalanced, forklift, stapler, gabelstapler, forklift agv, agv</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>vna, very narrow aisle, reach truck, counterbalanced, forklift, forklift agv, agv</t>
+        </is>
+      </c>
+      <c r="L4" t="b">
+        <v>1</v>
+      </c>
+      <c r="M4" t="inlineStr">
+        <is>
+          <t>forklift_specific</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>VNA (very narrow aisle) operation is required.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -4296,6 +4415,31 @@
           <t>✓</t>
         </is>
       </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>* "Tugger" → AGV tows a train of trolleys/trailers without lifting; no direct pallet fork interface. Signals: trailer train, towing, milk run</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>Tugger AGV</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>tugger, schlepper, routenzug, milk run, towing, anhaenger, tugger agv</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>tugger, tugger agv</t>
+        </is>
+      </c>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>tugger_specific</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -4321,6 +4465,69 @@
       <c r="F6" t="inlineStr">
         <is>
           <t>✓</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>* "Mobile AMR" → Autonomous robot in PRODUCTION or MANUFACTURING environment (filling lines, assembly, processing), or with conveyor/shelf top modules, SLAM navigation, dispatched from MES/WMS. ONLY use for LIGHT payloads (typically &lt;1000 kg). If payload &gt;1000 kg or if the task is heavy pallet transport → use Forklift AGV instead. Signals: production, filling lines, manufacturing, SLAM, MES — BUT only if payload &lt;1000 kg
+* "Underride AMR" → Robot slides under carts/dollies and lifts them a few cm for transport. Signals: underride, dolly, cart</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>Mobile AMR</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>amr, mobile robot, fahrroboter, autonomer, goods-to-person, goods to person, underride amr, unterfahrfahrzeug, underride, autonomous mobile robot</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>amr, mobile amr, underride, underride amr, autonomous mobile robot</t>
+        </is>
+      </c>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>amr_specific</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>FoodBev:Refrigeration</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>*</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Refrigeration Shared</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>✓</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>* "Industrial Refrigeration" → Industrial refrigeration system for food &amp; beverage: process cooling, cold storage, or deep-freeze applications. Keywords: Kälteanlage, Kältetechnik, refrigeration, industrial cooling, cold store, deep freeze, blast freezer.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>Industrial Refrigeration</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>Process Cooling, Cold Store, Deep Freeze</t>
         </is>
       </c>
     </row>
@@ -5253,9 +5460,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -5268,7 +5475,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S54"/>
+  <dimension ref="A1:T53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="57" min="1" max="1"/>
@@ -7300,58 +7507,7 @@
       </c>
       <c r="Q53" s="64" t="n"/>
     </row>
-    <row r="54" ht="15" customHeight="1" s="57">
-      <c r="A54" s="39" t="inlineStr">
-        <is>
-          <t>agv_type</t>
-        </is>
-      </c>
-      <c r="B54" s="39" t="inlineStr">
-        <is>
-          <t>Dropdown</t>
-        </is>
-      </c>
-      <c r="C54" s="71" t="inlineStr">
-        <is>
-          <t>Forklift AGV | Tugger AGV | Mobile AMR</t>
-        </is>
-      </c>
-      <c r="E54" s="40" t="inlineStr">
-        <is>
-          <t>K.O.</t>
-        </is>
-      </c>
-      <c r="F54" s="41" t="inlineStr">
-        <is>
-          <t>Product</t>
-        </is>
-      </c>
-      <c r="G54" s="71" t="inlineStr">
-        <is>
-          <t>AGV/AMR category. Output exactly one of the allowed values. Hard K.O.: Forklift AGV never matches Tugger or AMR.</t>
-        </is>
-      </c>
-      <c r="H54" s="52" t="inlineStr">
-        <is>
-          <t>KO_IF_NEQ</t>
-        </is>
-      </c>
-      <c r="P54" t="inlineStr">
-        <is>
-          <t>display</t>
-        </is>
-      </c>
-      <c r="Q54" s="64" t="inlineStr">
-        <is>
-          <t>What AGV type is required? (automatically detected from the document)</t>
-        </is>
-      </c>
-      <c r="R54" t="inlineStr">
-        <is>
-          <t>325dd61d-f828-4639-a128-fd5e1a1a3728</t>
-        </is>
-      </c>
-    </row>
+    <row r="54" ht="15" customHeight="1" s="57"/>
     <row r="55" ht="15" customHeight="1" s="57"/>
     <row r="56" ht="15" customHeight="1" s="57"/>
     <row r="57" ht="15" customHeight="1" s="57"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -18,6 +18,7 @@
     <sheet name="Representatives" sheetId="10" state="visible" r:id="rId10"/>
     <sheet name="Vehicle Types" sheetId="11" state="visible" r:id="rId11"/>
     <sheet name="Field Fallbacks" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="FoodBev_Refrigeration" sheetId="13" state="visible" r:id="rId13"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="0" fullCalcOnLoad="1" iterateDelta="0.0001"/>
@@ -904,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T12"/>
+  <dimension ref="A1:S12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2649,6 +2650,660 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:S14"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1">
+      <c r="A1" t="inlineStr">
+        <is>
+          <t>Fields applying to Industrial Refrigeration (FoodBev domain) — written into base_model_extensions. 12 IK fields: 6 KO + 6 Cond. K.O. Colour = level (red K.O. · orange Cond. K.O.).</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Field Name</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Data Type</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>Allowed Values</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Unit</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>Level</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>Entity</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>LLM Hint</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>Matching Operator</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>Scoring Weight</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>Score Function</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>Score Threshold A</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>Score Threshold B</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>Plausibility Min</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>Plausibility Max</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>result_card</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>Display Mode</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
+          <t>UI Hint</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>UUID</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>Value if Null</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>served_categories</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Multi-Select</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>@SCOPE_VARIANTS:FoodBev:Refrigeration</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>K.O.</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>Extract ALL categories of refrigeration applications this supplier can serve. Do NOT assume from product name alone — extract only if stated explicitly. NULL RULE: if not explicitly stated, return null.</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>KO_SUBSET</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>23992ff7-c679-4328-971a-e0ad5700af80</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>cooling_capacity_kw</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>kW</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>K.O.</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Extract the MAXIMUM total cooling capacity in kW. Use the highest stated value. Do NOT convert from tons of refrigeration unless the document provides an explicit conversion. NULL RULE: return null if no explicit kW or TR figure is found.</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>KO_IF_LT</t>
+        </is>
+      </c>
+      <c r="M4" t="n">
+        <v>1</v>
+      </c>
+      <c r="N4" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>b8e6446a-07dd-4414-91c5-55d2646651b8</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>temperature_min_celsius</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>°C</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>K.O.</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Extract the MINIMUM evaporation or supply temperature the system can achieve in °C. Use the lowest (most negative) stated temperature target. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>KO_IF_GT</t>
+        </is>
+      </c>
+      <c r="M5" t="n">
+        <v>-60</v>
+      </c>
+      <c r="N5" t="n">
+        <v>15</v>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>833fb224-f218-4b28-8719-591a0ba86483</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>refrigerant_types</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Multi-Select</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>R717|R744|R290|R134a|R32|R404A|R452A</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>K.O.</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Extract ALL refrigerant types supported by this system. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>KO_SUBSET</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>59b9c33b-833a-4026-8061-2fab3a68de0c</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>certifications_ik</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Multi-Select</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>PED|ATEX|EN 378|F-Gas</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>K.O.</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Extract ALL relevant certifications held by this system. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>KO_SUBSET</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>c7989fc1-f256-4159-9c4c-ae3f481836ff</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>cop_efficiency</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>K.O.</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Extract the COP (Coefficient of Performance) at rated conditions. Use the highest stated COP. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>KO_IF_LT</t>
+        </is>
+      </c>
+      <c r="M8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="N8" t="n">
+        <v>15</v>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>b5204d0e-9069-4f9b-844a-b464bf2c2ef7</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>cooling_medium</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Dropdown</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>glycol|water|direct</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>Cond. K.O.</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Extract the cooling medium used: glycol circuit, water, or direct expansion. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>KO_IF_NEQ</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>80fb3a63-341f-47b0-85ec-b41c8169f7af</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>temperature_stability_k</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>K</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>Cond. K.O.</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Extract the maximum temperature fluctuation tolerance in Kelvin. Lower is better. NULL RULE: return null if no explicit tolerance value is stated.</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>KO_IF_GT</t>
+        </is>
+      </c>
+      <c r="M10" t="n">
+        <v>0.01</v>
+      </c>
+      <c r="N10" t="n">
+        <v>10</v>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>d4acded7-017e-4328-a2f4-115095a717b1</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>room_volume_m3_max</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>m³</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>Cond. K.O.</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Extract the MAXIMUM room volume in m³ this system can handle. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>KO_IF_LT</t>
+        </is>
+      </c>
+      <c r="M11" t="n">
+        <v>1</v>
+      </c>
+      <c r="N11" t="n">
+        <v>1000000</v>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>fde5ac60-1669-4543-89ec-03e02a2930b4</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>humidity_control_capable</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>Boolean</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>Cond. K.O.</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Does this system provide active humidity control? Only mark true if explicitly confirmed. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>KO_BOOL_REQUIRED</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>b6921aa9-6d37-4432-9e26-b0b321052a07</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>blast_freeze_capacity_kg_h</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>kg/h</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>Cond. K.O.</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Extract the blast freezing throughput capacity in kg/h. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>KO_IF_LT</t>
+        </is>
+      </c>
+      <c r="M13" t="n">
+        <v>1</v>
+      </c>
+      <c r="N13" t="n">
+        <v>100000</v>
+      </c>
+      <c r="R13" t="inlineStr">
+        <is>
+          <t>fb9c7834-e48d-40d0-a0ef-4d5e8d1d75d2</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>pulldown_time_h</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>Float</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>h</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>Cond. K.O.</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Base Model</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Extract the required pulldown time in hours (time to reach target temperature). Lower is better for supplier. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>KO_IF_GT</t>
+        </is>
+      </c>
+      <c r="M14" t="n">
+        <v>0.1</v>
+      </c>
+      <c r="N14" t="n">
+        <v>48</v>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>265424b5-ee01-4bc4-9c3f-072d53ff64dd</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -4201,7 +4856,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4273,6 +4928,11 @@
       <c r="N1" t="inlineStr">
         <is>
           <t>vna_hint</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>variant_guide_json</t>
         </is>
       </c>
     </row>
@@ -4510,6 +5170,11 @@
           <t>Refrigeration Shared</t>
         </is>
       </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>FoodBev_Refrigeration</t>
+        </is>
+      </c>
       <c r="F7" t="inlineStr">
         <is>
           <t>✓</t>
@@ -4525,9 +5190,19 @@
           <t>Industrial Refrigeration</t>
         </is>
       </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>kälteanlage, kältetechnik, refrigeration, industrial cooling, cold store, deep freeze, blast freezer, prozesskühlung, tiefkühlung, kühlhaus</t>
+        </is>
+      </c>
       <c r="K7" t="inlineStr">
         <is>
           <t>Process Cooling, Cold Store, Deep Freeze</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>{"Process Cooling": "System actively cools process media (glycol circuits, milk, fermentation tanks, process water) in food or beverage production. Temperature range typically above freezing (+2°C to +15°C). Signals: Prozesskühlung, Brauerei, Milchkühlung, Gärung, process water, glycol chiller", "Cold Store": "System maintains a refrigerated room or warehouse for fresh product storage. Temperature range above freezing (+0°C to +8°C). Signals: Kühllager, Kühlhaus, cold store, cold room, fresh produce storage, Frischwarenlager", "Deep Freeze": "System freezes or maintains frozen products at temperatures well below freezing (-18°C to -40°C). Includes blast freezers and deep-freeze warehouses. Signals: Tiefkühlung, Tiefkühlanlage, Schockfrostung, blast freezer, deep freeze, frozen storage, Gefrieranlage"}</t>
         </is>
       </c>
     </row>
@@ -5460,9 +6135,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -5475,7 +6150,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:T53"/>
+  <dimension ref="A1:S53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="57" min="1" max="1"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -1458,7 +1458,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>agv_type</t>
+          <t>product_type</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -4654,7 +4654,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>agv_type</t>
+          <t>product_type</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4794,7 +4794,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>agv_type</t>
+          <t>product_type</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -6135,8 +6135,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -9641,7 +9641,7 @@
       </c>
       <c r="G4" s="68" t="inlineStr">
         <is>
-          <t>Total towed load in kg. [TUGGER ONLY] — output null unless required_agv_type is 'Tugger AGV'. Source: 'Schleppkraft / towing capacity'.</t>
+          <t>Total towed load in kg. [TUGGER ONLY] — output null unless required_product_type is 'Tugger AGV'. Source: 'Schleppkraft / towing capacity'.</t>
         </is>
       </c>
       <c r="H4" s="52" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -2979,6 +2979,11 @@
           <t>KO_SUBSET</t>
         </is>
       </c>
+      <c r="Q7" t="inlineStr">
+        <is>
+          <t>Required safety certifications for the refrigeration system (e.g. EN 378, PED, ATEX for explosive atmospheres, F-Gas regulation)</t>
+        </is>
+      </c>
       <c r="R7" t="inlineStr">
         <is>
           <t>c7989fc1-f256-4159-9c4c-ae3f481836ff</t>
@@ -2996,6 +3001,11 @@
           <t>Float</t>
         </is>
       </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>COP</t>
+        </is>
+      </c>
       <c r="E8" t="inlineStr">
         <is>
           <t>K.O.</t>
@@ -3021,6 +3031,11 @@
       </c>
       <c r="N8" t="n">
         <v>15</v>
+      </c>
+      <c r="Q8" t="inlineStr">
+        <is>
+          <t>Minimum Coefficient of Performance required — ratio of refrigeration output to electrical power input (e.g. COP 3.5 means 3.5 kW cooling per 1 kW electricity)</t>
+        </is>
       </c>
       <c r="R8" t="inlineStr">
         <is>
@@ -6135,8 +6150,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -5028,11 +5028,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>* "VNA" → AGV stores/retrieves in very narrow aisles (&lt;2m), lifts to tall racking (&gt;8m), high-bay warehouse. ONLY classify as VNA if the tender explicitly requires VNA capability for the AGVs being procured. If VNA racking is mentioned as existing infrastructure, historical context, or out-of-scope aisles not covered by this tender — do NOT classify as VNA. Signals: aisle&lt;2m, lift&gt;8m, high-bay, VNA keyword
-* "Very Narrow Aisle" → Same as VNA
-* "Reach Truck" → AGV picks/places in medium-width racking aisles (2–3m), lift 4–8m. Signals: 2–3m aisle, racking, lift 4–8m
-* "Counterbalanced" → AGV transports pallets on wide aisles (≥3m) or open floor between fixed transfer stations, floor-level pickup/deposit. USE THIS for heavy pallet transport (&gt;1000 kg) in F&amp;B, food production, or manufacturing environments — even when MES or OPC-UA integration is mentioned. The presence of filling lines or MES does NOT imply Mobile AMR if payload is heavy. Signals: ≥3m aisle, floor transport, transfer stations, warehouse/logistics, heavy pallet (&gt;1000 kg)
-* "Forklift" → Generic forklift AGV</t>
+          <t>Pallet-lifting fork-based AGV for transport, picking, and placing of pallets, IBCs, and similar loads.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -5063,6 +5059,11 @@
           <t>VNA (very narrow aisle) operation is required.</t>
         </is>
       </c>
+      <c r="O4" t="inlineStr">
+        <is>
+          <t>{"VNA": "AGV stores/retrieves in very narrow aisles (&lt;2m), lifts to tall racking (&gt;8m), high-bay warehouse. ONLY classify as VNA if the tender explicitly requires VNA capability for the AGVs being procured. If VNA racking is mentioned as existing infrastructure, historical context, or out-of-scope aisles not covered by this tender — do NOT classify as VNA. Signals: aisle&lt;2m, lift&gt;8m, high-bay, VNA keyword", "Very Narrow Aisle": "Same as VNA", "Reach Truck": "AGV picks/places in medium-width racking aisles (2–3m), lift 4–8m. Signals: 2–3m aisle, racking, lift 4–8m", "Counterbalanced": "AGV transports pallets on wide aisles (≥3m) or open floor between fixed transfer stations, floor-level pickup/deposit. USE THIS for heavy pallet transport (&gt;1000 kg) in F&amp;B, food production, or manufacturing environments — even when MES or OPC-UA integration is mentioned. The presence of filling lines or MES does NOT imply Mobile AMR if payload is heavy. Signals: ≥3m aisle, floor transport, transfer stations, warehouse/logistics, heavy pallet (&gt;1000 kg)", "Forklift": "Generic forklift AGV"}</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -5092,7 +5093,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>* "Tugger" → AGV tows a train of trolleys/trailers without lifting; no direct pallet fork interface. Signals: trailer train, towing, milk run</t>
+          <t>AGV tows a train of trolleys/trailers without lifting; no direct pallet fork interface. Signals: trailer train, towing, milk run</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
@@ -5144,8 +5145,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>* "Mobile AMR" → Autonomous robot in PRODUCTION or MANUFACTURING environment (filling lines, assembly, processing), or with conveyor/shelf top modules, SLAM navigation, dispatched from MES/WMS. ONLY use for LIGHT payloads (typically &lt;1000 kg). If payload &gt;1000 kg or if the task is heavy pallet transport → use Forklift AGV instead. Signals: production, filling lines, manufacturing, SLAM, MES — BUT only if payload &lt;1000 kg
-* "Underride AMR" → Robot slides under carts/dollies and lifts them a few cm for transport. Signals: underride, dolly, cart</t>
+          <t>Autonomous robot in PRODUCTION or MANUFACTURING environment (filling lines, assembly, processing), or with conveyor/shelf top modules, SLAM navigation, dispatched from MES/WMS. ONLY use for LIGHT payloads (typically &lt;1000 kg). If payload &gt;1000 kg or if the task is heavy pallet transport → use Forklift AGV instead. Signals: production, filling lines, manufacturing, SLAM, MES — BUT only if payload &lt;1000 kg</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
@@ -5166,6 +5166,11 @@
       <c r="M6" t="inlineStr">
         <is>
           <t>amr_specific</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
+          <t>{"Underride AMR": "Robot slides under carts/dollies and lifts them a few cm for transport. Signals: underride, dolly, cart"}</t>
         </is>
       </c>
     </row>
@@ -6150,9 +6155,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -5202,7 +5202,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>* "Industrial Refrigeration" → Industrial refrigeration system for food &amp; beverage: process cooling, cold storage, or deep-freeze applications. Keywords: Kälteanlage, Kältetechnik, refrigeration, industrial cooling, cold store, deep freeze, blast freezer.</t>
+          <t>Industrial refrigeration system for food &amp; beverage: process cooling, cold storage, or deep-freeze applications. Keywords: Kälteanlage, Kältetechnik, refrigeration, industrial cooling, cold store, deep freeze, blast freezer.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
@@ -6155,9 +6155,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -6155,8 +6155,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -7089,7 +7089,7 @@
       </c>
       <c r="G22" s="68" t="inlineStr">
         <is>
-          <t>Max ramp gradient the loaded unit handles. Source: spec 'gradeability' — must appear as an explicit % value. The value represents the steepest ramp gradient (%) the loaded vehicle must climb: 10 % ≈ 5.7° incline; most flat indoor warehouse floors have 0 % gradient and this field should be null. Cond. K.O.: binds only where the site has ramps/dock inclines. NULL RULE: null unless a slope or gradient percentage is explicitly stated in the document. Do NOT apply typical industry values (e.g. '5%') when the document is silent on gradients.</t>
+          <t>Max ramp gradient the loaded unit handles. Source: spec 'gradeability' — must appear as an explicit % value. The value represents the steepest ramp gradient (%) the loaded vehicle must climb. Cond. K.O.: binds only where the site has ramps/dock inclines. NULL RULE: null unless a slope or gradient percentage is explicitly stated in the document. An approximate value (e.g. 'approximately X%') counts as explicit — do not null it solely because the document qualifies the figure. Do NOT infer or apply typical values when the document is silent on gradients.</t>
         </is>
       </c>
       <c r="H22" s="52" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -6155,9 +6155,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -6594,7 +6594,7 @@
       </c>
       <c r="C11" s="69" t="inlineStr">
         <is>
-          <t>None | Pallet EUR | Pallet ISO | Half-Euro | UK Pallet | Medium Euro | Tote | Plastic Bin | Bulk Bin | Roll Container | Custom Carrier</t>
+          <t>Pallet EUR | Pallet ISO | Half-Euro | UK Pallet | Medium Euro | Tote | Plastic Bin | Bulk Bin | Roll Container | Custom Carrier</t>
         </is>
       </c>
       <c r="E11" s="25" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -3008,7 +3008,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>K.O.</t>
+          <t>Scoring</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3019,11 +3019,6 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>Extract the COP (Coefficient of Performance) at rated conditions. Use the highest stated COP. NULL RULE: return null if not stated.</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>KO_IF_LT</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -6155,9 +6150,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -3008,7 +3008,7 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Scoring</t>
+          <t>Cond. K.O.</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
@@ -3019,6 +3019,11 @@
       <c r="G8" t="inlineStr">
         <is>
           <t>Extract the COP (Coefficient of Performance) at rated conditions. Use the highest stated COP. NULL RULE: return null if not stated.</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>KO_IF_LT</t>
         </is>
       </c>
       <c r="M8" t="n">
@@ -6150,9 +6155,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -2149,7 +2149,7 @@
       </c>
       <c r="C3" s="54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D3" s="54" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="C4" s="54" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="D4" s="54" t="inlineStr">
@@ -6155,9 +6155,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -8696,7 +8696,7 @@
       </c>
       <c r="G10" s="68" t="inlineStr">
         <is>
-          <t>VNA / very narrow aisle operation required. true/false. Source: 'VNA', aisle &lt; 2 m with high-bay racking. If true, required_drive_type must be 'VNA Turret'.</t>
+          <t>Set to true ONLY if this tender explicitly mandates VNA (Very Narrow Aisle) capability — aisle widths below 1.8 m requiring turret or side-loader technology. Set to false if VNA is not mentioned or standard aisles are assumed — this is the default for standard Forklift AGV tenders. Do NOT set to true if VNA is mentioned only as existing warehouse context, historical infrastructure, or areas outside this procurement scope. Null only if aisle requirements are genuinely ambiguous.</t>
         </is>
       </c>
       <c r="H10" s="52" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -2791,7 +2791,7 @@
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Extract ALL categories of refrigeration applications this supplier can serve. Do NOT assume from product name alone — extract only if stated explicitly. NULL RULE: if not explicitly stated, return null.</t>
+          <t>Which refrigeration application categor(ies) does this tender require? Output only values from the classification guide above, comma-separated if the tender requires more than one. Match on meaning in any document language, not on the English wording. NULL RULE: if the document gives no indication of the application category, return null.</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -6155,8 +6155,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -6155,9 +6155,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -6837,7 +6837,7 @@
       </c>
       <c r="G17" s="70" t="inlineStr">
         <is>
-          <t>Lowest rated operating temperature the vehicle must sustain, in °C. NULL RULE — READ FIRST: this field is null by default. Only fill it if the tender document explicitly states a minimum operating or ambient temperature (with a °C or K unit). If not stated, output null. Do NOT supply any default, typical, or example value. Do NOT copy numbers from this description or from rule notes. Do NOT confuse temperatures with dates, year/revision numbers, quantities, or project metadata. Source: a temperature range or operating condition in the document's environment, site requirements, or technical specification section. For a range (e.g. 'X to Y °C'), this field holds the lower bound (X).</t>
+          <t>Lowest rated operating temperature the vehicle must sustain, in °C. Source: a temperature range or operating condition in the document's environment, site requirements, or technical specification section. For a range (e.g. 'X to Y °C'), this field holds the lower bound (X). NULL RULE — READ FIRST: this field is null by default. Only fill it if the tender document explicitly states a minimum operating or ambient temperature (with a °C or K unit). If not stated, output null. Do NOT supply any default, typical, or example value. Do NOT copy numbers from this description or from rule notes. Do NOT confuse temperatures with dates, year/revision numbers, quantities, or project metadata.</t>
         </is>
       </c>
       <c r="H17" s="52" t="inlineStr">
@@ -6891,7 +6891,7 @@
       </c>
       <c r="G18" s="68" t="inlineStr">
         <is>
-          <t>Highest rated operating temperature the vehicle must sustain, in °C. NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a maximum operating or ambient temperature (with a °C or K unit). If not stated, output null. Do NOT supply a default, typical, or example value. Do NOT copy numbers from this description or from rule notes. Do NOT confuse temperatures with dates, year numbers, or version codes. Source: a temperature range or operating condition in the document's environment, site requirements, or technical specification section. For a range (e.g. 'X to Y °C'), this field holds the upper bound (Y).</t>
+          <t>Highest rated operating temperature the vehicle must sustain, in °C. Source: a temperature range or operating condition in the document's environment, site requirements, or technical specification section. For a range (e.g. 'X to Y °C'), this field holds the upper bound (Y). NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a maximum operating or ambient temperature (with a °C or K unit). If not stated, output null. Do NOT supply a default, typical, or example value. Do NOT copy numbers from this description or from rule notes. Do NOT confuse temperatures with dates, year numbers, or version codes.</t>
         </is>
       </c>
       <c r="H18" s="52" t="inlineStr">
@@ -6945,7 +6945,7 @@
       </c>
       <c r="G19" s="70" t="inlineStr">
         <is>
-          <t>Maximum rated relative humidity the vehicle must tolerate, as a percentage. NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a relative-humidity value as a % figure in an environment or technical-specification section. If no humidity percentage is stated, output null. Do NOT supply a default, typical, or example value, and do NOT copy numbers from this description or from rule/domain notes. Do NOT infer humidity from warehouse type, food/beverage context, washdown wording, or cold-storage environment. Source: an explicit relative-humidity % figure in the environment specification.</t>
+          <t>Maximum rated relative humidity the vehicle must tolerate, as a percentage. Source: an explicit relative-humidity % figure in the environment specification. NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a relative-humidity value as a % figure in an environment or technical-specification section. If no humidity percentage is stated, output null. Do NOT supply a default, typical, or example value, and do NOT copy numbers from this description or from rule/domain notes. Do NOT infer humidity from warehouse type, food/beverage context, washdown wording, or cold-storage environment.</t>
         </is>
       </c>
       <c r="H19" s="52" t="inlineStr">
@@ -8510,7 +8510,7 @@
       </c>
       <c r="G6" s="68" t="inlineStr">
         <is>
-          <t>Non-standard fork or attachment type required by the tender. NULL RULE — READ FIRST: null by default. Only output a value if the tender document EXPLICITLY names a non-standard attachment type — i.e. 'telescopic forks', 'side-shift', or 'clamp'. Standard forks are the default for all forklifts and must NOT be extracted as a requirement. Rotating forks are the default for VNA/narrow-aisle turret trucks and are resolved from the vehicle classification, not from this field. If the document does not explicitly name Telescopic, Side-Shift, or Clamp — output null. A null value never disqualifies any supplier; a wrong value eliminates qualified suppliers.</t>
+          <t>Non-standard fork or attachment type required by the tender. Standard forks are the default for all forklifts and must NOT be extracted as a requirement. Rotating forks are the default for VNA/narrow-aisle turret trucks and are resolved from the vehicle classification, not from this field. NULL RULE — READ FIRST: null by default. Only output a value if the tender document EXPLICITLY names a non-standard attachment type — i.e. 'telescopic forks', 'side-shift', or 'clamp'. If the document does not explicitly name Telescopic, Side-Shift, or Clamp — output null. A null value never disqualifies any supplier; a wrong value eliminates qualified suppliers.</t>
         </is>
       </c>
       <c r="H6" s="52" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -905,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S12"/>
+  <dimension ref="A1:U12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1004,6 +1004,16 @@
           <t>Value if Null</t>
         </is>
       </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>Post Extraction Derived</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>Display Label</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -1505,6 +1515,9 @@
         <is>
           <t>325dd61d-f828-4639-a128-fd5e1a1a3728</t>
         </is>
+      </c>
+      <c r="T12" t="b">
+        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -2656,7 +2669,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S14"/>
+  <dimension ref="A1:T14"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2762,6 +2775,11 @@
           <t>Value if Null</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Display Label</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
@@ -2989,6 +3007,11 @@
           <t>c7989fc1-f256-4159-9c4c-ae3f481836ff</t>
         </is>
       </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Certifications IK</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -3040,6 +3063,11 @@
       <c r="R8" t="inlineStr">
         <is>
           <t>b5204d0e-9069-4f9b-844a-b464bf2c2ef7</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>COP Efficiency (COP)</t>
         </is>
       </c>
     </row>
@@ -6155,9 +6183,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B5:F5"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -6170,7 +6198,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S53"/>
+  <dimension ref="A1:T53"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="57" min="1" max="1"/>
@@ -6297,6 +6325,11 @@
           <t>Value if Null</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Display Label</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="62" t="inlineStr">
@@ -7743,6 +7776,11 @@
       <c r="R39" t="inlineStr">
         <is>
           <t>1830f69a-d29d-4a51-944f-32b621922117</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>VDA 5050 Compatible</t>
         </is>
       </c>
     </row>
@@ -8238,7 +8276,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S31"/>
+  <dimension ref="A1:T31"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="57" min="1" max="1"/>
@@ -8365,6 +8403,11 @@
           <t>Value if Null</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Display Label</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="62" t="inlineStr">
@@ -9496,7 +9539,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S20"/>
+  <dimension ref="A1:T20"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="57" min="1" max="1"/>
@@ -9623,6 +9666,11 @@
           <t>Value if Null</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Display Label</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="62" t="inlineStr">
@@ -10376,7 +10424,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:S44"/>
+  <dimension ref="A1:T44"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.6640625" defaultRowHeight="15"/>
   <cols>
     <col width="30" customWidth="1" style="57" min="1" max="1"/>
@@ -10503,6 +10551,11 @@
           <t>Value if Null</t>
         </is>
       </c>
+      <c r="T2" t="inlineStr">
+        <is>
+          <t>Display Label</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="15" customHeight="1" s="57">
       <c r="A3" s="62" t="inlineStr">
@@ -11824,6 +11877,11 @@
           <t>09ca5135-a860-4236-844e-d2b47e8db98d</t>
         </is>
       </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>Onboard UI</t>
+        </is>
+      </c>
     </row>
     <row r="38" ht="15" customHeight="1" s="57">
       <c r="A38" s="16" t="inlineStr">
@@ -12054,6 +12112,11 @@
       <c r="R44" t="inlineStr">
         <is>
           <t>23d088ad-1bd2-4bf7-83af-f4a170364e43</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>WMS Integration Native</t>
         </is>
       </c>
     </row>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -1006,11 +1006,6 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>Post Extraction Derived</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
           <t>Display Label</t>
         </is>
       </c>
@@ -1515,9 +1510,6 @@
         <is>
           <t>325dd61d-f828-4639-a128-fd5e1a1a3728</t>
         </is>
-      </c>
-      <c r="T12" t="b">
-        <v>1</v>
       </c>
     </row>
   </sheetData>
@@ -6183,9 +6175,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -905,7 +905,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U12"/>
+  <dimension ref="A1:T12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1236,7 +1236,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>HQ country of the selling company. Used as Cond. K.O. when buyer requires domestic or regional supplier. NULL RULE: output null unless the tender explicitly requires a domestic or specific-country supplier. Do NOT infer from buyer address or document language.</t>
+          <t>HQ country of the selling company. Used as Cond. K.O. when buyer requires domestic or regional supplier. NULL RULE: output null unless the tender explicitly requires a domestic or specific-country supplier. Do NOT infer from buyer address or document language. If a country requirement is stated, output the 2-letter ISO 3166-1 alpha-2 code in uppercase. Never output a country name, a region, or a word meaning "domestic".</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -6175,9 +6175,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -1132,12 +1132,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>None | DACH | EU | Global</t>
+          <t>None | Global | AT | BE | BG | HR | CY | CZ | DK | EE | FI | FR | DE | GR | HU | IE | IT | LV | LT | LU | MT | NL | PL | PT | RO | SK | SI | ES | SE | CH | NO | IS | LI | GB | AL | BA | ME | MK | RS | XK | UA | MD | BY | AD | MC | SM | VA</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>Cond. K.O.</t>
+          <t>Context</t>
         </is>
       </c>
       <c r="F4" t="inlineStr">
@@ -1147,12 +1147,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Geographic service &amp; support reach. Source: 'locations / service network'. Cond. K.O.: hard filter when the buyer needs fast on-site SLA in a specific region. 'None' = no own network stated. NULL RULE: output null unless the tender explicitly demands a service/support region. Do NOT infer coverage from the document language or buyer location.</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>KO_SUBSET</t>
+          <t>Geographic service &amp; support reach. Source: 'locations / service network'. Informational (Context) — shown to the buyer, not a hard filter. If the tender explicitly states one or more countries/regions for required on-site service, output the corresponding 2-letter ISO 3166-1 alpha-2 country codes in uppercase, comma-separated. Output 'Global' if worldwide coverage is required. Output 'None' only if the buyer explicitly states no dedicated service network is required. NULL RULE: output null unless the tender explicitly demands a service/support region. Do NOT infer coverage from the document language or buyer location.</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -6175,8 +6170,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -6170,9 +6170,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
+    <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="G10" s="68" t="inlineStr">
         <is>
-          <t>Maximum payload the AGV must carry per trip, in kg. This value may appear as prose (e.g. 'a maximum of X kg', 'loads up to X kg', 'pallets weigh up to X kg') OR as a table column (labelled 'Max Loaded weight' / 'gross weight'). Read BOTH prose sentences and table cells — do not restrict search to tables only. In tables, use the loaded/gross weight — IGNORE 'tare weight' / 'empty pallet weight'. If a range or several load types are given, report the heaviest stated number. NULL RULE: Output null only if no maximum load weight is stated anywhere in the document text. CONSERVATIVE EXTRACTION: if multiple values are stated, extract the MAXIMUM — the supplier must meet or exceed this threshold.</t>
+          <t>Maximum payload the AGV must carry per trip, in kg. This value may appear as prose (e.g. 'a maximum of X kg', 'loads up to X kg', 'pallets weigh up to X kg') OR as a table column (labelled 'Max Loaded weight' / 'gross weight'). Read BOTH prose sentences and table cells — do not restrict search to tables only. In tables, use the loaded/gross weight — IGNORE 'tare weight' / 'empty pallet weight'. If a range or several load types are given, report the heaviest stated number. NULL RULE: Output null only if no maximum load weight is stated anywhere in the document text.</t>
         </is>
       </c>
       <c r="H10" s="52" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -6170,9 +6170,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -10260,7 +10260,7 @@
       </c>
       <c r="G18" s="70" t="inlineStr">
         <is>
-          <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If doc states mm (e.g. 2700 mm) → divide by 1000 → 2.7. Hard filter; decisive for VNA. WARNING: Do NOT confuse aisle width with other dimensions. Source terms: 'Gangbreite', 'aisle width', 'working aisle'. If no explicit aisle width is stated → output null.</t>
+          <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If the document states the value in mm, divide by 1000 to convert to meters. Hard filter; decisive for VNA. WARNING: Do NOT confuse aisle width with other dimensions. Source terms: 'Gangbreite', 'aisle width', 'working aisle'. If no explicit aisle width is stated → output null.</t>
         </is>
       </c>
       <c r="H18" s="52" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="G20" s="71" t="inlineStr">
         <is>
-          <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If doc states mm (e.g. 2700 mm) → divide by 1000 → 2.7. Hard filter; decisive for VNA.</t>
+          <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If the document states the value in mm, divide by 1000 to convert to meters. Hard filter; decisive for VNA.</t>
         </is>
       </c>
       <c r="H20" s="52" t="inlineStr">
@@ -11445,7 +11445,7 @@
       </c>
       <c r="G27" s="68" t="inlineStr">
         <is>
-          <t>Pod/shelf footprint the robot drives under (e.g. 880×880, 1020×1020). Source: spec 'shelf size'. Cond. K.O.: binds when matching existing shelving dimensions.</t>
+          <t>Pod/shelf footprint the robot drives under, as length×width (typically in mm). Source: spec 'shelf size'. Cond. K.O.: binds when matching existing shelving dimensions. NULL RULE: output null unless the document explicitly states shelf/pod footprint dimensions.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -1110,7 +1110,7 @@
       </c>
       <c r="Q3" t="inlineStr">
         <is>
-          <t>How many weeks lead time until commissioning is acceptable?</t>
+          <t>What lead time until commissioning is acceptable?</t>
         </is>
       </c>
       <c r="R3" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Extract the MAXIMUM total cooling capacity in kW. Use the highest stated value. Do NOT convert from tons of refrigeration unless the document provides an explicit conversion. NULL RULE: return null if no explicit kW or TR figure is found.</t>
+          <t>Extract the MAXIMUM total cooling capacity. Use the highest stated value. Do NOT convert from tons of refrigeration unless the document provides an explicit conversion. NULL RULE: return null if no explicit kW or TR figure is found.</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
@@ -2886,7 +2886,7 @@
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Extract the MINIMUM evaporation or supply temperature the system can achieve in °C. Use the lowest (most negative) stated temperature target. NULL RULE: return null if not stated.</t>
+          <t>Extract the MINIMUM evaporation or supply temperature the system can achieve. Use the lowest (most negative) stated temperature target. NULL RULE: return null if not stated.</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
@@ -3028,7 +3028,7 @@
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Extract the COP (Coefficient of Performance) at rated conditions. Use the highest stated COP. NULL RULE: return null if not stated.</t>
+          <t>Extract the COP (Coefficient of Performance) at rated conditions. Use the highest stated value. NULL RULE: return null if not stated.</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
@@ -3176,7 +3176,7 @@
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Extract the MAXIMUM room volume in m³ this system can handle. NULL RULE: return null if not stated.</t>
+          <t>Extract the MAXIMUM room volume this system can handle. NULL RULE: return null if not stated.</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
@@ -3261,7 +3261,7 @@
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Extract the blast freezing throughput capacity in kg/h. NULL RULE: return null if not stated.</t>
+          <t>Extract the blast freezing throughput capacity. NULL RULE: return null if not stated.</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
@@ -3309,7 +3309,7 @@
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Extract the required pulldown time in hours (time to reach target temperature). Lower is better for supplier. NULL RULE: return null if not stated.</t>
+          <t>Extract the required pulldown time (time to reach target temperature). Lower is better for supplier. NULL RULE: return null if not stated.</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
@@ -6170,9 +6170,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
-    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -6576,7 +6576,7 @@
       </c>
       <c r="G10" s="68" t="inlineStr">
         <is>
-          <t>Maximum payload the AGV must carry per trip, in kg. This value may appear as prose (e.g. 'a maximum of X kg', 'loads up to X kg', 'pallets weigh up to X kg') OR as a table column (labelled 'Max Loaded weight' / 'gross weight'). Read BOTH prose sentences and table cells — do not restrict search to tables only. In tables, use the loaded/gross weight — IGNORE 'tare weight' / 'empty pallet weight'. If a range or several load types are given, report the heaviest stated number. NULL RULE: Output null only if no maximum load weight is stated anywhere in the document text.</t>
+          <t>Maximum payload the AGV must carry per trip. This value may appear as prose (e.g. 'a maximum of X kg', 'loads up to X kg', 'pallets weigh up to X kg') OR as a table column (labelled 'Max Loaded weight' / 'gross weight'). Read BOTH prose sentences and table cells — do not restrict search to tables only. In tables, use the loaded/gross weight — IGNORE 'tare weight' / 'empty pallet weight'. If a range or several load types are given, report the heaviest stated number. NULL RULE: Output null only if no maximum load weight is stated anywhere in the document text.</t>
         </is>
       </c>
       <c r="H10" s="52" t="inlineStr">
@@ -6733,7 +6733,7 @@
       </c>
       <c r="Q14" s="64" t="inlineStr">
         <is>
-          <t>What maximum speed should the AGV achieve? (m/s)</t>
+          <t>What maximum speed should the AGV achieve?</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -6776,7 +6776,7 @@
       </c>
       <c r="Q15" s="64" t="inlineStr">
         <is>
-          <t>Vehicle length. (mm; for reference only)</t>
+          <t>Vehicle length. (for reference only)</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="Q16" s="64" t="inlineStr">
         <is>
-          <t>Vehicle width. (mm; for reference only)</t>
+          <t>Vehicle width. (for reference only)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -6857,7 +6857,7 @@
       </c>
       <c r="G17" s="70" t="inlineStr">
         <is>
-          <t>Lowest rated operating temperature the vehicle must sustain, in °C. Source: a temperature range or operating condition in the document's environment, site requirements, or technical specification section. For a range (e.g. 'X to Y °C'), this field holds the lower bound (X). NULL RULE — READ FIRST: this field is null by default. Only fill it if the tender document explicitly states a minimum operating or ambient temperature (with a °C or K unit). If not stated, output null. Do NOT supply any default, typical, or example value. Do NOT copy numbers from this description or from rule notes. Do NOT confuse temperatures with dates, year/revision numbers, quantities, or project metadata.</t>
+          <t>Lowest rated operating temperature the vehicle must sustain. Source: a temperature range or operating condition in the document's environment, site requirements, or technical specification section. For a range (e.g. 'X to Y °C'), this field holds the lower bound (X). NULL RULE — READ FIRST: this field is null by default. Only fill it if the tender document explicitly states a minimum operating or ambient temperature (with a °C or K unit). If not stated, output null. Do NOT supply any default, typical, or example value. Do NOT copy numbers from this description or from rule notes. Do NOT confuse temperatures with dates, year/revision numbers, quantities, or project metadata.</t>
         </is>
       </c>
       <c r="H17" s="52" t="inlineStr">
@@ -6873,7 +6873,7 @@
       </c>
       <c r="Q17" s="64" t="inlineStr">
         <is>
-          <t>What is the minimum temperature at the operating site? (°C; e.g. -20°C for cold storage)</t>
+          <t>What is the minimum temperature at the operating site?</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -6911,7 +6911,7 @@
       </c>
       <c r="G18" s="68" t="inlineStr">
         <is>
-          <t>Highest rated operating temperature the vehicle must sustain, in °C. Source: a temperature range or operating condition in the document's environment, site requirements, or technical specification section. For a range (e.g. 'X to Y °C'), this field holds the upper bound (Y). NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a maximum operating or ambient temperature (with a °C or K unit). If not stated, output null. Do NOT supply a default, typical, or example value. Do NOT copy numbers from this description or from rule notes. Do NOT confuse temperatures with dates, year numbers, or version codes.</t>
+          <t>Highest rated operating temperature the vehicle must sustain. Source: a temperature range or operating condition in the document's environment, site requirements, or technical specification section. For a range (e.g. 'X to Y °C'), this field holds the upper bound (Y). NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a maximum operating or ambient temperature (with a °C or K unit). If not stated, output null. Do NOT supply a default, typical, or example value. Do NOT copy numbers from this description or from rule notes. Do NOT confuse temperatures with dates, year numbers, or version codes.</t>
         </is>
       </c>
       <c r="H18" s="52" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="Q18" s="64" t="inlineStr">
         <is>
-          <t>What is the maximum temperature at the operating site? (°C; e.g. 30°C for production hall)</t>
+          <t>What is the maximum temperature at the operating site?</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -6965,7 +6965,7 @@
       </c>
       <c r="G19" s="70" t="inlineStr">
         <is>
-          <t>Maximum rated relative humidity the vehicle must tolerate, as a percentage. Source: an explicit relative-humidity % figure in the environment specification. NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a relative-humidity value as a % figure in an environment or technical-specification section. If no humidity percentage is stated, output null. Do NOT supply a default, typical, or example value, and do NOT copy numbers from this description or from rule/domain notes. Do NOT infer humidity from warehouse type, food/beverage context, washdown wording, or cold-storage environment.</t>
+          <t>Maximum rated relative humidity the vehicle must tolerate. Source: an explicit relative-humidity % figure in the environment specification. NULL RULE — READ FIRST: null by default. Only fill it if the document explicitly states a relative-humidity value as a % figure in an environment or technical-specification section. If no humidity percentage is stated, output null. Do NOT supply a default, typical, or example value, and do NOT copy numbers from this description or from rule/domain notes. Do NOT infer humidity from warehouse type, food/beverage context, washdown wording, or cold-storage environment.</t>
         </is>
       </c>
       <c r="H19" s="52" t="inlineStr">
@@ -6981,7 +6981,7 @@
       </c>
       <c r="Q19" s="64" t="inlineStr">
         <is>
-          <t>What is the maximum relative humidity at the operating site? (%)</t>
+          <t>What is the maximum relative humidity at the operating site?</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -7125,7 +7125,7 @@
       </c>
       <c r="Q22" s="64" t="inlineStr">
         <is>
-          <t>How steep is the steepest driving route in the operating area? (% gradient; e.g. 1.5 for a 1.5% ramp)</t>
+          <t>How steep is the steepest driving route in the operating area?</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -7214,7 +7214,7 @@
       </c>
       <c r="G25" s="68" t="inlineStr">
         <is>
-          <t>General docking/stop positioning accuracy at a target (e.g. ±5–10 mm on premium units). Source: spec 'positioning / stop accuracy'. Tighter = reliable hand-off. (moved here; forklift adds detailed pick/drop accuracy on top)</t>
+          <t>General docking/stop positioning accuracy at a target (e.g. ±5–10 on premium units). Source: spec 'positioning / stop accuracy'. Tighter = reliable hand-off. (moved here; forklift adds detailed pick/drop accuracy on top)</t>
         </is>
       </c>
       <c r="I25" s="50" t="n">
@@ -7233,7 +7233,7 @@
       </c>
       <c r="Q25" s="64" t="inlineStr">
         <is>
-          <t>How precisely must the AGV position at transfer or pickup points? (mm deviation)</t>
+          <t>How precisely must the AGV position at transfer or pickup points?</t>
         </is>
       </c>
       <c r="R25" t="inlineStr">
@@ -7321,7 +7321,7 @@
       </c>
       <c r="G28" s="70" t="inlineStr">
         <is>
-          <t>Operating hours per charge. Source: 'runtime / operating time'. Pair with charge_time &amp; autonomous_charging for true uptime. (consolidated)</t>
+          <t>Operating time per charge. Source: 'runtime / operating time'. Pair with charge_time &amp; autonomous_charging for true uptime. (consolidated)</t>
         </is>
       </c>
       <c r="I28" s="50" t="n">
@@ -7337,7 +7337,7 @@
       </c>
       <c r="Q28" s="64" t="inlineStr">
         <is>
-          <t>How many hours of operating time per charge are required as a minimum? (h)</t>
+          <t>What operating time per charge is required as a minimum?</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">
@@ -7375,12 +7375,12 @@
       </c>
       <c r="G29" s="68" t="inlineStr">
         <is>
-          <t>Recharge / fast-charge duration. Source: 'charging time' (e.g. Geek+ ~10 min opportunity; Locus Vector ~60 min full). Short charge + auto-charging ≈ continuous run. (consolidated)</t>
+          <t>Recharge / fast-charge duration. Source: 'charging time'. Short charge + auto-charging ≈ continuous run. (consolidated)</t>
         </is>
       </c>
       <c r="Q29" s="64" t="inlineStr">
         <is>
-          <t>What is the maximum acceptable duration of a full charging cycle? (min)</t>
+          <t>What is the maximum acceptable duration of a full charging cycle?</t>
         </is>
       </c>
       <c r="R29" t="inlineStr">
@@ -8122,7 +8122,7 @@
       </c>
       <c r="Q49" s="64" t="inlineStr">
         <is>
-          <t>What budget is available for the AGV project? (EUR)</t>
+          <t>What budget is available for the AGV project?</t>
         </is>
       </c>
       <c r="R49" t="inlineStr">
@@ -8449,7 +8449,7 @@
       </c>
       <c r="Q4" s="64" t="inlineStr">
         <is>
-          <t>How high must the device lift loads? Enter the maximum pick height in the rack. (mm; e.g. 10,000 mm = 10 m for high-bay storage)</t>
+          <t>How high must the device lift loads? Enter the maximum pick height in the rack.</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -8503,7 +8503,7 @@
       </c>
       <c r="Q5" s="64" t="inlineStr">
         <is>
-          <t>What is the height of the lowest doorways or passages in the operating area? (mm)</t>
+          <t>What is the height of the lowest doorways or passages in the operating area?</t>
         </is>
       </c>
       <c r="R5" t="inlineStr">
@@ -8597,7 +8597,7 @@
       </c>
       <c r="Q7" s="64" t="inlineStr">
         <is>
-          <t>What fork spacing is required for the load carriers? (mm)</t>
+          <t>What fork spacing is required for the load carriers?</t>
         </is>
       </c>
       <c r="R7" t="inlineStr">
@@ -8865,7 +8865,7 @@
       </c>
       <c r="Q14" s="64" t="inlineStr">
         <is>
-          <t>How precisely must the AMR deposit loads laterally? (mm)</t>
+          <t>How precisely must the AMR deposit loads laterally?</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -8908,7 +8908,7 @@
       </c>
       <c r="Q15" s="64" t="inlineStr">
         <is>
-          <t>How precisely must the AMR deposit loads in depth? (mm)</t>
+          <t>How precisely must the AMR deposit loads in depth?</t>
         </is>
       </c>
       <c r="R15" t="inlineStr">
@@ -9005,7 +9005,7 @@
       </c>
       <c r="Q17" s="64" t="inlineStr">
         <is>
-          <t>What lateral precision is required when picking up loads? (mm)</t>
+          <t>What lateral precision is required when picking up loads?</t>
         </is>
       </c>
       <c r="R17" t="inlineStr">
@@ -9048,7 +9048,7 @@
       </c>
       <c r="Q18" s="64" t="inlineStr">
         <is>
-          <t>What depth precision is required during order picking? (mm)</t>
+          <t>What depth precision is required during order picking?</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="G4" s="68" t="inlineStr">
         <is>
-          <t>Total towed load in kg. [TUGGER ONLY] — output null unless required_product_type is 'Tugger AGV'. Source: 'Schleppkraft / towing capacity'.</t>
+          <t>Total towed load. [TUGGER ONLY] — output null unless required_product_type is 'Tugger AGV'. Source: 'Schleppkraft / towing capacity'.</t>
         </is>
       </c>
       <c r="H4" s="52" t="inlineStr">
@@ -9712,7 +9712,7 @@
       </c>
       <c r="Q4" s="64" t="inlineStr">
         <is>
-          <t>What is the maximum total weight of the train? (kg; sum of all trailers including load; e.g. 5,000 kg)</t>
+          <t>What is the maximum total weight of the train?</t>
         </is>
       </c>
       <c r="R4" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="Q8" s="64" t="inlineStr">
         <is>
-          <t>What positioning tolerance is acceptable for automatic coupling? (mm)</t>
+          <t>What positioning tolerance is acceptable for automatic coupling?</t>
         </is>
       </c>
       <c r="R8" t="inlineStr">
@@ -10314,7 +10314,7 @@
       </c>
       <c r="G19" s="68" t="inlineStr">
         <is>
-          <t>Tugger turning radius (tractor alone). Source: spec 'turning radius' (e.g. Vecna ATG ≈ 2,900 mm / 9'6"). Hard filter for tight bends &amp; dock turns.</t>
+          <t>Tugger turning radius (tractor alone). Source: spec 'turning radius' (e.g. Vecna ATG ≈ 2,900 / 9'6"). Hard filter for tight bends &amp; dock turns.</t>
         </is>
       </c>
       <c r="H19" s="52" t="inlineStr">
@@ -10330,7 +10330,7 @@
       </c>
       <c r="Q19" s="64" t="inlineStr">
         <is>
-          <t>How much space is available for cornering? (mm; vehicle turning radius must be smaller)</t>
+          <t>How much space is available for cornering? (vehicle turning radius must be smaller)</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="Q9" s="64" t="inlineStr">
         <is>
-          <t>How high must the AMR lift loads or shelving units? (mm)</t>
+          <t>How high must the AMR lift loads or shelving units?</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -10842,7 +10842,7 @@
       </c>
       <c r="Q10" s="64" t="inlineStr">
         <is>
-          <t>What minimum ground clearance is required? (mm; e.g. for floor unevenness)</t>
+          <t>What minimum ground clearance is required? (e.g. for floor unevenness)</t>
         </is>
       </c>
       <c r="R10" t="inlineStr">
@@ -10991,6 +10991,11 @@
         </is>
       </c>
       <c r="C14" s="69" t="n"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="E14" s="30" t="inlineStr">
         <is>
           <t>Scoring</t>
@@ -11008,7 +11013,7 @@
       </c>
       <c r="Q14" s="64" t="inlineStr">
         <is>
-          <t>At what height range must the AMR pick up carts or carriers? (mm)</t>
+          <t>At what height range must the AMR pick up carts or carriers?</t>
         </is>
       </c>
       <c r="R14" t="inlineStr">
@@ -11070,7 +11075,7 @@
       </c>
       <c r="Q16" s="64" t="inlineStr">
         <is>
-          <t>How much space is available for turning movements? (mm; turning radius must be smaller)</t>
+          <t>How much space is available for turning movements? (turning radius must be smaller)</t>
         </is>
       </c>
       <c r="R16" t="inlineStr">
@@ -11129,7 +11134,7 @@
       </c>
       <c r="Q19" s="64" t="inlineStr">
         <is>
-          <t>What depth precision is required during order picking? (mm)</t>
+          <t>What depth precision is required during order picking?</t>
         </is>
       </c>
       <c r="R19" t="inlineStr">
@@ -11215,7 +11220,7 @@
       </c>
       <c r="Q21" s="64" t="inlineStr">
         <is>
-          <t>How precisely must the AMR deposit loads laterally? (mm)</t>
+          <t>How precisely must the AMR deposit loads laterally?</t>
         </is>
       </c>
       <c r="R21" t="inlineStr">
@@ -11258,7 +11263,7 @@
       </c>
       <c r="Q22" s="64" t="inlineStr">
         <is>
-          <t>How precisely must the AMR deposit loads in depth? (mm)</t>
+          <t>How precisely must the AMR deposit loads in depth?</t>
         </is>
       </c>
       <c r="R22" t="inlineStr">
@@ -11412,7 +11417,7 @@
       </c>
       <c r="Q26" s="64" t="inlineStr">
         <is>
-          <t>How high are the storage racks the AMR should serve? (mm)</t>
+          <t>How high are the storage racks the AMR should serve?</t>
         </is>
       </c>
       <c r="R26" t="inlineStr">
@@ -11433,6 +11438,11 @@
         </is>
       </c>
       <c r="C27" s="67" t="n"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>mm</t>
+        </is>
+      </c>
       <c r="E27" s="29" t="inlineStr">
         <is>
           <t>Cond. K.O.</t>
@@ -11445,7 +11455,7 @@
       </c>
       <c r="G27" s="68" t="inlineStr">
         <is>
-          <t>Pod/shelf footprint the robot drives under, as length×width (typically in mm). Source: spec 'shelf size'. Cond. K.O.: binds when matching existing shelving dimensions. NULL RULE: output null unless the document explicitly states shelf/pod footprint dimensions.</t>
+          <t>Pod/shelf footprint the robot drives under, as length×width. Source: spec 'shelf size'. Cond. K.O.: binds when matching existing shelving dimensions. NULL RULE: output null unless the document explicitly states shelf/pod footprint dimensions.</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
@@ -11455,7 +11465,7 @@
       </c>
       <c r="Q27" s="64" t="inlineStr">
         <is>
-          <t>What is the footprint of the storage units? (mm)</t>
+          <t>What is the footprint of the storage units?</t>
         </is>
       </c>
       <c r="R27" t="inlineStr">
@@ -11498,7 +11508,7 @@
       </c>
       <c r="Q28" s="64" t="inlineStr">
         <is>
-          <t>What is the minimum storage area for the AMR system? (m²)</t>
+          <t>What is the minimum storage area for the AMR system?</t>
         </is>
       </c>
       <c r="R28" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -6170,9 +6170,9 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
-    <mergeCell ref="B5:F5"/>
     <mergeCell ref="B6:F6"/>
     <mergeCell ref="B3:F3"/>
+    <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" paperSize="9" horizontalDpi="300" verticalDpi="300"/>
@@ -8418,7 +8418,7 @@
       <c r="C4" s="67" t="n"/>
       <c r="D4" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E4" s="25" t="inlineStr">
@@ -8433,7 +8433,7 @@
       </c>
       <c r="G4" s="68" t="inlineStr">
         <is>
-          <t>AGV fork lift height in METERS — the height the forks travel, NOT building height, rack height or storage height. Source: 'Hubhöhe / lift height / fork height' in the AGV specification. If only building or rack height is stated → null. NULL RULE: null unless the document explicitly states a required AGV lift height as a technical specification with its own value and unit. Do NOT confuse with transfer station height, conveyor height, rack height, or building height — these are site dimensions, not AGV specifications. Do NOT compute, derive, or estimate the lift height from any other stated quantity — pallet height, stack height, number of storage levels, or rack capacity are design inputs, not AGV lift specifications. A lift height obtained by calculation rather than read directly from an AGV specification has no source sentence and must be output as null.</t>
+          <t>AGV fork lift height — the height the forks travel, NOT building height, rack height or storage height. Source: 'Hubhöhe / lift height / fork height' in the AGV specification. If only building or rack height is stated → null. NULL RULE: null unless the document explicitly states a required AGV lift height as a technical specification with its own value and unit. Do NOT confuse with transfer station height, conveyor height, rack height, or building height — these are site dimensions, not AGV specifications. Do NOT compute, derive, or estimate the lift height from any other stated quantity — pallet height, stack height, number of storage levels, or rack capacity are design inputs, not AGV lift specifications. A lift height obtained by calculation rather than read directly from an AGV specification has no source sentence and must be output as null.</t>
         </is>
       </c>
       <c r="H4" s="52" t="inlineStr">
@@ -8442,10 +8442,10 @@
         </is>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="N4" t="n">
-        <v>30</v>
+        <v>30000</v>
       </c>
       <c r="Q4" s="64" t="inlineStr">
         <is>
@@ -8662,7 +8662,7 @@
       <c r="C9" s="69" t="n"/>
       <c r="D9" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E9" s="25" t="inlineStr">
@@ -8677,7 +8677,7 @@
       </c>
       <c r="G9" s="70" t="inlineStr">
         <is>
-          <t>Minimum working aisle width available in the facility, in METERS. ONLY extract if the document explicitly states an aisle, corridor, or rack-to-rack width. Source terms: 'Gangbreite', 'aisle width', 'working aisle', 'corridor width'. If no explicit width is stated anywhere in the document → output null. Do NOT infer or estimate a width from the warehouse type, the forklift category, or any typical or standard value — absence of a stated width means null, never a guess. If the figure is given in mm, divide by 1000. Do NOT confuse aisle width with lift height, rack height, vehicle height, or transfer-station height.</t>
+          <t>Minimum working aisle width available in the facility. ONLY extract if the document explicitly states an aisle, corridor, or rack-to-rack width. Source terms: 'Gangbreite', 'aisle width', 'working aisle', 'corridor width'. If no explicit width is stated anywhere in the document → output null. Do NOT infer or estimate a width from the warehouse type, the forklift category, or any typical or standard value — absence of a stated width means null, never a guess. Do NOT confuse aisle width with lift height, rack height, vehicle height, or transfer-station height.</t>
         </is>
       </c>
       <c r="H9" s="52" t="inlineStr">
@@ -8686,14 +8686,14 @@
         </is>
       </c>
       <c r="M9" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="N9" t="n">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="Q9" s="64" t="inlineStr">
         <is>
-          <t>How wide are the narrowest aisles in your facility? The AGV must manoeuvre within this width. (mm; e.g. 1,800 mm for narrow-aisle operation)</t>
+          <t>How wide are the narrowest aisles in your facility? The AGV must manoeuvre within this width.</t>
         </is>
       </c>
       <c r="R9" t="inlineStr">
@@ -10245,7 +10245,7 @@
       <c r="C18" s="69" t="n"/>
       <c r="D18" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E18" s="25" t="inlineStr">
@@ -10260,7 +10260,7 @@
       </c>
       <c r="G18" s="70" t="inlineStr">
         <is>
-          <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If the document states the value in mm, divide by 1000 to convert to meters. Hard filter; decisive for VNA. WARNING: Do NOT confuse aisle width with other dimensions. Source terms: 'Gangbreite', 'aisle width', 'working aisle'. If no explicit aisle width is stated → output null.</t>
+          <t>Min working aisle width. Source: 'Gangbreite / aisle width'. Hard filter; decisive for VNA. WARNING: Do NOT confuse aisle width with other dimensions. Source terms: 'Gangbreite', 'aisle width', 'working aisle'. If no explicit aisle width is stated → output null.</t>
         </is>
       </c>
       <c r="H18" s="52" t="inlineStr">
@@ -10269,14 +10269,14 @@
         </is>
       </c>
       <c r="M18" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="N18" t="n">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="Q18" s="64" t="inlineStr">
         <is>
-          <t>How wide are the narrowest aisles in your facility? The AGV must manoeuvre within this width. (mm; e.g. 1,800 mm for narrow-aisle operation)</t>
+          <t>How wide are the narrowest aisles in your facility? The AGV must manoeuvre within this width.</t>
         </is>
       </c>
       <c r="R18" t="inlineStr">
@@ -10353,7 +10353,7 @@
       <c r="C20" s="71" t="n"/>
       <c r="D20" t="inlineStr">
         <is>
-          <t>m</t>
+          <t>mm</t>
         </is>
       </c>
       <c r="E20" s="40" t="inlineStr">
@@ -10368,7 +10368,7 @@
       </c>
       <c r="G20" s="71" t="inlineStr">
         <is>
-          <t>Min working aisle in METERS (not mm). Source: 'Gangbreite / aisle width'. If the document states the value in mm, divide by 1000 to convert to meters. Hard filter; decisive for VNA.</t>
+          <t>Min working aisle width. Source: 'Gangbreite / aisle width'. Hard filter; decisive for VNA.</t>
         </is>
       </c>
       <c r="H20" s="52" t="inlineStr">
@@ -10377,14 +10377,14 @@
         </is>
       </c>
       <c r="M20" t="n">
-        <v>0.5</v>
+        <v>500</v>
       </c>
       <c r="N20" t="n">
-        <v>5</v>
+        <v>5000</v>
       </c>
       <c r="Q20" s="64" t="inlineStr">
         <is>
-          <t>How wide are the narrowest passages in the entire travel area including trailers? (mm)</t>
+          <t>How wide are the narrowest passages in the entire travel area including trailers?</t>
         </is>
       </c>
       <c r="R20" t="inlineStr">

--- a/Spec/haystacked_AP0_field_spec_v0_10.xlsx
+++ b/Spec/haystacked_AP0_field_spec_v0_10.xlsx
@@ -2813,7 +2813,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>cooling_capacity_kw</t>
+          <t>cooling_capacity</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -2861,7 +2861,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>temperature_min_celsius</t>
+          <t>temperature_min</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -3103,7 +3103,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>temperature_stability_k</t>
+          <t>temperature_stability</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -3151,7 +3151,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>room_volume_m3_max</t>
+          <t>room_volume_max</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -3236,7 +3236,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>blast_freeze_capacity_kg_h</t>
+          <t>blast_freeze_capacity</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -3284,7 +3284,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>pulldown_time_h</t>
+          <t>pulldown_time</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6170,8 +6170,8 @@
   </sheetData>
   <mergeCells count="4">
     <mergeCell ref="B50:F50"/>
+    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B6:F6"/>
-    <mergeCell ref="B3:F3"/>
     <mergeCell ref="B5:F5"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -6550,7 +6550,7 @@
     <row r="10" ht="15" customHeight="1" s="57">
       <c r="A10" s="16" t="inlineStr">
         <is>
-          <t>max_payload_kg</t>
+          <t>max_payload</t>
         </is>
       </c>
       <c r="B10" s="23" t="inlineStr">
@@ -6702,7 +6702,7 @@
     <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>max_speed_ms</t>
+          <t>max_speed</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
@@ -6745,7 +6745,7 @@
     <row r="15" ht="15" customHeight="1" s="57">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>length_mm</t>
+          <t>vehicle_length</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
@@ -6788,7 +6788,7 @@
     <row r="16" ht="15" customHeight="1" s="57">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>width_mm</t>
+          <t>vehicle_width</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
@@ -6831,7 +6831,7 @@
     <row r="17" ht="15" customHeight="1" s="57">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>operating_temp_min_c</t>
+          <t>operating_temp_min</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
@@ -6885,7 +6885,7 @@
     <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>operating_temp_max_c</t>
+          <t>operating_temp_max</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
@@ -6939,7 +6939,7 @@
     <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>operating_humidity_max_pct</t>
+          <t>operating_humidity_max</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
@@ -7083,7 +7083,7 @@
     <row r="22" ht="15" customHeight="1" s="57">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>max_gradient_pct</t>
+          <t>max_gradient</t>
         </is>
       </c>
       <c r="B22" s="23" t="inlineStr">
@@ -7188,7 +7188,7 @@
     <row r="25" ht="15" customHeight="1" s="57">
       <c r="A25" s="16" t="inlineStr">
         <is>
-          <t>stop_accuracy_mm</t>
+          <t>stop_accuracy</t>
         </is>
       </c>
       <c r="B25" s="23" t="inlineStr">
@@ -7295,7 +7295,7 @@
     <row r="28" ht="15" customHeight="1" s="57">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>battery_runtime_h</t>
+          <t>battery_runtime</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
@@ -7349,7 +7349,7 @@
     <row r="29" ht="15" customHeight="1" s="57">
       <c r="A29" s="16" t="inlineStr">
         <is>
-          <t>charge_time_min</t>
+          <t>charge_time</t>
         </is>
       </c>
       <c r="B29" s="23" t="inlineStr">
@@ -8092,7 +8092,7 @@
     <row r="49" ht="15" customHeight="1" s="57">
       <c r="A49" s="16" t="inlineStr">
         <is>
-          <t>typical_project_value_eur</t>
+          <t>typical_project_value</t>
         </is>
       </c>
       <c r="B49" s="23" t="inlineStr">
@@ -8103,6 +8103,11 @@
       <c r="C49" s="67" t="inlineStr">
         <is>
           <t>&lt;50k | 50–250k | 250k–1M | &gt;1M</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>EUR</t>
         </is>
       </c>
       <c r="E49" s="31" t="inlineStr">
@@ -8407,7 +8412,7 @@
     <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>lifting_height_mm</t>
+          <t>lifting_height</t>
         </is>
       </c>
       <c r="B4" s="23" t="inlineStr">
@@ -8461,7 +8466,7 @@
     <row r="5" ht="15" customHeight="1" s="57">
       <c r="A5" s="19" t="inlineStr">
         <is>
-          <t>min_total_height_mm</t>
+          <t>min_total_height</t>
         </is>
       </c>
       <c r="B5" s="27" t="inlineStr">
@@ -8651,7 +8656,7 @@
     <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="19" t="inlineStr">
         <is>
-          <t>min_aisle_width_mm</t>
+          <t>min_aisle_width</t>
         </is>
       </c>
       <c r="B9" s="27" t="inlineStr">
@@ -8823,7 +8828,7 @@
     <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="16" t="inlineStr">
         <is>
-          <t>drop_accuracy_lat_mm</t>
+          <t>drop_accuracy_lat</t>
         </is>
       </c>
       <c r="B14" s="23" t="inlineStr">
@@ -8877,7 +8882,7 @@
     <row r="15" ht="15" customHeight="1" s="57">
       <c r="A15" s="19" t="inlineStr">
         <is>
-          <t>drop_accuracy_dep_mm</t>
+          <t>drop_accuracy_dep</t>
         </is>
       </c>
       <c r="B15" s="27" t="inlineStr">
@@ -8920,7 +8925,7 @@
     <row r="16" ht="15" customHeight="1" s="57">
       <c r="A16" s="16" t="inlineStr">
         <is>
-          <t>drop_accuracy_angle_deg</t>
+          <t>drop_accuracy_angle</t>
         </is>
       </c>
       <c r="B16" s="23" t="inlineStr">
@@ -8963,7 +8968,7 @@
     <row r="17" ht="15" customHeight="1" s="57">
       <c r="A17" s="19" t="inlineStr">
         <is>
-          <t>pick_req_accuracy_lat_mm</t>
+          <t>pick_req_accuracy_lat</t>
         </is>
       </c>
       <c r="B17" s="27" t="inlineStr">
@@ -9017,7 +9022,7 @@
     <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="16" t="inlineStr">
         <is>
-          <t>pick_req_accuracy_dep_mm</t>
+          <t>pick_req_accuracy_dep</t>
         </is>
       </c>
       <c r="B18" s="23" t="inlineStr">
@@ -9060,7 +9065,7 @@
     <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>pick_req_accuracy_angle_deg</t>
+          <t>pick_req_accuracy_angle</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
@@ -9670,7 +9675,7 @@
     <row r="4" ht="15" customHeight="1" s="57">
       <c r="A4" s="16" t="inlineStr">
         <is>
-          <t>towing_capacity_kg</t>
+          <t>towing_capacity</t>
         </is>
       </c>
       <c r="B4" s="23" t="inlineStr">
@@ -9876,7 +9881,7 @@
     <row r="8" ht="15" customHeight="1" s="57">
       <c r="A8" s="16" t="inlineStr">
         <is>
-          <t>auto_hitch_position_tolerance_mm</t>
+          <t>auto_hitch_position_tolerance</t>
         </is>
       </c>
       <c r="B8" s="23" t="inlineStr">
@@ -10234,7 +10239,7 @@
     <row r="18" ht="15" customHeight="1" s="57">
       <c r="A18" s="19" t="inlineStr">
         <is>
-          <t>min_aisle_width_mm</t>
+          <t>min_aisle_width</t>
         </is>
       </c>
       <c r="B18" s="27" t="inlineStr">
@@ -10288,7 +10293,7 @@
     <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="16" t="inlineStr">
         <is>
-          <t>turning_radius_mm</t>
+          <t>turning_radius</t>
         </is>
       </c>
       <c r="B19" s="23" t="inlineStr">
@@ -10342,7 +10347,7 @@
     <row r="20" ht="15" customHeight="1" s="57">
       <c r="A20" s="39" t="inlineStr">
         <is>
-          <t>tugger_min_aisle_width_mm</t>
+          <t>tugger_min_aisle_width</t>
         </is>
       </c>
       <c r="B20" s="39" t="inlineStr">
@@ -10746,7 +10751,7 @@
     <row r="9" ht="15" customHeight="1" s="57">
       <c r="A9" s="16" t="inlineStr">
         <is>
-          <t>lift_height_mm</t>
+          <t>lift_height</t>
         </is>
       </c>
       <c r="B9" s="23" t="inlineStr">
@@ -10800,7 +10805,7 @@
     <row r="10" ht="15" customHeight="1" s="57">
       <c r="A10" s="19" t="inlineStr">
         <is>
-          <t>min_ground_clearance_mm</t>
+          <t>min_ground_clearance</t>
         </is>
       </c>
       <c r="B10" s="27" t="inlineStr">
@@ -10982,7 +10987,7 @@
     <row r="14" ht="15" customHeight="1" s="57">
       <c r="A14" s="19" t="inlineStr">
         <is>
-          <t>cart_pickup_height_range_mm</t>
+          <t>cart_pickup_height_range</t>
         </is>
       </c>
       <c r="B14" s="27" t="inlineStr">
@@ -11033,7 +11038,7 @@
     <row r="16" ht="15" customHeight="1" s="57">
       <c r="A16" s="19" t="inlineStr">
         <is>
-          <t>min_turning_radius_mm</t>
+          <t>min_turning_radius</t>
         </is>
       </c>
       <c r="B16" s="27" t="inlineStr">
@@ -11103,7 +11108,7 @@
     <row r="19" ht="15" customHeight="1" s="57">
       <c r="A19" s="19" t="inlineStr">
         <is>
-          <t>pick_req_accuracy_dep_mm</t>
+          <t>pick_req_accuracy_dep</t>
         </is>
       </c>
       <c r="B19" s="27" t="inlineStr">
@@ -11146,7 +11151,7 @@
     <row r="20" ht="15" customHeight="1" s="57">
       <c r="A20" s="16" t="inlineStr">
         <is>
-          <t>pick_req_accuracy_angle_deg</t>
+          <t>pick_req_accuracy_angle</t>
         </is>
       </c>
       <c r="B20" s="23" t="inlineStr">
@@ -11189,7 +11194,7 @@
     <row r="21" ht="15" customHeight="1" s="57">
       <c r="A21" s="19" t="inlineStr">
         <is>
-          <t>drop_accuracy_lat_mm</t>
+          <t>drop_accuracy_lat</t>
         </is>
       </c>
       <c r="B21" s="27" t="inlineStr">
@@ -11232,7 +11237,7 @@
     <row r="22" ht="15" customHeight="1" s="57">
       <c r="A22" s="16" t="inlineStr">
         <is>
-          <t>drop_accuracy_dep_mm</t>
+          <t>drop_accuracy_dep</t>
         </is>
       </c>
       <c r="B22" s="23" t="inlineStr">
@@ -11275,7 +11280,7 @@
     <row r="23" ht="15" customHeight="1" s="57">
       <c r="A23" s="19" t="inlineStr">
         <is>
-          <t>drop_accuracy_angle_deg</t>
+          <t>drop_accuracy_angle</t>
         </is>
       </c>
       <c r="B23" s="27" t="inlineStr">
@@ -11375,7 +11380,7 @@
     <row r="26" ht="15" customHeight="1" s="57">
       <c r="A26" s="19" t="inlineStr">
         <is>
-          <t>shelf_height_mm</t>
+          <t>shelf_height</t>
         </is>
       </c>
       <c r="B26" s="27" t="inlineStr">
@@ -11429,7 +11434,7 @@
     <row r="27" ht="15" customHeight="1" s="57">
       <c r="A27" s="16" t="inlineStr">
         <is>
-          <t>shelf_footprint_mm</t>
+          <t>shelf_footprint</t>
         </is>
       </c>
       <c r="B27" s="23" t="inlineStr">
@@ -11477,7 +11482,7 @@
     <row r="28" ht="15" customHeight="1" s="57">
       <c r="A28" s="19" t="inlineStr">
         <is>
-          <t>min_grid_area_m2</t>
+          <t>min_grid_area</t>
         </is>
       </c>
       <c r="B28" s="27" t="inlineStr">
